--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2139C2-87C7-4017-89D5-761E09E05504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3FECDC-227B-4610-83E3-89E6717810FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="50">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,58 +54,127 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 27/10/2025</t>
-  </si>
-  <si>
-    <t>135054365</t>
-  </si>
-  <si>
-    <t>135028570</t>
-  </si>
-  <si>
-    <t>134932306</t>
-  </si>
-  <si>
-    <t>135050900</t>
-  </si>
-  <si>
-    <t>134963451</t>
-  </si>
-  <si>
-    <t>134994340</t>
-  </si>
-  <si>
-    <t>134988980</t>
-  </si>
-  <si>
-    <t>135033815</t>
-  </si>
-  <si>
-    <t>135054537</t>
-  </si>
-  <si>
-    <t>135055563</t>
-  </si>
-  <si>
-    <t>134983887</t>
-  </si>
-  <si>
-    <t>134986277</t>
-  </si>
-  <si>
-    <t>134995666</t>
-  </si>
-  <si>
-    <t>134996771</t>
-  </si>
-  <si>
-    <t>134999685</t>
-  </si>
-  <si>
-    <t>135051340</t>
-  </si>
-  <si>
-    <t>135073583</t>
+    <t>Relatório de Recusas Santander - 28/10/2025</t>
+  </si>
+  <si>
+    <t>134954593</t>
+  </si>
+  <si>
+    <t>134954580</t>
+  </si>
+  <si>
+    <t>134953873</t>
+  </si>
+  <si>
+    <t>134976368</t>
+  </si>
+  <si>
+    <t>135000174</t>
+  </si>
+  <si>
+    <t>134949643</t>
+  </si>
+  <si>
+    <t>135009736</t>
+  </si>
+  <si>
+    <t>135011662</t>
+  </si>
+  <si>
+    <t>135016864</t>
+  </si>
+  <si>
+    <t>135040056</t>
+  </si>
+  <si>
+    <t>135040123</t>
+  </si>
+  <si>
+    <t>134945073</t>
+  </si>
+  <si>
+    <t>135056992</t>
+  </si>
+  <si>
+    <t>135067409</t>
+  </si>
+  <si>
+    <t>134945001</t>
+  </si>
+  <si>
+    <t>135078174</t>
+  </si>
+  <si>
+    <t>135100764</t>
+  </si>
+  <si>
+    <t>135068300</t>
+  </si>
+  <si>
+    <t>135111265</t>
+  </si>
+  <si>
+    <t>134969357</t>
+  </si>
+  <si>
+    <t>134940138</t>
+  </si>
+  <si>
+    <t>134940600</t>
+  </si>
+  <si>
+    <t>134942677</t>
+  </si>
+  <si>
+    <t>134943358</t>
+  </si>
+  <si>
+    <t>134943983</t>
+  </si>
+  <si>
+    <t>134944838</t>
+  </si>
+  <si>
+    <t>134944891</t>
+  </si>
+  <si>
+    <t>134945877</t>
+  </si>
+  <si>
+    <t>134948611</t>
+  </si>
+  <si>
+    <t>134949601</t>
+  </si>
+  <si>
+    <t>134953644</t>
+  </si>
+  <si>
+    <t>134955203</t>
+  </si>
+  <si>
+    <t>134955467</t>
+  </si>
+  <si>
+    <t>135042534</t>
+  </si>
+  <si>
+    <t>135069992</t>
+  </si>
+  <si>
+    <t>134981862</t>
+  </si>
+  <si>
+    <t>135057013</t>
+  </si>
+  <si>
+    <t>135014593</t>
+  </si>
+  <si>
+    <t>135018905</t>
+  </si>
+  <si>
+    <t>135132162</t>
   </si>
   <si>
     <t>Relatório de Recusas 27.10.2025 a 02.11.2025</t>
@@ -138,8 +207,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -164,7 +233,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -172,41 +241,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -223,13 +262,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -549,7 +582,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -581,340 +614,340 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134971230</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="8" t="s">
+        <v>134942483</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <v>134988741</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>134987327</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>135019736</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>135015163</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>135026243</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>135046529</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>135048698</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>135048914</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>135050384</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
-        <v>135049543</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
-        <v>135050051</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
-        <v>135044777</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
-        <v>135052121</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
-        <v>135060115</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
-        <v>135048549</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
-        <v>135056897</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
-        <v>135083023</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>135058343</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -922,17 +955,17 @@
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
-        <v>135090745</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -940,17 +973,17 @@
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
-        <v>135052917</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="8" t="s">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -958,42 +991,44 @@
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
-        <v>135094626</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="8" t="s">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>134918888</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="8" t="s">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
@@ -1002,15 +1037,16 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
@@ -1019,15 +1055,16 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -1036,15 +1073,16 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -1053,15 +1091,16 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -1070,7 +1109,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1078,7 +1117,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
@@ -1087,7 +1126,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1095,7 +1134,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
@@ -1104,7 +1143,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1112,7 +1151,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -1121,7 +1160,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1129,7 +1168,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
@@ -1138,7 +1177,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1146,7 +1185,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
@@ -1155,7 +1194,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1163,7 +1202,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
@@ -1172,7 +1211,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1180,7 +1219,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -1189,7 +1228,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1197,7 +1236,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
@@ -1206,7 +1245,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1214,7 +1253,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
@@ -1223,7 +1262,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1231,7 +1270,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
@@ -1240,7 +1279,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1248,7 +1287,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
@@ -1257,7 +1296,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1265,7 +1304,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
@@ -1274,9 +1313,26 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A859DE7B-4A08-42CF-837B-61AF38FB7634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB63441-7AB0-41AC-A147-FB6B9FC29E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,19 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 28/10/2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 27.10.2025 a 02.11.2025</t>
-  </si>
-  <si>
-    <t>134962886</t>
-  </si>
-  <si>
-    <t>134962898</t>
-  </si>
-  <si>
-    <t>134963392</t>
-  </si>
-  <si>
-    <t>134975290</t>
-  </si>
-  <si>
-    <t>134970513</t>
-  </si>
-  <si>
-    <t>134972835</t>
+    <t>Relatório de Recusas Santander - 30/10/2025</t>
+  </si>
+  <si>
+    <t>134945204</t>
+  </si>
+  <si>
+    <t>134942378</t>
+  </si>
+  <si>
+    <t>134998471</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 27.10.2025 a 02.11.2025 (1)</t>
   </si>
 </sst>
 </file>
@@ -512,7 +503,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134944540</v>
+        <v>134938876</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -521,7 +512,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -530,7 +521,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
@@ -539,7 +530,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -548,7 +539,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -557,7 +548,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -566,7 +557,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
@@ -575,7 +566,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -583,57 +574,12 @@
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F8"/>
     </row>
   </sheetData>
@@ -650,31 +596,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB63441-7AB0-41AC-A147-FB6B9FC29E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7C3E0E-576F-4300-B126-EA0A1646F836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="46">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,19 +54,118 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 30/10/2025</t>
-  </si>
-  <si>
-    <t>134945204</t>
-  </si>
-  <si>
-    <t>134942378</t>
-  </si>
-  <si>
-    <t>134998471</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 27.10.2025 a 02.11.2025 (1)</t>
+    <t>Relatório de Recusas Santander - 31/10/2025 e 01/11/2025</t>
+  </si>
+  <si>
+    <t>135073326</t>
+  </si>
+  <si>
+    <t>135076966</t>
+  </si>
+  <si>
+    <t>135070167</t>
+  </si>
+  <si>
+    <t>135100689</t>
+  </si>
+  <si>
+    <t>135074617</t>
+  </si>
+  <si>
+    <t>135137862</t>
+  </si>
+  <si>
+    <t>135077032</t>
+  </si>
+  <si>
+    <t>135049162</t>
+  </si>
+  <si>
+    <t>135132787</t>
+  </si>
+  <si>
+    <t>135148311</t>
+  </si>
+  <si>
+    <t>135157305</t>
+  </si>
+  <si>
+    <t>135161501</t>
+  </si>
+  <si>
+    <t>135160469</t>
+  </si>
+  <si>
+    <t>135162510</t>
+  </si>
+  <si>
+    <t>135156075</t>
+  </si>
+  <si>
+    <t>135164353</t>
+  </si>
+  <si>
+    <t>135068030</t>
+  </si>
+  <si>
+    <t>135089128</t>
+  </si>
+  <si>
+    <t>135101302</t>
+  </si>
+  <si>
+    <t>135118291</t>
+  </si>
+  <si>
+    <t>135089966</t>
+  </si>
+  <si>
+    <t>135035358</t>
+  </si>
+  <si>
+    <t>135064123</t>
+  </si>
+  <si>
+    <t>135064936</t>
+  </si>
+  <si>
+    <t>135067216</t>
+  </si>
+  <si>
+    <t>135070255</t>
+  </si>
+  <si>
+    <t>135070455</t>
+  </si>
+  <si>
+    <t>135075513</t>
+  </si>
+  <si>
+    <t>135076206</t>
+  </si>
+  <si>
+    <t>135076764</t>
+  </si>
+  <si>
+    <t>135142225</t>
+  </si>
+  <si>
+    <t>135036209</t>
+  </si>
+  <si>
+    <t>135027110</t>
+  </si>
+  <si>
+    <t>135029391</t>
+  </si>
+  <si>
+    <t>135027742</t>
+  </si>
+  <si>
+    <t>135007494</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 27.10.2025 a 02.11.2025</t>
   </si>
 </sst>
 </file>
@@ -471,7 +570,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,7 +602,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134938876</v>
+        <v>135049705</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -512,7 +611,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -530,7 +629,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -548,7 +647,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -566,21 +665,576 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F8"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -596,31 +1250,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7C3E0E-576F-4300-B126-EA0A1646F836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2195E7-6F90-472A-9B8E-EEF42E72E721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,118 +54,106 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 31/10/2025 e 01/11/2025</t>
-  </si>
-  <si>
-    <t>135073326</t>
-  </si>
-  <si>
-    <t>135076966</t>
-  </si>
-  <si>
-    <t>135070167</t>
-  </si>
-  <si>
-    <t>135100689</t>
-  </si>
-  <si>
-    <t>135074617</t>
-  </si>
-  <si>
-    <t>135137862</t>
-  </si>
-  <si>
-    <t>135077032</t>
-  </si>
-  <si>
-    <t>135049162</t>
-  </si>
-  <si>
-    <t>135132787</t>
-  </si>
-  <si>
-    <t>135148311</t>
-  </si>
-  <si>
-    <t>135157305</t>
-  </si>
-  <si>
-    <t>135161501</t>
-  </si>
-  <si>
-    <t>135160469</t>
-  </si>
-  <si>
-    <t>135162510</t>
-  </si>
-  <si>
-    <t>135156075</t>
-  </si>
-  <si>
-    <t>135164353</t>
-  </si>
-  <si>
-    <t>135068030</t>
-  </si>
-  <si>
-    <t>135089128</t>
-  </si>
-  <si>
-    <t>135101302</t>
-  </si>
-  <si>
-    <t>135118291</t>
-  </si>
-  <si>
-    <t>135089966</t>
-  </si>
-  <si>
-    <t>135035358</t>
-  </si>
-  <si>
-    <t>135064123</t>
-  </si>
-  <si>
-    <t>135064936</t>
-  </si>
-  <si>
-    <t>135067216</t>
-  </si>
-  <si>
-    <t>135070255</t>
-  </si>
-  <si>
-    <t>135070455</t>
-  </si>
-  <si>
-    <t>135075513</t>
-  </si>
-  <si>
-    <t>135076206</t>
-  </si>
-  <si>
-    <t>135076764</t>
-  </si>
-  <si>
-    <t>135142225</t>
-  </si>
-  <si>
-    <t>135036209</t>
-  </si>
-  <si>
-    <t>135027110</t>
-  </si>
-  <si>
-    <t>135029391</t>
-  </si>
-  <si>
-    <t>135027742</t>
-  </si>
-  <si>
-    <t>135007494</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 27.10.2025 a 02.11.2025</t>
+    <t>Relatório de Recusas Santander - 03/11/2025</t>
+  </si>
+  <si>
+    <t>135105244</t>
+  </si>
+  <si>
+    <t>135133421</t>
+  </si>
+  <si>
+    <t>135140502</t>
+  </si>
+  <si>
+    <t>135137538</t>
+  </si>
+  <si>
+    <t>135133617</t>
+  </si>
+  <si>
+    <t>135133236</t>
+  </si>
+  <si>
+    <t>135155674</t>
+  </si>
+  <si>
+    <t>135156059</t>
+  </si>
+  <si>
+    <t>135155268</t>
+  </si>
+  <si>
+    <t>135156088</t>
+  </si>
+  <si>
+    <t>135162327</t>
+  </si>
+  <si>
+    <t>135163700</t>
+  </si>
+  <si>
+    <t>135154363</t>
+  </si>
+  <si>
+    <t>135164544</t>
+  </si>
+  <si>
+    <t>135159061</t>
+  </si>
+  <si>
+    <t>135154636</t>
+  </si>
+  <si>
+    <t>135146609</t>
+  </si>
+  <si>
+    <t>135174779</t>
+  </si>
+  <si>
+    <t>135129415</t>
+  </si>
+  <si>
+    <t>135171249</t>
+  </si>
+  <si>
+    <t>135168476</t>
+  </si>
+  <si>
+    <t>135176940</t>
+  </si>
+  <si>
+    <t>135180725</t>
+  </si>
+  <si>
+    <t>135193358</t>
+  </si>
+  <si>
+    <t>135191401</t>
+  </si>
+  <si>
+    <t>135200685</t>
+  </si>
+  <si>
+    <t>135133426</t>
+  </si>
+  <si>
+    <t>135139336</t>
+  </si>
+  <si>
+    <t>135110534</t>
+  </si>
+  <si>
+    <t>135100251</t>
+  </si>
+  <si>
+    <t>135116743</t>
+  </si>
+  <si>
+    <t>135111233</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 03.11.2025 a 09.11.2025</t>
   </si>
 </sst>
 </file>
@@ -570,7 +558,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -602,7 +590,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135049705</v>
+        <v>135123173</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -611,7 +599,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -629,7 +617,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -647,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -665,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -683,7 +671,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -701,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -719,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -737,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -754,7 +742,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -771,7 +759,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -788,7 +776,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -805,7 +793,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -822,7 +810,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -839,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -856,7 +844,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -873,7 +861,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -890,7 +878,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -907,7 +895,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -924,7 +912,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -941,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -958,7 +946,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -975,7 +963,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -992,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1009,7 +997,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1026,7 +1014,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1043,7 +1031,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1060,7 +1048,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1077,7 +1065,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1094,7 +1082,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1111,7 +1099,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1128,7 +1116,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1145,7 +1133,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1162,77 +1150,9 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1250,31 +1170,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2195E7-6F90-472A-9B8E-EEF42E72E721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9B2084-F37C-41A9-A5BB-7B24BB492B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="26">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,106 +54,58 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 03/11/2025</t>
-  </si>
-  <si>
-    <t>135105244</t>
-  </si>
-  <si>
-    <t>135133421</t>
-  </si>
-  <si>
-    <t>135140502</t>
-  </si>
-  <si>
-    <t>135137538</t>
-  </si>
-  <si>
-    <t>135133617</t>
-  </si>
-  <si>
-    <t>135133236</t>
-  </si>
-  <si>
-    <t>135155674</t>
-  </si>
-  <si>
-    <t>135156059</t>
-  </si>
-  <si>
-    <t>135155268</t>
-  </si>
-  <si>
-    <t>135156088</t>
-  </si>
-  <si>
-    <t>135162327</t>
-  </si>
-  <si>
-    <t>135163700</t>
-  </si>
-  <si>
-    <t>135154363</t>
-  </si>
-  <si>
-    <t>135164544</t>
-  </si>
-  <si>
-    <t>135159061</t>
-  </si>
-  <si>
-    <t>135154636</t>
-  </si>
-  <si>
-    <t>135146609</t>
-  </si>
-  <si>
-    <t>135174779</t>
-  </si>
-  <si>
-    <t>135129415</t>
-  </si>
-  <si>
-    <t>135171249</t>
-  </si>
-  <si>
-    <t>135168476</t>
-  </si>
-  <si>
-    <t>135176940</t>
-  </si>
-  <si>
-    <t>135180725</t>
-  </si>
-  <si>
-    <t>135193358</t>
-  </si>
-  <si>
-    <t>135191401</t>
-  </si>
-  <si>
-    <t>135200685</t>
-  </si>
-  <si>
-    <t>135133426</t>
-  </si>
-  <si>
-    <t>135139336</t>
-  </si>
-  <si>
-    <t>135110534</t>
-  </si>
-  <si>
-    <t>135100251</t>
-  </si>
-  <si>
-    <t>135116743</t>
-  </si>
-  <si>
-    <t>135111233</t>
-  </si>
-  <si>
     <t>Relatório de Recusas 03.11.2025 a 09.11.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 04/11/2025</t>
+  </si>
+  <si>
+    <t>135051461</t>
+  </si>
+  <si>
+    <t>135051444</t>
+  </si>
+  <si>
+    <t>135043044</t>
+  </si>
+  <si>
+    <t>135044605</t>
+  </si>
+  <si>
+    <t>135048417</t>
+  </si>
+  <si>
+    <t>135049114</t>
+  </si>
+  <si>
+    <t>135049373</t>
+  </si>
+  <si>
+    <t>135051429</t>
+  </si>
+  <si>
+    <t>135051570</t>
+  </si>
+  <si>
+    <t>135056953</t>
+  </si>
+  <si>
+    <t>135057252</t>
+  </si>
+  <si>
+    <t>135057776</t>
+  </si>
+  <si>
+    <t>135059630</t>
+  </si>
+  <si>
+    <t>135059784</t>
+  </si>
+  <si>
+    <t>135061235</t>
+  </si>
+  <si>
+    <t>135055840</t>
   </si>
 </sst>
 </file>
@@ -558,7 +510,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -590,16 +542,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135123173</v>
+        <v>135057851</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -608,16 +560,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -626,16 +578,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -644,16 +596,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -662,16 +614,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -680,16 +632,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -698,16 +650,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -716,16 +668,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -733,16 +685,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -750,16 +702,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -767,16 +719,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -784,16 +736,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -801,16 +753,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -818,16 +770,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -835,16 +787,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -852,16 +804,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -869,290 +821,18 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1170,31 +850,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9B2084-F37C-41A9-A5BB-7B24BB492B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7E0B31-0711-4F72-900B-DA7E852E2BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="48">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,55 +57,121 @@
     <t>Relatório de Recusas 03.11.2025 a 09.11.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 04/11/2025</t>
-  </si>
-  <si>
-    <t>135051461</t>
-  </si>
-  <si>
-    <t>135051444</t>
-  </si>
-  <si>
-    <t>135043044</t>
-  </si>
-  <si>
-    <t>135044605</t>
-  </si>
-  <si>
-    <t>135048417</t>
-  </si>
-  <si>
-    <t>135049114</t>
-  </si>
-  <si>
-    <t>135049373</t>
-  </si>
-  <si>
-    <t>135051429</t>
-  </si>
-  <si>
-    <t>135051570</t>
-  </si>
-  <si>
-    <t>135056953</t>
-  </si>
-  <si>
-    <t>135057252</t>
-  </si>
-  <si>
-    <t>135057776</t>
-  </si>
-  <si>
-    <t>135059630</t>
-  </si>
-  <si>
-    <t>135059784</t>
-  </si>
-  <si>
-    <t>135061235</t>
-  </si>
-  <si>
-    <t>135055840</t>
+    <t>Relatório de Recusas Santander - 05/11/2025</t>
+  </si>
+  <si>
+    <t>135099564</t>
+  </si>
+  <si>
+    <t>135128663</t>
+  </si>
+  <si>
+    <t>135128447</t>
+  </si>
+  <si>
+    <t>135136881</t>
+  </si>
+  <si>
+    <t>135139953</t>
+  </si>
+  <si>
+    <t>135141304</t>
+  </si>
+  <si>
+    <t>135135779</t>
+  </si>
+  <si>
+    <t>135143557</t>
+  </si>
+  <si>
+    <t>135163415</t>
+  </si>
+  <si>
+    <t>135144707</t>
+  </si>
+  <si>
+    <t>135167327</t>
+  </si>
+  <si>
+    <t>135142892</t>
+  </si>
+  <si>
+    <t>135169853</t>
+  </si>
+  <si>
+    <t>135175287</t>
+  </si>
+  <si>
+    <t>135196667</t>
+  </si>
+  <si>
+    <t>135198665</t>
+  </si>
+  <si>
+    <t>135189146</t>
+  </si>
+  <si>
+    <t>135196535</t>
+  </si>
+  <si>
+    <t>135162952</t>
+  </si>
+  <si>
+    <t>135217292</t>
+  </si>
+  <si>
+    <t>135221235</t>
+  </si>
+  <si>
+    <t>135213060</t>
+  </si>
+  <si>
+    <t>135211114</t>
+  </si>
+  <si>
+    <t>135099857</t>
+  </si>
+  <si>
+    <t>135083116</t>
+  </si>
+  <si>
+    <t>135148512</t>
+  </si>
+  <si>
+    <t>135069472</t>
+  </si>
+  <si>
+    <t>135177588</t>
+  </si>
+  <si>
+    <t>135198288</t>
+  </si>
+  <si>
+    <t>135127470</t>
+  </si>
+  <si>
+    <t>135127916</t>
+  </si>
+  <si>
+    <t>135128652</t>
+  </si>
+  <si>
+    <t>135130128</t>
+  </si>
+  <si>
+    <t>135134019</t>
+  </si>
+  <si>
+    <t>135134249</t>
+  </si>
+  <si>
+    <t>135138811</t>
+  </si>
+  <si>
+    <t>135142007</t>
+  </si>
+  <si>
+    <t>135144041</t>
   </si>
 </sst>
 </file>
@@ -510,7 +576,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -542,7 +608,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135057851</v>
+        <v>135076900</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -833,6 +899,380 @@
         <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -850,31 +1290,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7E0B31-0711-4F72-900B-DA7E852E2BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404F16F3-FB84-4786-BA66-4BA9B789DACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="63">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,124 +54,169 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas 03.11.2025 a 09.11.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 05/11/2025</t>
-  </si>
-  <si>
-    <t>135099564</t>
-  </si>
-  <si>
-    <t>135128663</t>
-  </si>
-  <si>
-    <t>135128447</t>
-  </si>
-  <si>
-    <t>135136881</t>
-  </si>
-  <si>
-    <t>135139953</t>
-  </si>
-  <si>
-    <t>135141304</t>
-  </si>
-  <si>
-    <t>135135779</t>
-  </si>
-  <si>
-    <t>135143557</t>
-  </si>
-  <si>
-    <t>135163415</t>
-  </si>
-  <si>
-    <t>135144707</t>
-  </si>
-  <si>
-    <t>135167327</t>
-  </si>
-  <si>
-    <t>135142892</t>
-  </si>
-  <si>
-    <t>135169853</t>
-  </si>
-  <si>
-    <t>135175287</t>
-  </si>
-  <si>
-    <t>135196667</t>
-  </si>
-  <si>
-    <t>135198665</t>
-  </si>
-  <si>
-    <t>135189146</t>
-  </si>
-  <si>
-    <t>135196535</t>
-  </si>
-  <si>
-    <t>135162952</t>
-  </si>
-  <si>
-    <t>135217292</t>
-  </si>
-  <si>
-    <t>135221235</t>
-  </si>
-  <si>
-    <t>135213060</t>
-  </si>
-  <si>
-    <t>135211114</t>
-  </si>
-  <si>
-    <t>135099857</t>
-  </si>
-  <si>
-    <t>135083116</t>
-  </si>
-  <si>
-    <t>135148512</t>
-  </si>
-  <si>
-    <t>135069472</t>
-  </si>
-  <si>
-    <t>135177588</t>
-  </si>
-  <si>
-    <t>135198288</t>
-  </si>
-  <si>
-    <t>135127470</t>
-  </si>
-  <si>
-    <t>135127916</t>
-  </si>
-  <si>
-    <t>135128652</t>
-  </si>
-  <si>
-    <t>135130128</t>
-  </si>
-  <si>
-    <t>135134019</t>
-  </si>
-  <si>
-    <t>135134249</t>
-  </si>
-  <si>
-    <t>135138811</t>
-  </si>
-  <si>
-    <t>135142007</t>
-  </si>
-  <si>
-    <t>135144041</t>
+    <t>Relatório de Recusas Santander - 06/11/2025</t>
+  </si>
+  <si>
+    <t>135098394</t>
+  </si>
+  <si>
+    <t>135088866</t>
+  </si>
+  <si>
+    <t>135102415</t>
+  </si>
+  <si>
+    <t>135101112</t>
+  </si>
+  <si>
+    <t>135090154</t>
+  </si>
+  <si>
+    <t>135150017</t>
+  </si>
+  <si>
+    <t>135161482</t>
+  </si>
+  <si>
+    <t>135162103</t>
+  </si>
+  <si>
+    <t>135163012</t>
+  </si>
+  <si>
+    <t>135163354</t>
+  </si>
+  <si>
+    <t>135164098</t>
+  </si>
+  <si>
+    <t>135147239</t>
+  </si>
+  <si>
+    <t>135148235</t>
+  </si>
+  <si>
+    <t>135152378</t>
+  </si>
+  <si>
+    <t>135164538</t>
+  </si>
+  <si>
+    <t>135164558</t>
+  </si>
+  <si>
+    <t>135164609</t>
+  </si>
+  <si>
+    <t>135164739</t>
+  </si>
+  <si>
+    <t>135164110</t>
+  </si>
+  <si>
+    <t>135159402</t>
+  </si>
+  <si>
+    <t>135164485</t>
+  </si>
+  <si>
+    <t>135152474</t>
+  </si>
+  <si>
+    <t>135195509</t>
+  </si>
+  <si>
+    <t>135200528</t>
+  </si>
+  <si>
+    <t>135159146</t>
+  </si>
+  <si>
+    <t>135218311</t>
+  </si>
+  <si>
+    <t>135215076</t>
+  </si>
+  <si>
+    <t>135211128</t>
+  </si>
+  <si>
+    <t>135230182</t>
+  </si>
+  <si>
+    <t>135084424</t>
+  </si>
+  <si>
+    <t>135091782</t>
+  </si>
+  <si>
+    <t>135094583</t>
+  </si>
+  <si>
+    <t>135095572</t>
+  </si>
+  <si>
+    <t>135097409</t>
+  </si>
+  <si>
+    <t>135096412</t>
+  </si>
+  <si>
+    <t>135096941</t>
+  </si>
+  <si>
+    <t>135097981</t>
+  </si>
+  <si>
+    <t>135099100</t>
+  </si>
+  <si>
+    <t>135099336</t>
+  </si>
+  <si>
+    <t>135089764</t>
+  </si>
+  <si>
+    <t>135096062</t>
+  </si>
+  <si>
+    <t>135091578</t>
+  </si>
+  <si>
+    <t>135101522</t>
+  </si>
+  <si>
+    <t>135088154</t>
+  </si>
+  <si>
+    <t>135221699</t>
+  </si>
+  <si>
+    <t>135148358</t>
+  </si>
+  <si>
+    <t>135153663</t>
+  </si>
+  <si>
+    <t>135154592</t>
+  </si>
+  <si>
+    <t>135156213</t>
+  </si>
+  <si>
+    <t>135157735</t>
+  </si>
+  <si>
+    <t>135159289</t>
+  </si>
+  <si>
+    <t>135164300</t>
+  </si>
+  <si>
+    <t>135164486</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 06.11.2025</t>
   </si>
 </sst>
 </file>
@@ -576,7 +621,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -608,16 +653,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135076900</v>
+        <v>135083025</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -626,16 +671,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -644,16 +689,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -662,16 +707,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -680,16 +725,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -698,16 +743,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -716,16 +761,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -734,16 +779,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -751,16 +796,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -768,16 +813,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -785,16 +830,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -802,16 +847,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -819,16 +864,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -836,16 +881,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -853,16 +898,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -870,16 +915,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -887,16 +932,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -904,16 +949,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -921,16 +966,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -938,16 +983,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -955,16 +1000,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -972,16 +1017,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -989,16 +1034,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1006,16 +1051,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1023,16 +1068,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1040,16 +1085,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1057,16 +1102,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1074,16 +1119,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1091,16 +1136,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1108,16 +1153,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1125,16 +1170,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1142,16 +1187,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1159,16 +1204,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1176,16 +1221,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1193,16 +1238,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1210,16 +1255,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1227,16 +1272,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1244,16 +1289,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1261,18 +1306,273 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1290,31 +1590,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404F16F3-FB84-4786-BA66-4BA9B789DACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BC813F-CC74-43C5-9C5B-6857BF24B59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="54">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,169 +54,142 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 06/11/2025</t>
-  </si>
-  <si>
-    <t>135098394</t>
-  </si>
-  <si>
-    <t>135088866</t>
-  </si>
-  <si>
-    <t>135102415</t>
-  </si>
-  <si>
-    <t>135101112</t>
-  </si>
-  <si>
-    <t>135090154</t>
-  </si>
-  <si>
-    <t>135150017</t>
-  </si>
-  <si>
-    <t>135161482</t>
-  </si>
-  <si>
-    <t>135162103</t>
-  </si>
-  <si>
-    <t>135163012</t>
-  </si>
-  <si>
-    <t>135163354</t>
-  </si>
-  <si>
-    <t>135164098</t>
-  </si>
-  <si>
-    <t>135147239</t>
-  </si>
-  <si>
-    <t>135148235</t>
-  </si>
-  <si>
-    <t>135152378</t>
-  </si>
-  <si>
-    <t>135164538</t>
-  </si>
-  <si>
-    <t>135164558</t>
-  </si>
-  <si>
-    <t>135164609</t>
-  </si>
-  <si>
-    <t>135164739</t>
-  </si>
-  <si>
-    <t>135164110</t>
-  </si>
-  <si>
-    <t>135159402</t>
-  </si>
-  <si>
-    <t>135164485</t>
-  </si>
-  <si>
-    <t>135152474</t>
-  </si>
-  <si>
-    <t>135195509</t>
-  </si>
-  <si>
-    <t>135200528</t>
-  </si>
-  <si>
-    <t>135159146</t>
-  </si>
-  <si>
-    <t>135218311</t>
-  </si>
-  <si>
-    <t>135215076</t>
-  </si>
-  <si>
-    <t>135211128</t>
-  </si>
-  <si>
-    <t>135230182</t>
-  </si>
-  <si>
-    <t>135084424</t>
-  </si>
-  <si>
-    <t>135091782</t>
-  </si>
-  <si>
-    <t>135094583</t>
-  </si>
-  <si>
-    <t>135095572</t>
-  </si>
-  <si>
-    <t>135097409</t>
-  </si>
-  <si>
-    <t>135096412</t>
-  </si>
-  <si>
-    <t>135096941</t>
-  </si>
-  <si>
-    <t>135097981</t>
-  </si>
-  <si>
-    <t>135099100</t>
-  </si>
-  <si>
-    <t>135099336</t>
-  </si>
-  <si>
-    <t>135089764</t>
-  </si>
-  <si>
-    <t>135096062</t>
-  </si>
-  <si>
-    <t>135091578</t>
-  </si>
-  <si>
-    <t>135101522</t>
-  </si>
-  <si>
-    <t>135088154</t>
-  </si>
-  <si>
-    <t>135221699</t>
-  </si>
-  <si>
-    <t>135148358</t>
-  </si>
-  <si>
-    <t>135153663</t>
-  </si>
-  <si>
-    <t>135154592</t>
-  </si>
-  <si>
-    <t>135156213</t>
-  </si>
-  <si>
-    <t>135157735</t>
-  </si>
-  <si>
-    <t>135159289</t>
-  </si>
-  <si>
-    <t>135164300</t>
-  </si>
-  <si>
-    <t>135164486</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 06.11.2025</t>
+    <t>Relatório de Recusas Santander - 07 e 08 /11/2025</t>
+  </si>
+  <si>
+    <t>135123518</t>
+  </si>
+  <si>
+    <t>135114020</t>
+  </si>
+  <si>
+    <t>135170165</t>
+  </si>
+  <si>
+    <t>135171770</t>
+  </si>
+  <si>
+    <t>135181015</t>
+  </si>
+  <si>
+    <t>135172614</t>
+  </si>
+  <si>
+    <t>135186149</t>
+  </si>
+  <si>
+    <t>135191534</t>
+  </si>
+  <si>
+    <t>135185493</t>
+  </si>
+  <si>
+    <t>135211786</t>
+  </si>
+  <si>
+    <t>135191074</t>
+  </si>
+  <si>
+    <t>135245695</t>
+  </si>
+  <si>
+    <t>135169298</t>
+  </si>
+  <si>
+    <t>135262875</t>
+  </si>
+  <si>
+    <t>135260735</t>
+  </si>
+  <si>
+    <t>135186289</t>
+  </si>
+  <si>
+    <t>135276707</t>
+  </si>
+  <si>
+    <t>135286641</t>
+  </si>
+  <si>
+    <t>135109372</t>
+  </si>
+  <si>
+    <t>135119133</t>
+  </si>
+  <si>
+    <t>135121726</t>
+  </si>
+  <si>
+    <t>135198264</t>
+  </si>
+  <si>
+    <t>135183640</t>
+  </si>
+  <si>
+    <t>135168728</t>
+  </si>
+  <si>
+    <t>135172468</t>
+  </si>
+  <si>
+    <t>135172922</t>
+  </si>
+  <si>
+    <t>135173613</t>
+  </si>
+  <si>
+    <t>135174178</t>
+  </si>
+  <si>
+    <t>135176096</t>
+  </si>
+  <si>
+    <t>135179982</t>
+  </si>
+  <si>
+    <t>135180377</t>
+  </si>
+  <si>
+    <t>135180081</t>
+  </si>
+  <si>
+    <t>135180853</t>
+  </si>
+  <si>
+    <t>135181489</t>
+  </si>
+  <si>
+    <t>135181844</t>
+  </si>
+  <si>
+    <t>135218972</t>
+  </si>
+  <si>
+    <t>135180464</t>
+  </si>
+  <si>
+    <t>135143631</t>
+  </si>
+  <si>
+    <t>135213647</t>
+  </si>
+  <si>
+    <t>135134061</t>
+  </si>
+  <si>
+    <t>135124368</t>
+  </si>
+  <si>
+    <t>135132584</t>
+  </si>
+  <si>
+    <t>135138425</t>
+  </si>
+  <si>
+    <t>135212565</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 03.11.2025 a 09.11.2025</t>
   </si>
 </sst>
 </file>
@@ -621,7 +594,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -653,7 +626,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135083025</v>
+        <v>135102201</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -662,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -680,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -698,7 +671,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -716,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -734,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -752,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -770,7 +743,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -788,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -805,7 +778,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -822,7 +795,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -839,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -856,7 +829,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -873,7 +846,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -890,7 +863,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -907,7 +880,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -924,7 +897,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -941,7 +914,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -958,7 +931,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -975,7 +948,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -992,7 +965,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1009,7 +982,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1026,7 +999,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1043,7 +1016,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1060,7 +1033,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1077,7 +1050,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1094,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1111,7 +1084,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1128,7 +1101,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1145,7 +1118,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1162,7 +1135,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1179,7 +1152,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1196,7 +1169,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1213,7 +1186,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1230,7 +1203,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1247,7 +1220,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1264,7 +1237,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1281,7 +1254,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1298,7 +1271,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1315,7 +1288,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1332,7 +1305,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1349,7 +1322,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1366,7 +1339,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1383,7 +1356,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1400,7 +1373,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1417,162 +1390,9 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BC813F-CC74-43C5-9C5B-6857BF24B59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC160D6-932E-4D03-A637-624ECF952E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="62">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,142 +54,166 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 07 e 08 /11/2025</t>
-  </si>
-  <si>
-    <t>135123518</t>
-  </si>
-  <si>
-    <t>135114020</t>
-  </si>
-  <si>
-    <t>135170165</t>
-  </si>
-  <si>
-    <t>135171770</t>
-  </si>
-  <si>
-    <t>135181015</t>
-  </si>
-  <si>
-    <t>135172614</t>
-  </si>
-  <si>
-    <t>135186149</t>
-  </si>
-  <si>
-    <t>135191534</t>
-  </si>
-  <si>
-    <t>135185493</t>
-  </si>
-  <si>
-    <t>135211786</t>
-  </si>
-  <si>
-    <t>135191074</t>
-  </si>
-  <si>
-    <t>135245695</t>
-  </si>
-  <si>
-    <t>135169298</t>
-  </si>
-  <si>
-    <t>135262875</t>
-  </si>
-  <si>
-    <t>135260735</t>
-  </si>
-  <si>
-    <t>135186289</t>
-  </si>
-  <si>
-    <t>135276707</t>
-  </si>
-  <si>
-    <t>135286641</t>
-  </si>
-  <si>
-    <t>135109372</t>
-  </si>
-  <si>
-    <t>135119133</t>
-  </si>
-  <si>
-    <t>135121726</t>
-  </si>
-  <si>
-    <t>135198264</t>
-  </si>
-  <si>
-    <t>135183640</t>
-  </si>
-  <si>
-    <t>135168728</t>
-  </si>
-  <si>
-    <t>135172468</t>
-  </si>
-  <si>
-    <t>135172922</t>
-  </si>
-  <si>
-    <t>135173613</t>
-  </si>
-  <si>
-    <t>135174178</t>
-  </si>
-  <si>
-    <t>135176096</t>
-  </si>
-  <si>
-    <t>135179982</t>
-  </si>
-  <si>
-    <t>135180377</t>
-  </si>
-  <si>
-    <t>135180081</t>
-  </si>
-  <si>
-    <t>135180853</t>
-  </si>
-  <si>
-    <t>135181489</t>
-  </si>
-  <si>
-    <t>135181844</t>
-  </si>
-  <si>
-    <t>135218972</t>
-  </si>
-  <si>
-    <t>135180464</t>
-  </si>
-  <si>
-    <t>135143631</t>
-  </si>
-  <si>
-    <t>135213647</t>
-  </si>
-  <si>
-    <t>135134061</t>
-  </si>
-  <si>
-    <t>135124368</t>
-  </si>
-  <si>
-    <t>135132584</t>
-  </si>
-  <si>
-    <t>135138425</t>
-  </si>
-  <si>
-    <t>135212565</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 03.11.2025 a 09.11.2025</t>
+    <t>Relatório de Recusas Santander - 10 /11/2025</t>
+  </si>
+  <si>
+    <t>135197711</t>
+  </si>
+  <si>
+    <t>135200268</t>
+  </si>
+  <si>
+    <t>135202825</t>
+  </si>
+  <si>
+    <t>135201502</t>
+  </si>
+  <si>
+    <t>135192671</t>
+  </si>
+  <si>
+    <t>135187919</t>
+  </si>
+  <si>
+    <t>135211996</t>
+  </si>
+  <si>
+    <t>135209254</t>
+  </si>
+  <si>
+    <t>135211310</t>
+  </si>
+  <si>
+    <t>135232531</t>
+  </si>
+  <si>
+    <t>135230948</t>
+  </si>
+  <si>
+    <t>135248952</t>
+  </si>
+  <si>
+    <t>135232801</t>
+  </si>
+  <si>
+    <t>135253679</t>
+  </si>
+  <si>
+    <t>135262021</t>
+  </si>
+  <si>
+    <t>135252214</t>
+  </si>
+  <si>
+    <t>135255569</t>
+  </si>
+  <si>
+    <t>135255237</t>
+  </si>
+  <si>
+    <t>135277723</t>
+  </si>
+  <si>
+    <t>135263839</t>
+  </si>
+  <si>
+    <t>135185328</t>
+  </si>
+  <si>
+    <t>135185646</t>
+  </si>
+  <si>
+    <t>135186679</t>
+  </si>
+  <si>
+    <t>135186700</t>
+  </si>
+  <si>
+    <t>135187651</t>
+  </si>
+  <si>
+    <t>135188014</t>
+  </si>
+  <si>
+    <t>135190587</t>
+  </si>
+  <si>
+    <t>135191056</t>
+  </si>
+  <si>
+    <t>135191224</t>
+  </si>
+  <si>
+    <t>135191415</t>
+  </si>
+  <si>
+    <t>135192125</t>
+  </si>
+  <si>
+    <t>135192284</t>
+  </si>
+  <si>
+    <t>135193921</t>
+  </si>
+  <si>
+    <t>135194531</t>
+  </si>
+  <si>
+    <t>135194649</t>
+  </si>
+  <si>
+    <t>135195086</t>
+  </si>
+  <si>
+    <t>135197096</t>
+  </si>
+  <si>
+    <t>135197605</t>
+  </si>
+  <si>
+    <t>135197701</t>
+  </si>
+  <si>
+    <t>135198371</t>
+  </si>
+  <si>
+    <t>135198501</t>
+  </si>
+  <si>
+    <t>135198652</t>
+  </si>
+  <si>
+    <t>135198941</t>
+  </si>
+  <si>
+    <t>135199874</t>
+  </si>
+  <si>
+    <t>135199949</t>
+  </si>
+  <si>
+    <t>135200217</t>
+  </si>
+  <si>
+    <t>135201673</t>
+  </si>
+  <si>
+    <t>135202033</t>
+  </si>
+  <si>
+    <t>135202267</t>
+  </si>
+  <si>
+    <t>135202275</t>
+  </si>
+  <si>
+    <t>135202300</t>
+  </si>
+  <si>
+    <t>135209835</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 10.11.2025 a 16.11.2025</t>
   </si>
 </sst>
 </file>
@@ -594,7 +618,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -626,7 +650,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135102201</v>
+        <v>135185295</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -635,7 +659,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -653,7 +677,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -671,7 +695,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -689,7 +713,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -707,7 +731,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -725,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -743,7 +767,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -761,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -778,7 +802,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -795,7 +819,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -812,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -829,7 +853,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -846,7 +870,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -863,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -880,7 +904,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -897,7 +921,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -914,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -931,7 +955,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -948,7 +972,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -965,7 +989,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -982,7 +1006,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -999,7 +1023,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1016,7 +1040,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1033,7 +1057,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1050,7 +1074,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1067,7 +1091,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1084,7 +1108,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1101,7 +1125,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1118,7 +1142,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1135,7 +1159,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1152,7 +1176,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1169,7 +1193,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1186,7 +1210,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1203,7 +1227,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1220,7 +1244,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1237,7 +1261,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1254,7 +1278,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1271,7 +1295,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1288,7 +1312,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1305,7 +1329,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1322,7 +1346,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1339,7 +1363,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1356,7 +1380,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1373,7 +1397,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1390,9 +1414,145 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1410,31 +1570,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC160D6-932E-4D03-A637-624ECF952E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813B192A-C445-43B0-82EB-103592104C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,166 +54,106 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 10 /11/2025</t>
-  </si>
-  <si>
-    <t>135197711</t>
-  </si>
-  <si>
-    <t>135200268</t>
-  </si>
-  <si>
-    <t>135202825</t>
-  </si>
-  <si>
-    <t>135201502</t>
-  </si>
-  <si>
-    <t>135192671</t>
-  </si>
-  <si>
-    <t>135187919</t>
-  </si>
-  <si>
-    <t>135211996</t>
-  </si>
-  <si>
-    <t>135209254</t>
-  </si>
-  <si>
-    <t>135211310</t>
-  </si>
-  <si>
-    <t>135232531</t>
-  </si>
-  <si>
-    <t>135230948</t>
-  </si>
-  <si>
-    <t>135248952</t>
-  </si>
-  <si>
-    <t>135232801</t>
-  </si>
-  <si>
-    <t>135253679</t>
-  </si>
-  <si>
-    <t>135262021</t>
-  </si>
-  <si>
-    <t>135252214</t>
-  </si>
-  <si>
-    <t>135255569</t>
-  </si>
-  <si>
-    <t>135255237</t>
-  </si>
-  <si>
-    <t>135277723</t>
-  </si>
-  <si>
-    <t>135263839</t>
-  </si>
-  <si>
-    <t>135185328</t>
-  </si>
-  <si>
-    <t>135185646</t>
-  </si>
-  <si>
-    <t>135186679</t>
-  </si>
-  <si>
-    <t>135186700</t>
-  </si>
-  <si>
-    <t>135187651</t>
-  </si>
-  <si>
-    <t>135188014</t>
-  </si>
-  <si>
-    <t>135190587</t>
-  </si>
-  <si>
-    <t>135191056</t>
-  </si>
-  <si>
-    <t>135191224</t>
-  </si>
-  <si>
-    <t>135191415</t>
-  </si>
-  <si>
-    <t>135192125</t>
-  </si>
-  <si>
-    <t>135192284</t>
-  </si>
-  <si>
-    <t>135193921</t>
-  </si>
-  <si>
-    <t>135194531</t>
-  </si>
-  <si>
-    <t>135194649</t>
-  </si>
-  <si>
-    <t>135195086</t>
-  </si>
-  <si>
-    <t>135197096</t>
-  </si>
-  <si>
-    <t>135197605</t>
-  </si>
-  <si>
-    <t>135197701</t>
-  </si>
-  <si>
-    <t>135198371</t>
-  </si>
-  <si>
-    <t>135198501</t>
-  </si>
-  <si>
-    <t>135198652</t>
-  </si>
-  <si>
-    <t>135198941</t>
-  </si>
-  <si>
-    <t>135199874</t>
-  </si>
-  <si>
-    <t>135199949</t>
-  </si>
-  <si>
-    <t>135200217</t>
-  </si>
-  <si>
-    <t>135201673</t>
-  </si>
-  <si>
-    <t>135202033</t>
-  </si>
-  <si>
-    <t>135202267</t>
-  </si>
-  <si>
-    <t>135202275</t>
-  </si>
-  <si>
-    <t>135202300</t>
-  </si>
-  <si>
-    <t>135209835</t>
-  </si>
-  <si>
     <t>Relatório de Recusas 10.11.2025 a 16.11.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 11 /11/2025</t>
+  </si>
+  <si>
+    <t>135209860</t>
+  </si>
+  <si>
+    <t>135221704</t>
+  </si>
+  <si>
+    <t>135232441</t>
+  </si>
+  <si>
+    <t>135254726</t>
+  </si>
+  <si>
+    <t>135256118</t>
+  </si>
+  <si>
+    <t>135278219</t>
+  </si>
+  <si>
+    <t>135281962</t>
+  </si>
+  <si>
+    <t>135284036</t>
+  </si>
+  <si>
+    <t>135273857</t>
+  </si>
+  <si>
+    <t>135254177</t>
+  </si>
+  <si>
+    <t>135286512</t>
+  </si>
+  <si>
+    <t>135296324</t>
+  </si>
+  <si>
+    <t>135244230</t>
+  </si>
+  <si>
+    <t>135256480</t>
+  </si>
+  <si>
+    <t>135296616</t>
+  </si>
+  <si>
+    <t>135220819</t>
+  </si>
+  <si>
+    <t>135219217</t>
+  </si>
+  <si>
+    <t>135251331</t>
+  </si>
+  <si>
+    <t>135161758</t>
+  </si>
+  <si>
+    <t>135131402</t>
+  </si>
+  <si>
+    <t>135156125</t>
+  </si>
+  <si>
+    <t>135253065</t>
+  </si>
+  <si>
+    <t>135162088</t>
+  </si>
+  <si>
+    <t>135275238</t>
+  </si>
+  <si>
+    <t>135201182</t>
+  </si>
+  <si>
+    <t>135205349</t>
+  </si>
+  <si>
+    <t>135228384</t>
+  </si>
+  <si>
+    <t>135239277</t>
+  </si>
+  <si>
+    <t>135240372</t>
+  </si>
+  <si>
+    <t>135265829</t>
+  </si>
+  <si>
+    <t>135266822</t>
+  </si>
+  <si>
+    <t>135281901</t>
   </si>
 </sst>
 </file>
@@ -618,7 +558,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -650,16 +590,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135185295</v>
+        <v>135139629</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -668,16 +608,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -686,16 +626,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -704,16 +644,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -722,16 +662,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -740,16 +680,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -758,16 +698,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -776,16 +716,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -793,16 +733,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -810,16 +750,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -827,16 +767,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -844,16 +784,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -861,16 +801,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -878,16 +818,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -895,16 +835,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -912,16 +852,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -929,16 +869,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -946,16 +886,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -963,16 +903,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -980,16 +920,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -997,16 +937,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1014,16 +954,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1031,16 +971,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1048,16 +988,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1065,16 +1005,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1082,16 +1022,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1099,16 +1039,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1116,16 +1056,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1133,16 +1073,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1150,16 +1090,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1167,16 +1107,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1184,16 +1124,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1201,358 +1141,18 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E54" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1570,31 +1170,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813B192A-C445-43B0-82EB-103592104C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E5A425-A229-4E3F-A96E-B369D1B72808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="31">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,106 +54,73 @@
     <t>1070</t>
   </si>
   <si>
+    <t>Relatório de Recusas Santander - 12 /11/2025</t>
+  </si>
+  <si>
+    <t>135287008</t>
+  </si>
+  <si>
+    <t>135269259</t>
+  </si>
+  <si>
+    <t>135309156</t>
+  </si>
+  <si>
+    <t>135298416</t>
+  </si>
+  <si>
+    <t>135290497</t>
+  </si>
+  <si>
+    <t>135296743</t>
+  </si>
+  <si>
+    <t>135309865</t>
+  </si>
+  <si>
+    <t>135292781</t>
+  </si>
+  <si>
+    <t>135291803</t>
+  </si>
+  <si>
+    <t>135318579</t>
+  </si>
+  <si>
+    <t>135347242</t>
+  </si>
+  <si>
+    <t>135171871</t>
+  </si>
+  <si>
+    <t>135178864</t>
+  </si>
+  <si>
+    <t>135191337</t>
+  </si>
+  <si>
+    <t>135284850</t>
+  </si>
+  <si>
+    <t>135340447</t>
+  </si>
+  <si>
+    <t>135214192</t>
+  </si>
+  <si>
+    <t>135222346</t>
+  </si>
+  <si>
+    <t>135200738</t>
+  </si>
+  <si>
+    <t>135279407</t>
+  </si>
+  <si>
+    <t>135265102</t>
+  </si>
+  <si>
     <t>Relatório de Recusas 10.11.2025 a 16.11.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 11 /11/2025</t>
-  </si>
-  <si>
-    <t>135209860</t>
-  </si>
-  <si>
-    <t>135221704</t>
-  </si>
-  <si>
-    <t>135232441</t>
-  </si>
-  <si>
-    <t>135254726</t>
-  </si>
-  <si>
-    <t>135256118</t>
-  </si>
-  <si>
-    <t>135278219</t>
-  </si>
-  <si>
-    <t>135281962</t>
-  </si>
-  <si>
-    <t>135284036</t>
-  </si>
-  <si>
-    <t>135273857</t>
-  </si>
-  <si>
-    <t>135254177</t>
-  </si>
-  <si>
-    <t>135286512</t>
-  </si>
-  <si>
-    <t>135296324</t>
-  </si>
-  <si>
-    <t>135244230</t>
-  </si>
-  <si>
-    <t>135256480</t>
-  </si>
-  <si>
-    <t>135296616</t>
-  </si>
-  <si>
-    <t>135220819</t>
-  </si>
-  <si>
-    <t>135219217</t>
-  </si>
-  <si>
-    <t>135251331</t>
-  </si>
-  <si>
-    <t>135161758</t>
-  </si>
-  <si>
-    <t>135131402</t>
-  </si>
-  <si>
-    <t>135156125</t>
-  </si>
-  <si>
-    <t>135253065</t>
-  </si>
-  <si>
-    <t>135162088</t>
-  </si>
-  <si>
-    <t>135275238</t>
-  </si>
-  <si>
-    <t>135201182</t>
-  </si>
-  <si>
-    <t>135205349</t>
-  </si>
-  <si>
-    <t>135228384</t>
-  </si>
-  <si>
-    <t>135239277</t>
-  </si>
-  <si>
-    <t>135240372</t>
-  </si>
-  <si>
-    <t>135265829</t>
-  </si>
-  <si>
-    <t>135266822</t>
-  </si>
-  <si>
-    <t>135281901</t>
   </si>
 </sst>
 </file>
@@ -558,7 +525,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -590,16 +557,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135139629</v>
+        <v>135177676</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -608,16 +575,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -626,16 +593,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -644,16 +611,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -662,16 +629,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -680,16 +647,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -698,16 +665,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -716,16 +683,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -733,16 +700,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -750,16 +717,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -767,16 +734,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -784,16 +751,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -801,16 +768,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -818,16 +785,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -835,16 +802,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -852,16 +819,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -869,16 +836,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -886,16 +853,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -903,16 +870,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -920,16 +887,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -937,16 +904,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -954,205 +921,18 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E5A425-A229-4E3F-A96E-B369D1B72808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63A7BDB-B2A2-480F-8893-B1BDDFF7EE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="25">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,73 +54,55 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 12 /11/2025</t>
-  </si>
-  <si>
-    <t>135287008</t>
-  </si>
-  <si>
-    <t>135269259</t>
-  </si>
-  <si>
-    <t>135309156</t>
-  </si>
-  <si>
-    <t>135298416</t>
-  </si>
-  <si>
-    <t>135290497</t>
-  </si>
-  <si>
-    <t>135296743</t>
-  </si>
-  <si>
-    <t>135309865</t>
-  </si>
-  <si>
-    <t>135292781</t>
-  </si>
-  <si>
-    <t>135291803</t>
-  </si>
-  <si>
-    <t>135318579</t>
-  </si>
-  <si>
-    <t>135347242</t>
-  </si>
-  <si>
-    <t>135171871</t>
-  </si>
-  <si>
-    <t>135178864</t>
-  </si>
-  <si>
-    <t>135191337</t>
-  </si>
-  <si>
-    <t>135284850</t>
-  </si>
-  <si>
-    <t>135340447</t>
-  </si>
-  <si>
-    <t>135214192</t>
-  </si>
-  <si>
-    <t>135222346</t>
-  </si>
-  <si>
-    <t>135200738</t>
-  </si>
-  <si>
-    <t>135279407</t>
-  </si>
-  <si>
-    <t>135265102</t>
-  </si>
-  <si>
     <t>Relatório de Recusas 10.11.2025 a 16.11.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 13/11/2025</t>
+  </si>
+  <si>
+    <t>135195250</t>
+  </si>
+  <si>
+    <t>135216762</t>
+  </si>
+  <si>
+    <t>135252707</t>
+  </si>
+  <si>
+    <t>135294771</t>
+  </si>
+  <si>
+    <t>135293513</t>
+  </si>
+  <si>
+    <t>135316201</t>
+  </si>
+  <si>
+    <t>135342549</t>
+  </si>
+  <si>
+    <t>135337305</t>
+  </si>
+  <si>
+    <t>135342217</t>
+  </si>
+  <si>
+    <t>135202087</t>
+  </si>
+  <si>
+    <t>135296927</t>
+  </si>
+  <si>
+    <t>135191265</t>
+  </si>
+  <si>
+    <t>135296887</t>
+  </si>
+  <si>
+    <t>135254648</t>
+  </si>
+  <si>
+    <t>135241970</t>
   </si>
 </sst>
 </file>
@@ -525,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -557,16 +539,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135177676</v>
+        <v>135202255</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -575,16 +557,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -593,16 +575,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -611,16 +593,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -629,16 +611,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -647,16 +629,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -665,16 +647,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -683,16 +665,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -700,16 +682,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -717,16 +699,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -734,16 +716,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -751,16 +733,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -768,16 +750,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -785,16 +767,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -802,16 +784,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -819,120 +801,18 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -950,31 +830,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63A7BDB-B2A2-480F-8893-B1BDDFF7EE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9188FD31-4564-44E8-B375-A23B3BCC6CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24120" yWindow="1770" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="57">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,52 +57,148 @@
     <t>Relatório de Recusas 10.11.2025 a 16.11.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 13/11/2025</t>
-  </si>
-  <si>
-    <t>135195250</t>
-  </si>
-  <si>
-    <t>135216762</t>
-  </si>
-  <si>
-    <t>135252707</t>
-  </si>
-  <si>
-    <t>135294771</t>
-  </si>
-  <si>
-    <t>135293513</t>
-  </si>
-  <si>
-    <t>135316201</t>
-  </si>
-  <si>
-    <t>135342549</t>
-  </si>
-  <si>
-    <t>135337305</t>
-  </si>
-  <si>
-    <t>135342217</t>
-  </si>
-  <si>
-    <t>135202087</t>
-  </si>
-  <si>
-    <t>135296927</t>
-  </si>
-  <si>
-    <t>135191265</t>
-  </si>
-  <si>
-    <t>135296887</t>
-  </si>
-  <si>
-    <t>135254648</t>
-  </si>
-  <si>
-    <t>135241970</t>
+    <t>Relatório de Recusas Santander - 14 e 15/11/2025</t>
+  </si>
+  <si>
+    <t>135214973</t>
+  </si>
+  <si>
+    <t>135231974</t>
+  </si>
+  <si>
+    <t>135237661</t>
+  </si>
+  <si>
+    <t>135285115</t>
+  </si>
+  <si>
+    <t>135309267</t>
+  </si>
+  <si>
+    <t>135256693</t>
+  </si>
+  <si>
+    <t>135341208</t>
+  </si>
+  <si>
+    <t>135349648</t>
+  </si>
+  <si>
+    <t>135349913</t>
+  </si>
+  <si>
+    <t>135353474</t>
+  </si>
+  <si>
+    <t>135197785</t>
+  </si>
+  <si>
+    <t>135215229</t>
+  </si>
+  <si>
+    <t>135216652</t>
+  </si>
+  <si>
+    <t>135250749</t>
+  </si>
+  <si>
+    <t>135273340</t>
+  </si>
+  <si>
+    <t>135210735</t>
+  </si>
+  <si>
+    <t>135206428</t>
+  </si>
+  <si>
+    <t>135322892</t>
+  </si>
+  <si>
+    <t>135318527</t>
+  </si>
+  <si>
+    <t>135223146</t>
+  </si>
+  <si>
+    <t>135212079</t>
+  </si>
+  <si>
+    <t>135214309</t>
+  </si>
+  <si>
+    <t>135219311</t>
+  </si>
+  <si>
+    <t>135221053</t>
+  </si>
+  <si>
+    <t>135229207</t>
+  </si>
+  <si>
+    <t>135222154</t>
+  </si>
+  <si>
+    <t>135222203</t>
+  </si>
+  <si>
+    <t>135221690</t>
+  </si>
+  <si>
+    <t>135236513</t>
+  </si>
+  <si>
+    <t>135207629</t>
+  </si>
+  <si>
+    <t>135208277</t>
+  </si>
+  <si>
+    <t>135208380</t>
+  </si>
+  <si>
+    <t>135208539</t>
+  </si>
+  <si>
+    <t>135210020</t>
+  </si>
+  <si>
+    <t>135211010</t>
+  </si>
+  <si>
+    <t>135211849</t>
+  </si>
+  <si>
+    <t>135212084</t>
+  </si>
+  <si>
+    <t>135213849</t>
+  </si>
+  <si>
+    <t>135218690</t>
+  </si>
+  <si>
+    <t>135219384</t>
+  </si>
+  <si>
+    <t>135222769</t>
+  </si>
+  <si>
+    <t>135230689</t>
+  </si>
+  <si>
+    <t>135234887</t>
+  </si>
+  <si>
+    <t>135236142</t>
+  </si>
+  <si>
+    <t>135240947</t>
+  </si>
+  <si>
+    <t>135220277</t>
+  </si>
+  <si>
+    <t>135234370</t>
   </si>
 </sst>
 </file>
@@ -507,7 +603,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -539,7 +635,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135202255</v>
+        <v>135203182</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -813,6 +909,550 @@
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -830,31 +1470,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9188FD31-4564-44E8-B375-A23B3BCC6CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB248582-2E02-483D-8F12-C0B5767759AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24120" yWindow="1770" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="122">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,151 +54,346 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas 10.11.2025 a 16.11.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 14 e 15/11/2025</t>
-  </si>
-  <si>
-    <t>135214973</t>
-  </si>
-  <si>
-    <t>135231974</t>
-  </si>
-  <si>
-    <t>135237661</t>
-  </si>
-  <si>
-    <t>135285115</t>
-  </si>
-  <si>
-    <t>135309267</t>
-  </si>
-  <si>
-    <t>135256693</t>
-  </si>
-  <si>
-    <t>135341208</t>
-  </si>
-  <si>
-    <t>135349648</t>
-  </si>
-  <si>
-    <t>135349913</t>
-  </si>
-  <si>
-    <t>135353474</t>
-  </si>
-  <si>
-    <t>135197785</t>
-  </si>
-  <si>
-    <t>135215229</t>
-  </si>
-  <si>
-    <t>135216652</t>
-  </si>
-  <si>
-    <t>135250749</t>
-  </si>
-  <si>
-    <t>135273340</t>
-  </si>
-  <si>
-    <t>135210735</t>
-  </si>
-  <si>
-    <t>135206428</t>
-  </si>
-  <si>
-    <t>135322892</t>
-  </si>
-  <si>
-    <t>135318527</t>
-  </si>
-  <si>
-    <t>135223146</t>
-  </si>
-  <si>
-    <t>135212079</t>
-  </si>
-  <si>
-    <t>135214309</t>
-  </si>
-  <si>
-    <t>135219311</t>
-  </si>
-  <si>
-    <t>135221053</t>
-  </si>
-  <si>
-    <t>135229207</t>
-  </si>
-  <si>
-    <t>135222154</t>
-  </si>
-  <si>
-    <t>135222203</t>
-  </si>
-  <si>
-    <t>135221690</t>
-  </si>
-  <si>
-    <t>135236513</t>
-  </si>
-  <si>
-    <t>135207629</t>
-  </si>
-  <si>
-    <t>135208277</t>
-  </si>
-  <si>
-    <t>135208380</t>
-  </si>
-  <si>
-    <t>135208539</t>
-  </si>
-  <si>
-    <t>135210020</t>
-  </si>
-  <si>
-    <t>135211010</t>
-  </si>
-  <si>
-    <t>135211849</t>
-  </si>
-  <si>
-    <t>135212084</t>
-  </si>
-  <si>
-    <t>135213849</t>
-  </si>
-  <si>
-    <t>135218690</t>
-  </si>
-  <si>
-    <t>135219384</t>
-  </si>
-  <si>
-    <t>135222769</t>
-  </si>
-  <si>
-    <t>135230689</t>
-  </si>
-  <si>
-    <t>135234887</t>
-  </si>
-  <si>
-    <t>135236142</t>
-  </si>
-  <si>
-    <t>135240947</t>
-  </si>
-  <si>
-    <t>135220277</t>
-  </si>
-  <si>
-    <t>135234370</t>
+    <t>Relatório de Recusas Santander - 17/11/2025</t>
+  </si>
+  <si>
+    <t>135263703</t>
+  </si>
+  <si>
+    <t>135253574</t>
+  </si>
+  <si>
+    <t>135258876</t>
+  </si>
+  <si>
+    <t>135276369</t>
+  </si>
+  <si>
+    <t>135281055</t>
+  </si>
+  <si>
+    <t>135286413</t>
+  </si>
+  <si>
+    <t>135285241</t>
+  </si>
+  <si>
+    <t>135269213</t>
+  </si>
+  <si>
+    <t>135284898</t>
+  </si>
+  <si>
+    <t>135285223</t>
+  </si>
+  <si>
+    <t>135290592</t>
+  </si>
+  <si>
+    <t>135301223</t>
+  </si>
+  <si>
+    <t>135289956</t>
+  </si>
+  <si>
+    <t>135297389</t>
+  </si>
+  <si>
+    <t>135299215</t>
+  </si>
+  <si>
+    <t>135219869</t>
+  </si>
+  <si>
+    <t>135302691</t>
+  </si>
+  <si>
+    <t>135291479</t>
+  </si>
+  <si>
+    <t>135302257</t>
+  </si>
+  <si>
+    <t>135321785</t>
+  </si>
+  <si>
+    <t>135320502</t>
+  </si>
+  <si>
+    <t>135319454</t>
+  </si>
+  <si>
+    <t>135325999</t>
+  </si>
+  <si>
+    <t>135295885</t>
+  </si>
+  <si>
+    <t>135337490</t>
+  </si>
+  <si>
+    <t>135348170</t>
+  </si>
+  <si>
+    <t>135350684</t>
+  </si>
+  <si>
+    <t>135348750</t>
+  </si>
+  <si>
+    <t>135348899</t>
+  </si>
+  <si>
+    <t>135347277</t>
+  </si>
+  <si>
+    <t>135342764</t>
+  </si>
+  <si>
+    <t>135345538</t>
+  </si>
+  <si>
+    <t>135350601</t>
+  </si>
+  <si>
+    <t>135358226</t>
+  </si>
+  <si>
+    <t>135337039</t>
+  </si>
+  <si>
+    <t>135363286</t>
+  </si>
+  <si>
+    <t>135363654</t>
+  </si>
+  <si>
+    <t>135326989</t>
+  </si>
+  <si>
+    <t>135365421</t>
+  </si>
+  <si>
+    <t>135367081</t>
+  </si>
+  <si>
+    <t>135274867</t>
+  </si>
+  <si>
+    <t>135369278</t>
+  </si>
+  <si>
+    <t>135369940</t>
+  </si>
+  <si>
+    <t>135367116</t>
+  </si>
+  <si>
+    <t>135366184</t>
+  </si>
+  <si>
+    <t>135368946</t>
+  </si>
+  <si>
+    <t>135367780</t>
+  </si>
+  <si>
+    <t>135362902</t>
+  </si>
+  <si>
+    <t>135362890</t>
+  </si>
+  <si>
+    <t>135379314</t>
+  </si>
+  <si>
+    <t>135309418</t>
+  </si>
+  <si>
+    <t>135378065</t>
+  </si>
+  <si>
+    <t>135390733</t>
+  </si>
+  <si>
+    <t>135381845</t>
+  </si>
+  <si>
+    <t>135323190</t>
+  </si>
+  <si>
+    <t>135331833</t>
+  </si>
+  <si>
+    <t>135328650</t>
+  </si>
+  <si>
+    <t>135359705</t>
+  </si>
+  <si>
+    <t>135229503</t>
+  </si>
+  <si>
+    <t>135343211</t>
+  </si>
+  <si>
+    <t>135264551</t>
+  </si>
+  <si>
+    <t>135297311</t>
+  </si>
+  <si>
+    <t>135258166</t>
+  </si>
+  <si>
+    <t>135367248</t>
+  </si>
+  <si>
+    <t>135357698</t>
+  </si>
+  <si>
+    <t>135362858</t>
+  </si>
+  <si>
+    <t>135243660</t>
+  </si>
+  <si>
+    <t>135248613</t>
+  </si>
+  <si>
+    <t>135252585</t>
+  </si>
+  <si>
+    <t>135256387</t>
+  </si>
+  <si>
+    <t>135256972</t>
+  </si>
+  <si>
+    <t>135259176</t>
+  </si>
+  <si>
+    <t>135260994</t>
+  </si>
+  <si>
+    <t>135262124</t>
+  </si>
+  <si>
+    <t>135263437</t>
+  </si>
+  <si>
+    <t>135265560</t>
+  </si>
+  <si>
+    <t>135265565</t>
+  </si>
+  <si>
+    <t>135274115</t>
+  </si>
+  <si>
+    <t>135273181</t>
+  </si>
+  <si>
+    <t>135276025</t>
+  </si>
+  <si>
+    <t>135276658</t>
+  </si>
+  <si>
+    <t>135279960</t>
+  </si>
+  <si>
+    <t>135283050</t>
+  </si>
+  <si>
+    <t>135283325</t>
+  </si>
+  <si>
+    <t>135284818</t>
+  </si>
+  <si>
+    <t>135285736</t>
+  </si>
+  <si>
+    <t>135286139</t>
+  </si>
+  <si>
+    <t>135286502</t>
+  </si>
+  <si>
+    <t>135291391</t>
+  </si>
+  <si>
+    <t>135291966</t>
+  </si>
+  <si>
+    <t>135293121</t>
+  </si>
+  <si>
+    <t>135296042</t>
+  </si>
+  <si>
+    <t>135296915</t>
+  </si>
+  <si>
+    <t>135297228</t>
+  </si>
+  <si>
+    <t>135297364</t>
+  </si>
+  <si>
+    <t>135298091</t>
+  </si>
+  <si>
+    <t>135298767</t>
+  </si>
+  <si>
+    <t>135298875</t>
+  </si>
+  <si>
+    <t>135299007</t>
+  </si>
+  <si>
+    <t>135299581</t>
+  </si>
+  <si>
+    <t>135301363</t>
+  </si>
+  <si>
+    <t>135302866</t>
+  </si>
+  <si>
+    <t>135305849</t>
+  </si>
+  <si>
+    <t>135306614</t>
+  </si>
+  <si>
+    <t>135306715</t>
+  </si>
+  <si>
+    <t>135306993</t>
+  </si>
+  <si>
+    <t>135307482</t>
+  </si>
+  <si>
+    <t>135321780</t>
+  </si>
+  <si>
+    <t>135309779</t>
+  </si>
+  <si>
+    <t>135310611</t>
+  </si>
+  <si>
+    <t>135341606</t>
+  </si>
+  <si>
+    <t>135358439</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 17.11.2025 a 23.11.2025</t>
   </si>
 </sst>
 </file>
@@ -603,7 +798,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -635,16 +830,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135203182</v>
+        <v>135254575</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -653,16 +848,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -671,16 +866,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -689,16 +884,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -707,16 +902,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -725,16 +920,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -743,16 +938,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -761,16 +956,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -778,16 +973,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -795,16 +990,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -812,16 +1007,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -829,16 +1024,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -846,16 +1041,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -863,16 +1058,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -880,16 +1075,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -897,16 +1092,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -914,16 +1109,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -931,16 +1126,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -948,16 +1143,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -965,16 +1160,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -982,16 +1177,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -999,16 +1194,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1016,16 +1211,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1033,16 +1228,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1050,16 +1245,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1067,16 +1262,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1084,16 +1279,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1101,16 +1296,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1118,16 +1313,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1135,16 +1330,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1152,16 +1347,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1169,16 +1364,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1186,16 +1381,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1203,16 +1398,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1220,16 +1415,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1237,16 +1432,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1254,16 +1449,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1271,16 +1466,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1288,16 +1483,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1305,16 +1500,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1322,16 +1517,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1339,16 +1534,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1356,16 +1551,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1373,16 +1568,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1390,16 +1585,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1407,16 +1602,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1424,16 +1619,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1441,18 +1636,1123 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="2" t="s">
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1470,31 +2770,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10409F99-02F1-4C79-A441-A8B3D1C966FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400CAB8E-D97D-48F8-87E8-3B20879E9E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -575,7 +575,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -593,7 +593,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -611,7 +611,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -629,7 +629,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -665,7 +665,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -683,7 +683,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -701,7 +701,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -718,7 +718,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -752,7 +752,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -769,7 +769,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -786,7 +786,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -803,7 +803,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -820,7 +820,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -837,7 +837,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -854,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -871,7 +871,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -888,7 +888,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -905,7 +905,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -922,7 +922,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -939,7 +939,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -956,7 +956,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -973,7 +973,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400CAB8E-D97D-48F8-87E8-3B20879E9E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D16786-7573-44C1-8127-04F662D6477A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1010,31 +1010,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D16786-7573-44C1-8127-04F662D6477A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8661EDFD-8257-4A88-AFEC-9A7357124FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>1070</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 17.11.2025 a 23.11.2025</t>
   </si>
   <si>
     <t>Relatório de Recusas Santander - 18/11/2025</t>
@@ -572,10 +569,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -584,16 +581,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -602,16 +599,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -620,16 +617,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -638,13 +635,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
@@ -656,16 +653,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -674,16 +671,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -692,16 +689,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -709,16 +706,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -726,16 +723,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -743,16 +740,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -760,16 +757,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -777,16 +774,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -794,16 +791,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -811,16 +808,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -828,16 +825,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -845,16 +842,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -862,16 +859,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -879,16 +876,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -896,16 +893,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -913,16 +910,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -930,16 +927,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -947,16 +944,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -964,16 +961,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -981,16 +978,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1010,31 +1007,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8661EDFD-8257-4A88-AFEC-9A7357124FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E6292A-959C-4F67-A2FC-A73E6CB75BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>135401182</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 17.11.2025 a 23.11.2025</t>
   </si>
 </sst>
 </file>
@@ -572,7 +575,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -590,7 +593,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -608,7 +611,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -626,7 +629,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -644,7 +647,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -662,7 +665,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -680,7 +683,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -698,7 +701,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -715,7 +718,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -732,7 +735,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -749,7 +752,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -766,7 +769,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -783,7 +786,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -800,7 +803,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -817,7 +820,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -834,7 +837,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -851,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -868,7 +871,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -885,7 +888,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -902,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -919,7 +922,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -936,7 +939,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -953,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -970,7 +973,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -987,7 +990,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1007,31 +1010,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E6292A-959C-4F67-A2FC-A73E6CB75BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D475A31-D8D7-4001-BF65-EB03F00E421A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="76">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,82 +54,208 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 18/11/2025</t>
-  </si>
-  <si>
-    <t>135322770</t>
-  </si>
-  <si>
-    <t>135343907</t>
-  </si>
-  <si>
-    <t>135369383</t>
-  </si>
-  <si>
-    <t>135375585</t>
-  </si>
-  <si>
-    <t>135381258</t>
-  </si>
-  <si>
-    <t>135379927</t>
-  </si>
-  <si>
-    <t>135381540</t>
-  </si>
-  <si>
-    <t>135386042</t>
-  </si>
-  <si>
-    <t>135380421</t>
-  </si>
-  <si>
-    <t>135401219</t>
-  </si>
-  <si>
-    <t>135399619</t>
-  </si>
-  <si>
-    <t>135387693</t>
-  </si>
-  <si>
-    <t>135400496</t>
-  </si>
-  <si>
-    <t>135412937</t>
-  </si>
-  <si>
-    <t>135403396</t>
-  </si>
-  <si>
-    <t>135396609</t>
-  </si>
-  <si>
-    <t>135410884</t>
-  </si>
-  <si>
-    <t>135239368</t>
-  </si>
-  <si>
-    <t>135240201</t>
-  </si>
-  <si>
-    <t>135273571</t>
-  </si>
-  <si>
-    <t>135294003</t>
-  </si>
-  <si>
-    <t>135323024</t>
-  </si>
-  <si>
-    <t>135309543</t>
-  </si>
-  <si>
-    <t>135401182</t>
-  </si>
-  <si>
     <t>Relatório de Recusas 17.11.2025 a 23.11.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 19 e 20/11/2025</t>
+  </si>
+  <si>
+    <t>135272339</t>
+  </si>
+  <si>
+    <t>135332671</t>
+  </si>
+  <si>
+    <t>135325423</t>
+  </si>
+  <si>
+    <t>135365508</t>
+  </si>
+  <si>
+    <t>135367636</t>
+  </si>
+  <si>
+    <t>135369093</t>
+  </si>
+  <si>
+    <t>135385850</t>
+  </si>
+  <si>
+    <t>135384637</t>
+  </si>
+  <si>
+    <t>135383866</t>
+  </si>
+  <si>
+    <t>135401328</t>
+  </si>
+  <si>
+    <t>135412649</t>
+  </si>
+  <si>
+    <t>135404300</t>
+  </si>
+  <si>
+    <t>135402345</t>
+  </si>
+  <si>
+    <t>135407770</t>
+  </si>
+  <si>
+    <t>135425602</t>
+  </si>
+  <si>
+    <t>135409244</t>
+  </si>
+  <si>
+    <t>135432305</t>
+  </si>
+  <si>
+    <t>135368544</t>
+  </si>
+  <si>
+    <t>135404264</t>
+  </si>
+  <si>
+    <t>135319003</t>
+  </si>
+  <si>
+    <t>135427601</t>
+  </si>
+  <si>
+    <t>135443624</t>
+  </si>
+  <si>
+    <t>135421480</t>
+  </si>
+  <si>
+    <t>135450619</t>
+  </si>
+  <si>
+    <t>135453129</t>
+  </si>
+  <si>
+    <t>135443910</t>
+  </si>
+  <si>
+    <t>135272426</t>
+  </si>
+  <si>
+    <t>10/11/2025</t>
+  </si>
+  <si>
+    <t>135274950</t>
+  </si>
+  <si>
+    <t>135359719</t>
+  </si>
+  <si>
+    <t>135402070</t>
+  </si>
+  <si>
+    <t>135286262</t>
+  </si>
+  <si>
+    <t>135342282</t>
+  </si>
+  <si>
+    <t>135328296</t>
+  </si>
+  <si>
+    <t>135271641</t>
+  </si>
+  <si>
+    <t>135385934</t>
+  </si>
+  <si>
+    <t>135461280</t>
+  </si>
+  <si>
+    <t>135351508</t>
+  </si>
+  <si>
+    <t>135317274</t>
+  </si>
+  <si>
+    <t>135322715</t>
+  </si>
+  <si>
+    <t>135322802</t>
+  </si>
+  <si>
+    <t>135320212</t>
+  </si>
+  <si>
+    <t>135320362</t>
+  </si>
+  <si>
+    <t>135321662</t>
+  </si>
+  <si>
+    <t>135321977</t>
+  </si>
+  <si>
+    <t>135322098</t>
+  </si>
+  <si>
+    <t>135322866</t>
+  </si>
+  <si>
+    <t>135331241</t>
+  </si>
+  <si>
+    <t>135331507</t>
+  </si>
+  <si>
+    <t>135358026</t>
+  </si>
+  <si>
+    <t>135357785</t>
+  </si>
+  <si>
+    <t>135355834</t>
+  </si>
+  <si>
+    <t>135356447</t>
+  </si>
+  <si>
+    <t>135359740</t>
+  </si>
+  <si>
+    <t>135363422</t>
+  </si>
+  <si>
+    <t>135363430</t>
+  </si>
+  <si>
+    <t>135364007</t>
+  </si>
+  <si>
+    <t>135365647</t>
+  </si>
+  <si>
+    <t>135367652</t>
+  </si>
+  <si>
+    <t>135369126</t>
+  </si>
+  <si>
+    <t>135371344</t>
+  </si>
+  <si>
+    <t>135252088</t>
+  </si>
+  <si>
+    <t>135301281</t>
+  </si>
+  <si>
+    <t>135308735</t>
+  </si>
+  <si>
+    <t>135298366</t>
+  </si>
+  <si>
+    <t>135298769</t>
   </si>
 </sst>
 </file>
@@ -534,7 +660,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -566,16 +692,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135232311</v>
+        <v>135271039</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -584,16 +710,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -602,16 +728,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -620,16 +746,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -638,16 +764,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -656,16 +782,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -674,16 +800,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -692,16 +818,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -709,16 +835,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -726,16 +852,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -743,16 +869,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -760,16 +886,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -777,16 +903,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -794,16 +920,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -811,16 +937,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -828,16 +954,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -845,16 +971,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -862,16 +988,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -879,16 +1005,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -896,16 +1022,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -913,16 +1039,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -930,16 +1056,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -947,16 +1073,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -964,16 +1090,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -981,18 +1107,732 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D475A31-D8D7-4001-BF65-EB03F00E421A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9784909E-331C-4B5F-8F58-56CDE4A09D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="86">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,205 +57,235 @@
     <t>Relatório de Recusas 17.11.2025 a 23.11.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 19 e 20/11/2025</t>
-  </si>
-  <si>
-    <t>135272339</t>
-  </si>
-  <si>
-    <t>135332671</t>
-  </si>
-  <si>
-    <t>135325423</t>
-  </si>
-  <si>
-    <t>135365508</t>
-  </si>
-  <si>
-    <t>135367636</t>
-  </si>
-  <si>
-    <t>135369093</t>
-  </si>
-  <si>
-    <t>135385850</t>
-  </si>
-  <si>
-    <t>135384637</t>
-  </si>
-  <si>
-    <t>135383866</t>
-  </si>
-  <si>
-    <t>135401328</t>
-  </si>
-  <si>
-    <t>135412649</t>
-  </si>
-  <si>
-    <t>135404300</t>
-  </si>
-  <si>
-    <t>135402345</t>
-  </si>
-  <si>
-    <t>135407770</t>
-  </si>
-  <si>
-    <t>135425602</t>
-  </si>
-  <si>
-    <t>135409244</t>
-  </si>
-  <si>
-    <t>135432305</t>
-  </si>
-  <si>
-    <t>135368544</t>
-  </si>
-  <si>
-    <t>135404264</t>
-  </si>
-  <si>
-    <t>135319003</t>
-  </si>
-  <si>
-    <t>135427601</t>
-  </si>
-  <si>
-    <t>135443624</t>
-  </si>
-  <si>
-    <t>135421480</t>
-  </si>
-  <si>
-    <t>135450619</t>
-  </si>
-  <si>
-    <t>135453129</t>
-  </si>
-  <si>
-    <t>135443910</t>
-  </si>
-  <si>
-    <t>135272426</t>
-  </si>
-  <si>
-    <t>10/11/2025</t>
-  </si>
-  <si>
-    <t>135274950</t>
-  </si>
-  <si>
-    <t>135359719</t>
-  </si>
-  <si>
-    <t>135402070</t>
-  </si>
-  <si>
-    <t>135286262</t>
-  </si>
-  <si>
-    <t>135342282</t>
-  </si>
-  <si>
-    <t>135328296</t>
-  </si>
-  <si>
-    <t>135271641</t>
-  </si>
-  <si>
-    <t>135385934</t>
-  </si>
-  <si>
-    <t>135461280</t>
-  </si>
-  <si>
-    <t>135351508</t>
-  </si>
-  <si>
-    <t>135317274</t>
-  </si>
-  <si>
-    <t>135322715</t>
-  </si>
-  <si>
-    <t>135322802</t>
-  </si>
-  <si>
-    <t>135320212</t>
-  </si>
-  <si>
-    <t>135320362</t>
-  </si>
-  <si>
-    <t>135321662</t>
-  </si>
-  <si>
-    <t>135321977</t>
-  </si>
-  <si>
-    <t>135322098</t>
-  </si>
-  <si>
-    <t>135322866</t>
-  </si>
-  <si>
-    <t>135331241</t>
-  </si>
-  <si>
-    <t>135331507</t>
-  </si>
-  <si>
-    <t>135358026</t>
-  </si>
-  <si>
-    <t>135357785</t>
-  </si>
-  <si>
-    <t>135355834</t>
-  </si>
-  <si>
-    <t>135356447</t>
-  </si>
-  <si>
-    <t>135359740</t>
-  </si>
-  <si>
-    <t>135363422</t>
-  </si>
-  <si>
-    <t>135363430</t>
-  </si>
-  <si>
-    <t>135364007</t>
-  </si>
-  <si>
-    <t>135365647</t>
-  </si>
-  <si>
-    <t>135367652</t>
-  </si>
-  <si>
-    <t>135369126</t>
-  </si>
-  <si>
-    <t>135371344</t>
-  </si>
-  <si>
-    <t>135252088</t>
-  </si>
-  <si>
-    <t>135301281</t>
-  </si>
-  <si>
-    <t>135308735</t>
-  </si>
-  <si>
-    <t>135298366</t>
-  </si>
-  <si>
-    <t>135298769</t>
+    <t>Relatório de Recusas Santander - 21 e 22/11/2025</t>
+  </si>
+  <si>
+    <t>135353339</t>
+  </si>
+  <si>
+    <t>135383311</t>
+  </si>
+  <si>
+    <t>135387528</t>
+  </si>
+  <si>
+    <t>135384685</t>
+  </si>
+  <si>
+    <t>135387590</t>
+  </si>
+  <si>
+    <t>135392746</t>
+  </si>
+  <si>
+    <t>135391589</t>
+  </si>
+  <si>
+    <t>135383436</t>
+  </si>
+  <si>
+    <t>135411756</t>
+  </si>
+  <si>
+    <t>135402717</t>
+  </si>
+  <si>
+    <t>135412135</t>
+  </si>
+  <si>
+    <t>135399248</t>
+  </si>
+  <si>
+    <t>135402388</t>
+  </si>
+  <si>
+    <t>135397889</t>
+  </si>
+  <si>
+    <t>135432291</t>
+  </si>
+  <si>
+    <t>135412501</t>
+  </si>
+  <si>
+    <t>135424027</t>
+  </si>
+  <si>
+    <t>135429701</t>
+  </si>
+  <si>
+    <t>135433959</t>
+  </si>
+  <si>
+    <t>135389714</t>
+  </si>
+  <si>
+    <t>135453654</t>
+  </si>
+  <si>
+    <t>135437149</t>
+  </si>
+  <si>
+    <t>135381341</t>
+  </si>
+  <si>
+    <t>135317421</t>
+  </si>
+  <si>
+    <t>135346666</t>
+  </si>
+  <si>
+    <t>135319310</t>
+  </si>
+  <si>
+    <t>135291535</t>
+  </si>
+  <si>
+    <t>135375520</t>
+  </si>
+  <si>
+    <t>135297492</t>
+  </si>
+  <si>
+    <t>135377061</t>
+  </si>
+  <si>
+    <t>135299296</t>
+  </si>
+  <si>
+    <t>135388850</t>
+  </si>
+  <si>
+    <t>135348508</t>
+  </si>
+  <si>
+    <t>135341023</t>
+  </si>
+  <si>
+    <t>135375492</t>
+  </si>
+  <si>
+    <t>135376608</t>
+  </si>
+  <si>
+    <t>135377454</t>
+  </si>
+  <si>
+    <t>135377581</t>
+  </si>
+  <si>
+    <t>135378691</t>
+  </si>
+  <si>
+    <t>135378762</t>
+  </si>
+  <si>
+    <t>135380667</t>
+  </si>
+  <si>
+    <t>135380811</t>
+  </si>
+  <si>
+    <t>135380949</t>
+  </si>
+  <si>
+    <t>135380985</t>
+  </si>
+  <si>
+    <t>135381095</t>
+  </si>
+  <si>
+    <t>135386998</t>
+  </si>
+  <si>
+    <t>135388034</t>
+  </si>
+  <si>
+    <t>135388426</t>
+  </si>
+  <si>
+    <t>135389639</t>
+  </si>
+  <si>
+    <t>135411191</t>
+  </si>
+  <si>
+    <t>135353357</t>
+  </si>
+  <si>
+    <t>135341716</t>
+  </si>
+  <si>
+    <t>135342234</t>
+  </si>
+  <si>
+    <t>135425814</t>
+  </si>
+  <si>
+    <t>135423476</t>
+  </si>
+  <si>
+    <t>135336924</t>
+  </si>
+  <si>
+    <t>135337516</t>
+  </si>
+  <si>
+    <t>135338105</t>
+  </si>
+  <si>
+    <t>135338314</t>
+  </si>
+  <si>
+    <t>135339890</t>
+  </si>
+  <si>
+    <t>135341441</t>
+  </si>
+  <si>
+    <t>135341943</t>
+  </si>
+  <si>
+    <t>135342297</t>
+  </si>
+  <si>
+    <t>135344593</t>
+  </si>
+  <si>
+    <t>135346170</t>
+  </si>
+  <si>
+    <t>135346676</t>
+  </si>
+  <si>
+    <t>135346945</t>
+  </si>
+  <si>
+    <t>135347258</t>
+  </si>
+  <si>
+    <t>135347708</t>
+  </si>
+  <si>
+    <t>135348142</t>
+  </si>
+  <si>
+    <t>135349343</t>
+  </si>
+  <si>
+    <t>135349924</t>
+  </si>
+  <si>
+    <t>135350981</t>
+  </si>
+  <si>
+    <t>135352673</t>
+  </si>
+  <si>
+    <t>135352931</t>
+  </si>
+  <si>
+    <t>135429934</t>
   </si>
 </sst>
 </file>
@@ -660,7 +690,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -692,7 +722,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135271039</v>
+        <v>135337052</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1833,6 +1863,176 @@
         <v>8</v>
       </c>
       <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1850,31 +2050,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9784909E-331C-4B5F-8F58-56CDE4A09D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4471718-FE43-4FFF-899E-C6E64EE4E2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="50">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,238 +54,130 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas 17.11.2025 a 23.11.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 21 e 22/11/2025</t>
-  </si>
-  <si>
-    <t>135353339</t>
-  </si>
-  <si>
-    <t>135383311</t>
-  </si>
-  <si>
-    <t>135387528</t>
-  </si>
-  <si>
-    <t>135384685</t>
-  </si>
-  <si>
-    <t>135387590</t>
-  </si>
-  <si>
-    <t>135392746</t>
-  </si>
-  <si>
-    <t>135391589</t>
-  </si>
-  <si>
-    <t>135383436</t>
-  </si>
-  <si>
-    <t>135411756</t>
-  </si>
-  <si>
-    <t>135402717</t>
-  </si>
-  <si>
-    <t>135412135</t>
-  </si>
-  <si>
-    <t>135399248</t>
-  </si>
-  <si>
-    <t>135402388</t>
-  </si>
-  <si>
-    <t>135397889</t>
-  </si>
-  <si>
-    <t>135432291</t>
-  </si>
-  <si>
-    <t>135412501</t>
-  </si>
-  <si>
-    <t>135424027</t>
-  </si>
-  <si>
-    <t>135429701</t>
-  </si>
-  <si>
-    <t>135433959</t>
-  </si>
-  <si>
-    <t>135389714</t>
-  </si>
-  <si>
-    <t>135453654</t>
-  </si>
-  <si>
-    <t>135437149</t>
-  </si>
-  <si>
-    <t>135381341</t>
-  </si>
-  <si>
-    <t>135317421</t>
-  </si>
-  <si>
-    <t>135346666</t>
-  </si>
-  <si>
-    <t>135319310</t>
-  </si>
-  <si>
-    <t>135291535</t>
-  </si>
-  <si>
-    <t>135375520</t>
-  </si>
-  <si>
-    <t>135297492</t>
-  </si>
-  <si>
-    <t>135377061</t>
-  </si>
-  <si>
-    <t>135299296</t>
-  </si>
-  <si>
-    <t>135388850</t>
-  </si>
-  <si>
-    <t>135348508</t>
-  </si>
-  <si>
-    <t>135341023</t>
-  </si>
-  <si>
-    <t>135375492</t>
-  </si>
-  <si>
-    <t>135376608</t>
-  </si>
-  <si>
-    <t>135377454</t>
-  </si>
-  <si>
-    <t>135377581</t>
-  </si>
-  <si>
-    <t>135378691</t>
-  </si>
-  <si>
-    <t>135378762</t>
-  </si>
-  <si>
-    <t>135380667</t>
-  </si>
-  <si>
-    <t>135380811</t>
-  </si>
-  <si>
-    <t>135380949</t>
-  </si>
-  <si>
-    <t>135380985</t>
-  </si>
-  <si>
-    <t>135381095</t>
-  </si>
-  <si>
-    <t>135386998</t>
-  </si>
-  <si>
-    <t>135388034</t>
-  </si>
-  <si>
-    <t>135388426</t>
-  </si>
-  <si>
-    <t>135389639</t>
-  </si>
-  <si>
-    <t>135411191</t>
-  </si>
-  <si>
-    <t>135353357</t>
-  </si>
-  <si>
-    <t>135341716</t>
-  </si>
-  <si>
-    <t>135342234</t>
-  </si>
-  <si>
-    <t>135425814</t>
-  </si>
-  <si>
-    <t>135423476</t>
-  </si>
-  <si>
-    <t>135336924</t>
-  </si>
-  <si>
-    <t>135337516</t>
-  </si>
-  <si>
-    <t>135338105</t>
-  </si>
-  <si>
-    <t>135338314</t>
-  </si>
-  <si>
-    <t>135339890</t>
-  </si>
-  <si>
-    <t>135341441</t>
-  </si>
-  <si>
-    <t>135341943</t>
-  </si>
-  <si>
-    <t>135342297</t>
-  </si>
-  <si>
-    <t>135344593</t>
-  </si>
-  <si>
-    <t>135346170</t>
-  </si>
-  <si>
-    <t>135346676</t>
-  </si>
-  <si>
-    <t>135346945</t>
-  </si>
-  <si>
-    <t>135347258</t>
-  </si>
-  <si>
-    <t>135347708</t>
-  </si>
-  <si>
-    <t>135348142</t>
-  </si>
-  <si>
-    <t>135349343</t>
-  </si>
-  <si>
-    <t>135349924</t>
-  </si>
-  <si>
-    <t>135350981</t>
-  </si>
-  <si>
-    <t>135352673</t>
-  </si>
-  <si>
-    <t>135352931</t>
-  </si>
-  <si>
-    <t>135429934</t>
+    <t>Relatório de Recusas Santander - 24/11/2025</t>
+  </si>
+  <si>
+    <t>135416176</t>
+  </si>
+  <si>
+    <t>135424757</t>
+  </si>
+  <si>
+    <t>135436845</t>
+  </si>
+  <si>
+    <t>135455689</t>
+  </si>
+  <si>
+    <t>135447706</t>
+  </si>
+  <si>
+    <t>135447865</t>
+  </si>
+  <si>
+    <t>135460163</t>
+  </si>
+  <si>
+    <t>135430722</t>
+  </si>
+  <si>
+    <t>135465542</t>
+  </si>
+  <si>
+    <t>135411669</t>
+  </si>
+  <si>
+    <t>135453300</t>
+  </si>
+  <si>
+    <t>135429256</t>
+  </si>
+  <si>
+    <t>135426886</t>
+  </si>
+  <si>
+    <t>135369003</t>
+  </si>
+  <si>
+    <t>135349448</t>
+  </si>
+  <si>
+    <t>135341393</t>
+  </si>
+  <si>
+    <t>135453744</t>
+  </si>
+  <si>
+    <t>135441593</t>
+  </si>
+  <si>
+    <t>135421095</t>
+  </si>
+  <si>
+    <t>135209200</t>
+  </si>
+  <si>
+    <t>135465046</t>
+  </si>
+  <si>
+    <t>135443260</t>
+  </si>
+  <si>
+    <t>135466041</t>
+  </si>
+  <si>
+    <t>135430362</t>
+  </si>
+  <si>
+    <t>135451102</t>
+  </si>
+  <si>
+    <t>135466627</t>
+  </si>
+  <si>
+    <t>135397039</t>
+  </si>
+  <si>
+    <t>135398313</t>
+  </si>
+  <si>
+    <t>135399941</t>
+  </si>
+  <si>
+    <t>135400989</t>
+  </si>
+  <si>
+    <t>135407001</t>
+  </si>
+  <si>
+    <t>135407729</t>
+  </si>
+  <si>
+    <t>135408921</t>
+  </si>
+  <si>
+    <t>135441855</t>
+  </si>
+  <si>
+    <t>135410250</t>
+  </si>
+  <si>
+    <t>135410697</t>
+  </si>
+  <si>
+    <t>135412025</t>
+  </si>
+  <si>
+    <t>135412039</t>
+  </si>
+  <si>
+    <t>135412102</t>
+  </si>
+  <si>
+    <t>135413036</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 24.11.2025 a 30.11.2025</t>
   </si>
 </sst>
 </file>
@@ -690,7 +582,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -722,16 +614,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135337052</v>
+        <v>135401772</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -740,16 +632,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -758,16 +650,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -776,16 +668,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -794,16 +686,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -812,16 +704,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -830,16 +722,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -848,16 +740,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -865,16 +757,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -882,16 +774,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -899,16 +791,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -916,16 +808,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -933,16 +825,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -950,16 +842,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -967,16 +859,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -984,16 +876,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1001,16 +893,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1018,16 +910,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1035,16 +927,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1052,16 +944,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1069,16 +961,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1086,16 +978,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1103,16 +995,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1120,16 +1012,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1137,16 +1029,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1154,16 +1046,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1171,16 +1063,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1188,16 +1080,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1205,16 +1097,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1222,16 +1114,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1239,16 +1131,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1256,16 +1148,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1273,16 +1165,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1290,16 +1182,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1307,16 +1199,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1324,16 +1216,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1341,16 +1233,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1358,16 +1250,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1375,16 +1267,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1392,16 +1284,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1409,630 +1301,18 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E78" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4471718-FE43-4FFF-899E-C6E64EE4E2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4C82F1-C55A-43BE-A2DA-0F897E20DF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,130 +54,100 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 24/11/2025</t>
-  </si>
-  <si>
-    <t>135416176</t>
-  </si>
-  <si>
-    <t>135424757</t>
-  </si>
-  <si>
-    <t>135436845</t>
-  </si>
-  <si>
-    <t>135455689</t>
-  </si>
-  <si>
-    <t>135447706</t>
-  </si>
-  <si>
-    <t>135447865</t>
-  </si>
-  <si>
-    <t>135460163</t>
-  </si>
-  <si>
-    <t>135430722</t>
-  </si>
-  <si>
-    <t>135465542</t>
-  </si>
-  <si>
-    <t>135411669</t>
-  </si>
-  <si>
-    <t>135453300</t>
-  </si>
-  <si>
-    <t>135429256</t>
-  </si>
-  <si>
-    <t>135426886</t>
-  </si>
-  <si>
-    <t>135369003</t>
-  </si>
-  <si>
-    <t>135349448</t>
-  </si>
-  <si>
-    <t>135341393</t>
-  </si>
-  <si>
-    <t>135453744</t>
-  </si>
-  <si>
-    <t>135441593</t>
-  </si>
-  <si>
-    <t>135421095</t>
-  </si>
-  <si>
-    <t>135209200</t>
-  </si>
-  <si>
-    <t>135465046</t>
-  </si>
-  <si>
-    <t>135443260</t>
-  </si>
-  <si>
-    <t>135466041</t>
-  </si>
-  <si>
-    <t>135430362</t>
-  </si>
-  <si>
-    <t>135451102</t>
-  </si>
-  <si>
-    <t>135466627</t>
-  </si>
-  <si>
-    <t>135397039</t>
-  </si>
-  <si>
-    <t>135398313</t>
-  </si>
-  <si>
-    <t>135399941</t>
-  </si>
-  <si>
-    <t>135400989</t>
-  </si>
-  <si>
-    <t>135407001</t>
-  </si>
-  <si>
-    <t>135407729</t>
-  </si>
-  <si>
-    <t>135408921</t>
-  </si>
-  <si>
-    <t>135441855</t>
-  </si>
-  <si>
-    <t>135410250</t>
-  </si>
-  <si>
-    <t>135410697</t>
-  </si>
-  <si>
-    <t>135412025</t>
-  </si>
-  <si>
-    <t>135412039</t>
-  </si>
-  <si>
-    <t>135412102</t>
-  </si>
-  <si>
-    <t>135413036</t>
-  </si>
-  <si>
     <t>Relatório de Recusas 24.11.2025 a 30.11.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 25/11/2025</t>
+  </si>
+  <si>
+    <t>135362829</t>
+  </si>
+  <si>
+    <t>135370895</t>
+  </si>
+  <si>
+    <t>135418067</t>
+  </si>
+  <si>
+    <t>135431815</t>
+  </si>
+  <si>
+    <t>135475935</t>
+  </si>
+  <si>
+    <t>135469811</t>
+  </si>
+  <si>
+    <t>135475033</t>
+  </si>
+  <si>
+    <t>135365526</t>
+  </si>
+  <si>
+    <t>135466743</t>
+  </si>
+  <si>
+    <t>135487600</t>
+  </si>
+  <si>
+    <t>135470636</t>
+  </si>
+  <si>
+    <t>135491304</t>
+  </si>
+  <si>
+    <t>135493505</t>
+  </si>
+  <si>
+    <t>135464753</t>
+  </si>
+  <si>
+    <t>135490210</t>
+  </si>
+  <si>
+    <t>135423401</t>
+  </si>
+  <si>
+    <t>135513778</t>
+  </si>
+  <si>
+    <t>135371138</t>
+  </si>
+  <si>
+    <t>135422961</t>
+  </si>
+  <si>
+    <t>135465259</t>
+  </si>
+  <si>
+    <t>135384088</t>
+  </si>
+  <si>
+    <t>135380282</t>
+  </si>
+  <si>
+    <t>135424489</t>
+  </si>
+  <si>
+    <t>135421815</t>
+  </si>
+  <si>
+    <t>135427573</t>
+  </si>
+  <si>
+    <t>135443033</t>
+  </si>
+  <si>
+    <t>135497978</t>
+  </si>
+  <si>
+    <t>135440916</t>
+  </si>
+  <si>
+    <t>135442838</t>
+  </si>
+  <si>
+    <t>135460460</t>
   </si>
 </sst>
 </file>
@@ -582,7 +552,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -614,16 +584,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135401772</v>
+        <v>135367670</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -632,16 +602,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -650,16 +620,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -668,16 +638,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -686,16 +656,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -704,16 +674,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -722,16 +692,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -740,16 +710,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -757,16 +727,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -774,16 +744,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -791,16 +761,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -808,16 +778,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -825,16 +795,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -842,16 +812,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -859,16 +829,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -876,16 +846,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -893,16 +863,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -910,16 +880,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -927,16 +897,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -944,16 +914,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -961,16 +931,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -978,16 +948,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -995,16 +965,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1012,16 +982,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1029,16 +999,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1046,16 +1016,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1063,16 +1033,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1080,16 +1050,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1097,16 +1067,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1114,16 +1084,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1131,188 +1101,18 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1330,31 +1130,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4C82F1-C55A-43BE-A2DA-0F897E20DF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763A4C35-A331-4F79-8F4D-B76503B14A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="26">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,97 +57,55 @@
     <t>Relatório de Recusas 24.11.2025 a 30.11.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 25/11/2025</t>
-  </si>
-  <si>
-    <t>135362829</t>
-  </si>
-  <si>
-    <t>135370895</t>
-  </si>
-  <si>
-    <t>135418067</t>
-  </si>
-  <si>
-    <t>135431815</t>
-  </si>
-  <si>
-    <t>135475935</t>
-  </si>
-  <si>
-    <t>135469811</t>
-  </si>
-  <si>
-    <t>135475033</t>
-  </si>
-  <si>
-    <t>135365526</t>
-  </si>
-  <si>
-    <t>135466743</t>
-  </si>
-  <si>
-    <t>135487600</t>
-  </si>
-  <si>
-    <t>135470636</t>
-  </si>
-  <si>
-    <t>135491304</t>
-  </si>
-  <si>
-    <t>135493505</t>
-  </si>
-  <si>
-    <t>135464753</t>
-  </si>
-  <si>
-    <t>135490210</t>
-  </si>
-  <si>
-    <t>135423401</t>
-  </si>
-  <si>
-    <t>135513778</t>
-  </si>
-  <si>
-    <t>135371138</t>
-  </si>
-  <si>
-    <t>135422961</t>
-  </si>
-  <si>
-    <t>135465259</t>
-  </si>
-  <si>
-    <t>135384088</t>
-  </si>
-  <si>
-    <t>135380282</t>
-  </si>
-  <si>
-    <t>135424489</t>
-  </si>
-  <si>
-    <t>135421815</t>
-  </si>
-  <si>
-    <t>135427573</t>
-  </si>
-  <si>
-    <t>135443033</t>
-  </si>
-  <si>
-    <t>135497978</t>
-  </si>
-  <si>
-    <t>135440916</t>
-  </si>
-  <si>
-    <t>135442838</t>
-  </si>
-  <si>
-    <t>135460460</t>
+    <t>Relatório de Recusas Santander - 26/11/2025</t>
+  </si>
+  <si>
+    <t>135411282</t>
+  </si>
+  <si>
+    <t>135431683</t>
+  </si>
+  <si>
+    <t>135480068</t>
+  </si>
+  <si>
+    <t>135413293</t>
+  </si>
+  <si>
+    <t>135489165</t>
+  </si>
+  <si>
+    <t>135537702</t>
+  </si>
+  <si>
+    <t>135377794</t>
+  </si>
+  <si>
+    <t>135360568</t>
+  </si>
+  <si>
+    <t>135380046</t>
+  </si>
+  <si>
+    <t>135465358</t>
+  </si>
+  <si>
+    <t>135486931</t>
+  </si>
+  <si>
+    <t>135472368</t>
+  </si>
+  <si>
+    <t>135447654</t>
+  </si>
+  <si>
+    <t>135466143</t>
+  </si>
+  <si>
+    <t>135444405</t>
+  </si>
+  <si>
+    <t>135416666</t>
   </si>
 </sst>
 </file>
@@ -552,7 +510,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -584,7 +542,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135367670</v>
+        <v>135401884</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -875,244 +833,6 @@
         <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1130,31 +850,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15127C2-D24A-4B9A-ABD9-334D207F8D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77329678-4B41-446C-B64F-A00F89EE5DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="45">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,67 +57,112 @@
     <t>Relatório de Recusas 24.11.2025 a 30.11.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 27/11/2025</t>
-  </si>
-  <si>
-    <t>135434074</t>
-  </si>
-  <si>
-    <t>135433573</t>
-  </si>
-  <si>
-    <t>135418972</t>
-  </si>
-  <si>
-    <t>135484086</t>
-  </si>
-  <si>
-    <t>135487946</t>
-  </si>
-  <si>
-    <t>135493049</t>
-  </si>
-  <si>
-    <t>135512518</t>
-  </si>
-  <si>
-    <t>135525374</t>
-  </si>
-  <si>
-    <t>135427218</t>
-  </si>
-  <si>
-    <t>135367051</t>
-  </si>
-  <si>
-    <t>135451165</t>
-  </si>
-  <si>
-    <t>135419502</t>
-  </si>
-  <si>
-    <t>135419605</t>
-  </si>
-  <si>
-    <t>135421535</t>
-  </si>
-  <si>
-    <t>135421899</t>
-  </si>
-  <si>
-    <t>135423885</t>
-  </si>
-  <si>
-    <t>135423988</t>
-  </si>
-  <si>
-    <t>135431196</t>
-  </si>
-  <si>
-    <t>135463294</t>
-  </si>
-  <si>
-    <t>135487561</t>
+    <t>Relatório de Recusas Santander - 28 e 29/11/2025</t>
+  </si>
+  <si>
+    <t>135453413</t>
+  </si>
+  <si>
+    <t>135495417</t>
+  </si>
+  <si>
+    <t>135496890</t>
+  </si>
+  <si>
+    <t>135508446</t>
+  </si>
+  <si>
+    <t>135544316</t>
+  </si>
+  <si>
+    <t>135566474</t>
+  </si>
+  <si>
+    <t>135555363</t>
+  </si>
+  <si>
+    <t>135579863</t>
+  </si>
+  <si>
+    <t>135551990</t>
+  </si>
+  <si>
+    <t>135579646</t>
+  </si>
+  <si>
+    <t>135362848</t>
+  </si>
+  <si>
+    <t>135437329</t>
+  </si>
+  <si>
+    <t>135442855</t>
+  </si>
+  <si>
+    <t>135443192</t>
+  </si>
+  <si>
+    <t>135495623</t>
+  </si>
+  <si>
+    <t>135444073</t>
+  </si>
+  <si>
+    <t>135444264</t>
+  </si>
+  <si>
+    <t>135445469</t>
+  </si>
+  <si>
+    <t>135447755</t>
+  </si>
+  <si>
+    <t>135497474</t>
+  </si>
+  <si>
+    <t>135535136</t>
+  </si>
+  <si>
+    <t>135392070</t>
+  </si>
+  <si>
+    <t>135433556</t>
+  </si>
+  <si>
+    <t>135444774</t>
+  </si>
+  <si>
+    <t>135454453</t>
+  </si>
+  <si>
+    <t>135453985</t>
+  </si>
+  <si>
+    <t>135492232</t>
+  </si>
+  <si>
+    <t>135582251</t>
+  </si>
+  <si>
+    <t>135398051</t>
+  </si>
+  <si>
+    <t>135436941</t>
+  </si>
+  <si>
+    <t>135449994</t>
+  </si>
+  <si>
+    <t>135425867</t>
+  </si>
+  <si>
+    <t>135431023</t>
+  </si>
+  <si>
+    <t>135448363</t>
+  </si>
+  <si>
+    <t>135466244</t>
   </si>
 </sst>
 </file>
@@ -522,7 +567,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -554,7 +599,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135419308</v>
+        <v>135443133</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -913,6 +958,261 @@
         <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77329678-4B41-446C-B64F-A00F89EE5DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8997B8-9C30-436E-9067-F62814F77E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="78">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,115 +54,214 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas 24.11.2025 a 30.11.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 28 e 29/11/2025</t>
-  </si>
-  <si>
-    <t>135453413</t>
-  </si>
-  <si>
-    <t>135495417</t>
-  </si>
-  <si>
-    <t>135496890</t>
-  </si>
-  <si>
-    <t>135508446</t>
-  </si>
-  <si>
-    <t>135544316</t>
-  </si>
-  <si>
-    <t>135566474</t>
-  </si>
-  <si>
-    <t>135555363</t>
-  </si>
-  <si>
-    <t>135579863</t>
-  </si>
-  <si>
-    <t>135551990</t>
-  </si>
-  <si>
-    <t>135579646</t>
-  </si>
-  <si>
-    <t>135362848</t>
-  </si>
-  <si>
-    <t>135437329</t>
-  </si>
-  <si>
-    <t>135442855</t>
-  </si>
-  <si>
-    <t>135443192</t>
-  </si>
-  <si>
-    <t>135495623</t>
-  </si>
-  <si>
-    <t>135444073</t>
-  </si>
-  <si>
-    <t>135444264</t>
-  </si>
-  <si>
-    <t>135445469</t>
-  </si>
-  <si>
-    <t>135447755</t>
-  </si>
-  <si>
-    <t>135497474</t>
-  </si>
-  <si>
-    <t>135535136</t>
-  </si>
-  <si>
-    <t>135392070</t>
-  </si>
-  <si>
-    <t>135433556</t>
-  </si>
-  <si>
-    <t>135444774</t>
-  </si>
-  <si>
-    <t>135454453</t>
-  </si>
-  <si>
-    <t>135453985</t>
-  </si>
-  <si>
-    <t>135492232</t>
-  </si>
-  <si>
-    <t>135582251</t>
-  </si>
-  <si>
-    <t>135398051</t>
-  </si>
-  <si>
-    <t>135436941</t>
-  </si>
-  <si>
-    <t>135449994</t>
-  </si>
-  <si>
-    <t>135425867</t>
-  </si>
-  <si>
-    <t>135431023</t>
-  </si>
-  <si>
-    <t>135448363</t>
-  </si>
-  <si>
-    <t>135466244</t>
+    <t>Relatório de Recusas Santander - 01.12.2025</t>
+  </si>
+  <si>
+    <t>135474812</t>
+  </si>
+  <si>
+    <t>135468066</t>
+  </si>
+  <si>
+    <t>135475160</t>
+  </si>
+  <si>
+    <t>135475293</t>
+  </si>
+  <si>
+    <t>135479583</t>
+  </si>
+  <si>
+    <t>135498971</t>
+  </si>
+  <si>
+    <t>135493667</t>
+  </si>
+  <si>
+    <t>135514119</t>
+  </si>
+  <si>
+    <t>135512202</t>
+  </si>
+  <si>
+    <t>135522219</t>
+  </si>
+  <si>
+    <t>135523239</t>
+  </si>
+  <si>
+    <t>135522967</t>
+  </si>
+  <si>
+    <t>135492497</t>
+  </si>
+  <si>
+    <t>135478449</t>
+  </si>
+  <si>
+    <t>135529810</t>
+  </si>
+  <si>
+    <t>135534132</t>
+  </si>
+  <si>
+    <t>135544398</t>
+  </si>
+  <si>
+    <t>135546544</t>
+  </si>
+  <si>
+    <t>135533868</t>
+  </si>
+  <si>
+    <t>135535321</t>
+  </si>
+  <si>
+    <t>135533044</t>
+  </si>
+  <si>
+    <t>135546431</t>
+  </si>
+  <si>
+    <t>135545842</t>
+  </si>
+  <si>
+    <t>135529148</t>
+  </si>
+  <si>
+    <t>135536166</t>
+  </si>
+  <si>
+    <t>135557269</t>
+  </si>
+  <si>
+    <t>135494206</t>
+  </si>
+  <si>
+    <t>135460854</t>
+  </si>
+  <si>
+    <t>135485806</t>
+  </si>
+  <si>
+    <t>135560592</t>
+  </si>
+  <si>
+    <t>135579805</t>
+  </si>
+  <si>
+    <t>135581568</t>
+  </si>
+  <si>
+    <t>135574821</t>
+  </si>
+  <si>
+    <t>135555960</t>
+  </si>
+  <si>
+    <t>135547329</t>
+  </si>
+  <si>
+    <t>135595402</t>
+  </si>
+  <si>
+    <t>135491263</t>
+  </si>
+  <si>
+    <t>135516843</t>
+  </si>
+  <si>
+    <t>135472699</t>
+  </si>
+  <si>
+    <t>135461886</t>
+  </si>
+  <si>
+    <t>135632322</t>
+  </si>
+  <si>
+    <t>135458498</t>
+  </si>
+  <si>
+    <t>135491743</t>
+  </si>
+  <si>
+    <t>135464003</t>
+  </si>
+  <si>
+    <t>135464315</t>
+  </si>
+  <si>
+    <t>135465557</t>
+  </si>
+  <si>
+    <t>135467783</t>
+  </si>
+  <si>
+    <t>135468824</t>
+  </si>
+  <si>
+    <t>135469361</t>
+  </si>
+  <si>
+    <t>135474843</t>
+  </si>
+  <si>
+    <t>135475874</t>
+  </si>
+  <si>
+    <t>135476431</t>
+  </si>
+  <si>
+    <t>135477461</t>
+  </si>
+  <si>
+    <t>135485394</t>
+  </si>
+  <si>
+    <t>135488494</t>
+  </si>
+  <si>
+    <t>135490205</t>
+  </si>
+  <si>
+    <t>135491118</t>
+  </si>
+  <si>
+    <t>135491355</t>
+  </si>
+  <si>
+    <t>135491432</t>
+  </si>
+  <si>
+    <t>135491465</t>
+  </si>
+  <si>
+    <t>135491559</t>
+  </si>
+  <si>
+    <t>135491650</t>
+  </si>
+  <si>
+    <t>135493212</t>
+  </si>
+  <si>
+    <t>135495564</t>
+  </si>
+  <si>
+    <t>135497503</t>
+  </si>
+  <si>
+    <t>135500468</t>
+  </si>
+  <si>
+    <t>135501247</t>
+  </si>
+  <si>
+    <t>135501543</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 01.12.2025 a 08.12.2025</t>
   </si>
 </sst>
 </file>
@@ -567,7 +666,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -599,16 +698,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135443133</v>
+        <v>135474140</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -617,16 +716,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -635,16 +734,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -653,16 +752,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -671,16 +770,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -689,16 +788,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -707,16 +806,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -725,16 +824,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -742,16 +841,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -759,16 +858,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -776,16 +875,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -793,16 +892,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -810,16 +909,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -827,16 +926,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -844,16 +943,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -861,16 +960,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -878,16 +977,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -895,16 +994,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -912,16 +1011,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -929,16 +1028,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -946,16 +1045,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -963,16 +1062,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -980,16 +1079,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -997,16 +1096,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1014,16 +1113,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1031,16 +1130,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1048,16 +1147,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1065,16 +1164,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1082,16 +1181,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1099,16 +1198,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1116,16 +1215,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1133,16 +1232,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1150,16 +1249,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1167,16 +1266,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1184,16 +1283,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1201,18 +1300,579 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1230,31 +1890,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8997B8-9C30-436E-9067-F62814F77E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E73CA5E-D91E-497B-B6FB-94FF402550DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="59">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,214 +54,157 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 01.12.2025</t>
-  </si>
-  <si>
-    <t>135474812</t>
-  </si>
-  <si>
-    <t>135468066</t>
-  </si>
-  <si>
-    <t>135475160</t>
-  </si>
-  <si>
-    <t>135475293</t>
-  </si>
-  <si>
-    <t>135479583</t>
-  </si>
-  <si>
-    <t>135498971</t>
-  </si>
-  <si>
-    <t>135493667</t>
-  </si>
-  <si>
-    <t>135514119</t>
-  </si>
-  <si>
-    <t>135512202</t>
-  </si>
-  <si>
-    <t>135522219</t>
-  </si>
-  <si>
-    <t>135523239</t>
-  </si>
-  <si>
-    <t>135522967</t>
-  </si>
-  <si>
-    <t>135492497</t>
-  </si>
-  <si>
-    <t>135478449</t>
-  </si>
-  <si>
-    <t>135529810</t>
-  </si>
-  <si>
-    <t>135534132</t>
-  </si>
-  <si>
-    <t>135544398</t>
-  </si>
-  <si>
-    <t>135546544</t>
-  </si>
-  <si>
-    <t>135533868</t>
-  </si>
-  <si>
-    <t>135535321</t>
-  </si>
-  <si>
-    <t>135533044</t>
-  </si>
-  <si>
-    <t>135546431</t>
-  </si>
-  <si>
-    <t>135545842</t>
-  </si>
-  <si>
-    <t>135529148</t>
-  </si>
-  <si>
-    <t>135536166</t>
-  </si>
-  <si>
-    <t>135557269</t>
-  </si>
-  <si>
-    <t>135494206</t>
-  </si>
-  <si>
-    <t>135460854</t>
-  </si>
-  <si>
-    <t>135485806</t>
-  </si>
-  <si>
-    <t>135560592</t>
-  </si>
-  <si>
-    <t>135579805</t>
-  </si>
-  <si>
-    <t>135581568</t>
-  </si>
-  <si>
-    <t>135574821</t>
-  </si>
-  <si>
-    <t>135555960</t>
-  </si>
-  <si>
-    <t>135547329</t>
-  </si>
-  <si>
-    <t>135595402</t>
-  </si>
-  <si>
-    <t>135491263</t>
-  </si>
-  <si>
-    <t>135516843</t>
-  </si>
-  <si>
-    <t>135472699</t>
-  </si>
-  <si>
-    <t>135461886</t>
-  </si>
-  <si>
-    <t>135632322</t>
-  </si>
-  <si>
-    <t>135458498</t>
-  </si>
-  <si>
-    <t>135491743</t>
-  </si>
-  <si>
-    <t>135464003</t>
-  </si>
-  <si>
-    <t>135464315</t>
-  </si>
-  <si>
-    <t>135465557</t>
-  </si>
-  <si>
-    <t>135467783</t>
-  </si>
-  <si>
-    <t>135468824</t>
-  </si>
-  <si>
-    <t>135469361</t>
-  </si>
-  <si>
-    <t>135474843</t>
-  </si>
-  <si>
-    <t>135475874</t>
-  </si>
-  <si>
-    <t>135476431</t>
-  </si>
-  <si>
-    <t>135477461</t>
-  </si>
-  <si>
-    <t>135485394</t>
-  </si>
-  <si>
-    <t>135488494</t>
-  </si>
-  <si>
-    <t>135490205</t>
-  </si>
-  <si>
-    <t>135491118</t>
-  </si>
-  <si>
-    <t>135491355</t>
-  </si>
-  <si>
-    <t>135491432</t>
-  </si>
-  <si>
-    <t>135491465</t>
-  </si>
-  <si>
-    <t>135491559</t>
-  </si>
-  <si>
-    <t>135491650</t>
-  </si>
-  <si>
-    <t>135493212</t>
-  </si>
-  <si>
-    <t>135495564</t>
-  </si>
-  <si>
-    <t>135497503</t>
-  </si>
-  <si>
-    <t>135500468</t>
-  </si>
-  <si>
-    <t>135501247</t>
-  </si>
-  <si>
-    <t>135501543</t>
-  </si>
-  <si>
     <t>Relatório de Recusas 01.12.2025 a 08.12.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 02.12.2025</t>
+  </si>
+  <si>
+    <t>135476128</t>
+  </si>
+  <si>
+    <t>135474963</t>
+  </si>
+  <si>
+    <t>135522118</t>
+  </si>
+  <si>
+    <t>135533831</t>
+  </si>
+  <si>
+    <t>135538973</t>
+  </si>
+  <si>
+    <t>135517415</t>
+  </si>
+  <si>
+    <t>135547880</t>
+  </si>
+  <si>
+    <t>135559942</t>
+  </si>
+  <si>
+    <t>135567017</t>
+  </si>
+  <si>
+    <t>135573429</t>
+  </si>
+  <si>
+    <t>135555249</t>
+  </si>
+  <si>
+    <t>135559287</t>
+  </si>
+  <si>
+    <t>135579972</t>
+  </si>
+  <si>
+    <t>135583928</t>
+  </si>
+  <si>
+    <t>135578989</t>
+  </si>
+  <si>
+    <t>135606960</t>
+  </si>
+  <si>
+    <t>135574132</t>
+  </si>
+  <si>
+    <t>135552819</t>
+  </si>
+  <si>
+    <t>135622491</t>
+  </si>
+  <si>
+    <t>135633604</t>
+  </si>
+  <si>
+    <t>135636611</t>
+  </si>
+  <si>
+    <t>135424805</t>
+  </si>
+  <si>
+    <t>135461082</t>
+  </si>
+  <si>
+    <t>135467713</t>
+  </si>
+  <si>
+    <t>135476188</t>
+  </si>
+  <si>
+    <t>135551705</t>
+  </si>
+  <si>
+    <t>135558261</t>
+  </si>
+  <si>
+    <t>135561802</t>
+  </si>
+  <si>
+    <t>135565511</t>
+  </si>
+  <si>
+    <t>135521668</t>
+  </si>
+  <si>
+    <t>135567034</t>
+  </si>
+  <si>
+    <t>135559199</t>
+  </si>
+  <si>
+    <t>135556960</t>
+  </si>
+  <si>
+    <t>135547182</t>
+  </si>
+  <si>
+    <t>135530271</t>
+  </si>
+  <si>
+    <t>135519157</t>
+  </si>
+  <si>
+    <t>135561675</t>
+  </si>
+  <si>
+    <t>135559785</t>
+  </si>
+  <si>
+    <t>135459425</t>
+  </si>
+  <si>
+    <t>135462249</t>
+  </si>
+  <si>
+    <t>135464234</t>
+  </si>
+  <si>
+    <t>135465443</t>
+  </si>
+  <si>
+    <t>135467241</t>
+  </si>
+  <si>
+    <t>135468654</t>
+  </si>
+  <si>
+    <t>135471047</t>
+  </si>
+  <si>
+    <t>135471126</t>
+  </si>
+  <si>
+    <t>135473171</t>
+  </si>
+  <si>
+    <t>135474791</t>
+  </si>
+  <si>
+    <t>135475190</t>
   </si>
 </sst>
 </file>
@@ -666,7 +609,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -698,16 +641,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135474140</v>
+        <v>135472314</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -716,16 +659,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -734,16 +677,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -752,16 +695,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -770,16 +713,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -788,16 +731,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -806,16 +749,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -824,16 +767,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -841,16 +784,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -858,16 +801,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -875,16 +818,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -892,16 +835,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -909,16 +852,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -926,16 +869,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -943,16 +886,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -960,16 +903,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -977,16 +920,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -994,16 +937,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1011,16 +954,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1028,16 +971,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1045,16 +988,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1062,16 +1005,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1079,16 +1022,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1096,16 +1039,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1113,16 +1056,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1130,16 +1073,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1147,16 +1090,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1164,16 +1107,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1181,16 +1124,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1198,16 +1141,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1215,16 +1158,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1232,16 +1175,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1249,16 +1192,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1266,16 +1209,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1283,16 +1226,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1300,16 +1243,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1317,16 +1260,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1334,16 +1277,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1351,16 +1294,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1368,16 +1311,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1385,16 +1328,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1402,16 +1345,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1419,16 +1362,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1436,16 +1379,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1453,16 +1396,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1470,16 +1413,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1487,16 +1430,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1504,16 +1447,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1521,16 +1464,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1538,341 +1481,18 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E70" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1890,31 +1510,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E73CA5E-D91E-497B-B6FB-94FF402550DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A099CB14-357D-4FC2-AF25-DF44C0E56E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,154 +57,79 @@
     <t>Relatório de Recusas 01.12.2025 a 08.12.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 02.12.2025</t>
-  </si>
-  <si>
-    <t>135476128</t>
-  </si>
-  <si>
-    <t>135474963</t>
-  </si>
-  <si>
-    <t>135522118</t>
-  </si>
-  <si>
-    <t>135533831</t>
-  </si>
-  <si>
-    <t>135538973</t>
-  </si>
-  <si>
-    <t>135517415</t>
-  </si>
-  <si>
-    <t>135547880</t>
-  </si>
-  <si>
-    <t>135559942</t>
-  </si>
-  <si>
-    <t>135567017</t>
-  </si>
-  <si>
-    <t>135573429</t>
-  </si>
-  <si>
-    <t>135555249</t>
-  </si>
-  <si>
-    <t>135559287</t>
-  </si>
-  <si>
-    <t>135579972</t>
-  </si>
-  <si>
-    <t>135583928</t>
-  </si>
-  <si>
-    <t>135578989</t>
-  </si>
-  <si>
-    <t>135606960</t>
-  </si>
-  <si>
-    <t>135574132</t>
-  </si>
-  <si>
-    <t>135552819</t>
-  </si>
-  <si>
-    <t>135622491</t>
-  </si>
-  <si>
-    <t>135633604</t>
-  </si>
-  <si>
-    <t>135636611</t>
-  </si>
-  <si>
-    <t>135424805</t>
-  </si>
-  <si>
-    <t>135461082</t>
-  </si>
-  <si>
-    <t>135467713</t>
-  </si>
-  <si>
-    <t>135476188</t>
-  </si>
-  <si>
-    <t>135551705</t>
-  </si>
-  <si>
-    <t>135558261</t>
-  </si>
-  <si>
-    <t>135561802</t>
-  </si>
-  <si>
-    <t>135565511</t>
-  </si>
-  <si>
-    <t>135521668</t>
-  </si>
-  <si>
-    <t>135567034</t>
-  </si>
-  <si>
-    <t>135559199</t>
-  </si>
-  <si>
-    <t>135556960</t>
-  </si>
-  <si>
-    <t>135547182</t>
-  </si>
-  <si>
-    <t>135530271</t>
-  </si>
-  <si>
-    <t>135519157</t>
-  </si>
-  <si>
-    <t>135561675</t>
-  </si>
-  <si>
-    <t>135559785</t>
-  </si>
-  <si>
-    <t>135459425</t>
-  </si>
-  <si>
-    <t>135462249</t>
-  </si>
-  <si>
-    <t>135464234</t>
-  </si>
-  <si>
-    <t>135465443</t>
-  </si>
-  <si>
-    <t>135467241</t>
-  </si>
-  <si>
-    <t>135468654</t>
-  </si>
-  <si>
-    <t>135471047</t>
-  </si>
-  <si>
-    <t>135471126</t>
-  </si>
-  <si>
-    <t>135473171</t>
-  </si>
-  <si>
-    <t>135474791</t>
-  </si>
-  <si>
-    <t>135475190</t>
+    <t>Relatório de Recusas Santander - 03.12.2025</t>
+  </si>
+  <si>
+    <t>135558402</t>
+  </si>
+  <si>
+    <t>135582657</t>
+  </si>
+  <si>
+    <t>135576695</t>
+  </si>
+  <si>
+    <t>135573735</t>
+  </si>
+  <si>
+    <t>135577253</t>
+  </si>
+  <si>
+    <t>135585027</t>
+  </si>
+  <si>
+    <t>135600339</t>
+  </si>
+  <si>
+    <t>135609801</t>
+  </si>
+  <si>
+    <t>135596142</t>
+  </si>
+  <si>
+    <t>135615125</t>
+  </si>
+  <si>
+    <t>135631884</t>
+  </si>
+  <si>
+    <t>135642942</t>
+  </si>
+  <si>
+    <t>135655094</t>
+  </si>
+  <si>
+    <t>135580945</t>
+  </si>
+  <si>
+    <t>135581020</t>
+  </si>
+  <si>
+    <t>135551622</t>
+  </si>
+  <si>
+    <t>135662360</t>
+  </si>
+  <si>
+    <t>135477306</t>
+  </si>
+  <si>
+    <t>135581856</t>
+  </si>
+  <si>
+    <t>135487438</t>
+  </si>
+  <si>
+    <t>135561219</t>
+  </si>
+  <si>
+    <t>135492844</t>
+  </si>
+  <si>
+    <t>135544155</t>
+  </si>
+  <si>
+    <t>135581566</t>
   </si>
 </sst>
 </file>
@@ -609,7 +534,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -641,7 +566,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135472314</v>
+        <v>135533519</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1068,431 +993,6 @@
         <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1510,31 +1010,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A099CB14-357D-4FC2-AF25-DF44C0E56E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E853D8BA-2BD6-48FB-9A7D-A5DFFEABC92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="38">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,79 +57,91 @@
     <t>Relatório de Recusas 01.12.2025 a 08.12.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 03.12.2025</t>
-  </si>
-  <si>
-    <t>135558402</t>
-  </si>
-  <si>
-    <t>135582657</t>
-  </si>
-  <si>
-    <t>135576695</t>
-  </si>
-  <si>
-    <t>135573735</t>
-  </si>
-  <si>
-    <t>135577253</t>
-  </si>
-  <si>
-    <t>135585027</t>
-  </si>
-  <si>
-    <t>135600339</t>
-  </si>
-  <si>
-    <t>135609801</t>
-  </si>
-  <si>
-    <t>135596142</t>
-  </si>
-  <si>
-    <t>135615125</t>
-  </si>
-  <si>
-    <t>135631884</t>
-  </si>
-  <si>
-    <t>135642942</t>
-  </si>
-  <si>
-    <t>135655094</t>
-  </si>
-  <si>
-    <t>135580945</t>
-  </si>
-  <si>
-    <t>135581020</t>
-  </si>
-  <si>
-    <t>135551622</t>
-  </si>
-  <si>
-    <t>135662360</t>
-  </si>
-  <si>
-    <t>135477306</t>
-  </si>
-  <si>
-    <t>135581856</t>
-  </si>
-  <si>
-    <t>135487438</t>
-  </si>
-  <si>
-    <t>135561219</t>
-  </si>
-  <si>
-    <t>135492844</t>
-  </si>
-  <si>
-    <t>135544155</t>
-  </si>
-  <si>
-    <t>135581566</t>
+    <t>Relatório de Recusas Santander - 04.12.2025</t>
+  </si>
+  <si>
+    <t>135508040</t>
+  </si>
+  <si>
+    <t>135518927</t>
+  </si>
+  <si>
+    <t>135574859</t>
+  </si>
+  <si>
+    <t>135602448</t>
+  </si>
+  <si>
+    <t>135607689</t>
+  </si>
+  <si>
+    <t>135616350</t>
+  </si>
+  <si>
+    <t>135603102</t>
+  </si>
+  <si>
+    <t>135617144</t>
+  </si>
+  <si>
+    <t>135608598</t>
+  </si>
+  <si>
+    <t>135613210</t>
+  </si>
+  <si>
+    <t>135616894</t>
+  </si>
+  <si>
+    <t>135597411</t>
+  </si>
+  <si>
+    <t>135616932</t>
+  </si>
+  <si>
+    <t>135607242</t>
+  </si>
+  <si>
+    <t>135608569</t>
+  </si>
+  <si>
+    <t>135604720</t>
+  </si>
+  <si>
+    <t>135658305</t>
+  </si>
+  <si>
+    <t>135681487</t>
+  </si>
+  <si>
+    <t>135492193</t>
+  </si>
+  <si>
+    <t>135510893</t>
+  </si>
+  <si>
+    <t>135508650</t>
+  </si>
+  <si>
+    <t>135509673</t>
+  </si>
+  <si>
+    <t>135515765</t>
+  </si>
+  <si>
+    <t>135517113</t>
+  </si>
+  <si>
+    <t>135517549</t>
+  </si>
+  <si>
+    <t>135520409</t>
+  </si>
+  <si>
+    <t>135520535</t>
+  </si>
+  <si>
+    <t>135522141</t>
   </si>
 </sst>
 </file>
@@ -534,7 +546,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -566,7 +578,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135533519</v>
+        <v>135498261</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -993,6 +1005,74 @@
         <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1010,31 +1090,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E853D8BA-2BD6-48FB-9A7D-A5DFFEABC92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E3E2EC-C5B8-4D77-951D-99A2A109FC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,91 +57,97 @@
     <t>Relatório de Recusas 01.12.2025 a 08.12.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 04.12.2025</t>
-  </si>
-  <si>
-    <t>135508040</t>
-  </si>
-  <si>
-    <t>135518927</t>
-  </si>
-  <si>
-    <t>135574859</t>
-  </si>
-  <si>
-    <t>135602448</t>
-  </si>
-  <si>
-    <t>135607689</t>
-  </si>
-  <si>
-    <t>135616350</t>
-  </si>
-  <si>
-    <t>135603102</t>
-  </si>
-  <si>
-    <t>135617144</t>
-  </si>
-  <si>
-    <t>135608598</t>
-  </si>
-  <si>
-    <t>135613210</t>
-  </si>
-  <si>
-    <t>135616894</t>
-  </si>
-  <si>
-    <t>135597411</t>
-  </si>
-  <si>
-    <t>135616932</t>
-  </si>
-  <si>
-    <t>135607242</t>
-  </si>
-  <si>
-    <t>135608569</t>
-  </si>
-  <si>
-    <t>135604720</t>
-  </si>
-  <si>
-    <t>135658305</t>
-  </si>
-  <si>
-    <t>135681487</t>
-  </si>
-  <si>
-    <t>135492193</t>
-  </si>
-  <si>
-    <t>135510893</t>
-  </si>
-  <si>
-    <t>135508650</t>
-  </si>
-  <si>
-    <t>135509673</t>
-  </si>
-  <si>
-    <t>135515765</t>
-  </si>
-  <si>
-    <t>135517113</t>
-  </si>
-  <si>
-    <t>135517549</t>
-  </si>
-  <si>
-    <t>135520409</t>
-  </si>
-  <si>
-    <t>135520535</t>
-  </si>
-  <si>
-    <t>135522141</t>
+    <t>Relatório de Recusas Santander - 05 e 06.12.2025</t>
+  </si>
+  <si>
+    <t>135517944</t>
+  </si>
+  <si>
+    <t>135535217</t>
+  </si>
+  <si>
+    <t>135538097</t>
+  </si>
+  <si>
+    <t>135546055</t>
+  </si>
+  <si>
+    <t>135535236</t>
+  </si>
+  <si>
+    <t>135518797</t>
+  </si>
+  <si>
+    <t>135588685</t>
+  </si>
+  <si>
+    <t>135638249</t>
+  </si>
+  <si>
+    <t>135633267</t>
+  </si>
+  <si>
+    <t>135650005</t>
+  </si>
+  <si>
+    <t>135661305</t>
+  </si>
+  <si>
+    <t>135678326</t>
+  </si>
+  <si>
+    <t>135517068</t>
+  </si>
+  <si>
+    <t>135530099</t>
+  </si>
+  <si>
+    <t>135530182</t>
+  </si>
+  <si>
+    <t>135533249</t>
+  </si>
+  <si>
+    <t>135534438</t>
+  </si>
+  <si>
+    <t>135534712</t>
+  </si>
+  <si>
+    <t>135535116</t>
+  </si>
+  <si>
+    <t>135535598</t>
+  </si>
+  <si>
+    <t>135536496</t>
+  </si>
+  <si>
+    <t>135536526</t>
+  </si>
+  <si>
+    <t>135538263</t>
+  </si>
+  <si>
+    <t>135545659</t>
+  </si>
+  <si>
+    <t>135547529</t>
+  </si>
+  <si>
+    <t>135548051</t>
+  </si>
+  <si>
+    <t>135488590</t>
+  </si>
+  <si>
+    <t>135522548</t>
+  </si>
+  <si>
+    <t>135530449</t>
+  </si>
+  <si>
+    <t>135548004</t>
   </si>
 </sst>
 </file>
@@ -546,7 +552,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -578,7 +584,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135498261</v>
+        <v>135506321</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1073,6 +1079,40 @@
         <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1090,31 +1130,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E3E2EC-C5B8-4D77-951D-99A2A109FC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9B2B4E-7CD2-4E95-B447-8BA54395EF63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="1230" windowWidth="15375" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,97 +57,76 @@
     <t>Relatório de Recusas 01.12.2025 a 08.12.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 05 e 06.12.2025</t>
-  </si>
-  <si>
-    <t>135517944</t>
-  </si>
-  <si>
-    <t>135535217</t>
-  </si>
-  <si>
-    <t>135538097</t>
-  </si>
-  <si>
-    <t>135546055</t>
-  </si>
-  <si>
-    <t>135535236</t>
-  </si>
-  <si>
-    <t>135518797</t>
-  </si>
-  <si>
-    <t>135588685</t>
-  </si>
-  <si>
-    <t>135638249</t>
-  </si>
-  <si>
-    <t>135633267</t>
-  </si>
-  <si>
-    <t>135650005</t>
-  </si>
-  <si>
-    <t>135661305</t>
-  </si>
-  <si>
-    <t>135678326</t>
-  </si>
-  <si>
-    <t>135517068</t>
-  </si>
-  <si>
-    <t>135530099</t>
-  </si>
-  <si>
-    <t>135530182</t>
-  </si>
-  <si>
-    <t>135533249</t>
-  </si>
-  <si>
-    <t>135534438</t>
-  </si>
-  <si>
-    <t>135534712</t>
-  </si>
-  <si>
-    <t>135535116</t>
-  </si>
-  <si>
-    <t>135535598</t>
-  </si>
-  <si>
-    <t>135536496</t>
-  </si>
-  <si>
-    <t>135536526</t>
-  </si>
-  <si>
-    <t>135538263</t>
-  </si>
-  <si>
-    <t>135545659</t>
-  </si>
-  <si>
-    <t>135547529</t>
-  </si>
-  <si>
-    <t>135548051</t>
-  </si>
-  <si>
-    <t>135488590</t>
-  </si>
-  <si>
-    <t>135522548</t>
-  </si>
-  <si>
-    <t>135530449</t>
-  </si>
-  <si>
-    <t>135548004</t>
+    <t>Relatório de Recusas Santander - 08.12.2025</t>
+  </si>
+  <si>
+    <t>135675052</t>
+  </si>
+  <si>
+    <t>135728160</t>
+  </si>
+  <si>
+    <t>135730475</t>
+  </si>
+  <si>
+    <t>135740065</t>
+  </si>
+  <si>
+    <t>135654069</t>
+  </si>
+  <si>
+    <t>135576150</t>
+  </si>
+  <si>
+    <t>135622007</t>
+  </si>
+  <si>
+    <t>135609744</t>
+  </si>
+  <si>
+    <t>135611907</t>
+  </si>
+  <si>
+    <t>135670333</t>
+  </si>
+  <si>
+    <t>135569060</t>
+  </si>
+  <si>
+    <t>135635401</t>
+  </si>
+  <si>
+    <t>135591228</t>
+  </si>
+  <si>
+    <t>135580003</t>
+  </si>
+  <si>
+    <t>135601184</t>
+  </si>
+  <si>
+    <t>135653926</t>
+  </si>
+  <si>
+    <t>135633453</t>
+  </si>
+  <si>
+    <t>135637074</t>
+  </si>
+  <si>
+    <t>135653660</t>
+  </si>
+  <si>
+    <t>135659491</t>
+  </si>
+  <si>
+    <t>135643003</t>
+  </si>
+  <si>
+    <t>135637294</t>
+  </si>
+  <si>
+    <t>135633111</t>
   </si>
 </sst>
 </file>
@@ -552,7 +531,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -584,7 +563,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135506321</v>
+        <v>135655680</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -994,125 +973,6 @@
         <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1130,31 +990,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3FECDC-227B-4610-83E3-89E6717810FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C55F5E-1848-40AF-8B03-C276D25E2887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,130 +54,85 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 28/10/2025</t>
-  </si>
-  <si>
-    <t>134954593</t>
-  </si>
-  <si>
-    <t>134954580</t>
-  </si>
-  <si>
-    <t>134953873</t>
-  </si>
-  <si>
-    <t>134976368</t>
-  </si>
-  <si>
-    <t>135000174</t>
-  </si>
-  <si>
-    <t>134949643</t>
-  </si>
-  <si>
-    <t>135009736</t>
-  </si>
-  <si>
-    <t>135011662</t>
-  </si>
-  <si>
-    <t>135016864</t>
-  </si>
-  <si>
-    <t>135040056</t>
-  </si>
-  <si>
-    <t>135040123</t>
-  </si>
-  <si>
-    <t>134945073</t>
-  </si>
-  <si>
-    <t>135056992</t>
-  </si>
-  <si>
-    <t>135067409</t>
-  </si>
-  <si>
-    <t>134945001</t>
-  </si>
-  <si>
-    <t>135078174</t>
-  </si>
-  <si>
-    <t>135100764</t>
-  </si>
-  <si>
-    <t>135068300</t>
-  </si>
-  <si>
-    <t>135111265</t>
-  </si>
-  <si>
-    <t>134969357</t>
-  </si>
-  <si>
-    <t>134940138</t>
-  </si>
-  <si>
-    <t>134940600</t>
-  </si>
-  <si>
-    <t>134942677</t>
-  </si>
-  <si>
-    <t>134943358</t>
-  </si>
-  <si>
-    <t>134943983</t>
-  </si>
-  <si>
-    <t>134944838</t>
-  </si>
-  <si>
-    <t>134944891</t>
-  </si>
-  <si>
-    <t>134945877</t>
-  </si>
-  <si>
-    <t>134948611</t>
-  </si>
-  <si>
-    <t>134949601</t>
-  </si>
-  <si>
-    <t>134953644</t>
-  </si>
-  <si>
-    <t>134955203</t>
-  </si>
-  <si>
-    <t>134955467</t>
-  </si>
-  <si>
-    <t>135042534</t>
-  </si>
-  <si>
-    <t>135069992</t>
-  </si>
-  <si>
-    <t>134981862</t>
-  </si>
-  <si>
-    <t>135057013</t>
-  </si>
-  <si>
-    <t>135014593</t>
-  </si>
-  <si>
-    <t>135018905</t>
-  </si>
-  <si>
-    <t>135132162</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 27.10.2025 a 02.11.2025</t>
+    <t>Relatório de Recusas Santander - 19 e 20.12.2025</t>
+  </si>
+  <si>
+    <t>135684503</t>
+  </si>
+  <si>
+    <t>135739166</t>
+  </si>
+  <si>
+    <t>135778337</t>
+  </si>
+  <si>
+    <t>135766819</t>
+  </si>
+  <si>
+    <t>135812151</t>
+  </si>
+  <si>
+    <t>135823672</t>
+  </si>
+  <si>
+    <t>135841920</t>
+  </si>
+  <si>
+    <t>135892469</t>
+  </si>
+  <si>
+    <t>135774607</t>
+  </si>
+  <si>
+    <t>135921089</t>
+  </si>
+  <si>
+    <t>135933634</t>
+  </si>
+  <si>
+    <t>135686031</t>
+  </si>
+  <si>
+    <t>135739165</t>
+  </si>
+  <si>
+    <t>135833562</t>
+  </si>
+  <si>
+    <t>135760750</t>
+  </si>
+  <si>
+    <t>135762192</t>
+  </si>
+  <si>
+    <t>135767139</t>
+  </si>
+  <si>
+    <t>135767429</t>
+  </si>
+  <si>
+    <t>135829887</t>
+  </si>
+  <si>
+    <t>135773164</t>
+  </si>
+  <si>
+    <t>135778040</t>
+  </si>
+  <si>
+    <t>135775679</t>
+  </si>
+  <si>
+    <t>135735276</t>
+  </si>
+  <si>
+    <t>135744670</t>
+  </si>
+  <si>
+    <t>135777498</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 17.12.2025 a 24.12.2025</t>
   </si>
 </sst>
 </file>
@@ -582,7 +537,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -614,7 +569,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134942483</v>
+        <v>135894726</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -623,7 +578,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -641,7 +596,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -659,7 +614,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -677,7 +632,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -695,7 +650,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -713,7 +668,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -731,7 +686,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -749,7 +704,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -767,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -785,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -803,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -821,7 +776,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -839,7 +794,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -857,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -875,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -893,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -911,7 +866,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -929,7 +884,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -947,7 +902,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -965,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -983,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1001,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1019,7 +974,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1037,7 +992,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1055,7 +1010,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1073,268 +1028,12 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F27"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1350,31 +1049,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C55F5E-1848-40AF-8B03-C276D25E2887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E851263-075C-4342-B00F-668494AA3D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="52">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,85 +54,136 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 19 e 20.12.2025</t>
-  </si>
-  <si>
-    <t>135684503</t>
-  </si>
-  <si>
-    <t>135739166</t>
-  </si>
-  <si>
-    <t>135778337</t>
-  </si>
-  <si>
-    <t>135766819</t>
-  </si>
-  <si>
-    <t>135812151</t>
-  </si>
-  <si>
-    <t>135823672</t>
-  </si>
-  <si>
-    <t>135841920</t>
-  </si>
-  <si>
-    <t>135892469</t>
-  </si>
-  <si>
-    <t>135774607</t>
-  </si>
-  <si>
-    <t>135921089</t>
-  </si>
-  <si>
-    <t>135933634</t>
-  </si>
-  <si>
-    <t>135686031</t>
-  </si>
-  <si>
-    <t>135739165</t>
-  </si>
-  <si>
-    <t>135833562</t>
-  </si>
-  <si>
-    <t>135760750</t>
-  </si>
-  <si>
-    <t>135762192</t>
-  </si>
-  <si>
-    <t>135767139</t>
-  </si>
-  <si>
-    <t>135767429</t>
-  </si>
-  <si>
-    <t>135829887</t>
-  </si>
-  <si>
-    <t>135773164</t>
-  </si>
-  <si>
-    <t>135778040</t>
-  </si>
-  <si>
-    <t>135775679</t>
-  </si>
-  <si>
-    <t>135735276</t>
-  </si>
-  <si>
-    <t>135744670</t>
-  </si>
-  <si>
-    <t>135777498</t>
-  </si>
-  <si>
     <t>Relatório de Recusas 17.12.2025 a 24.12.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 22.12.2025</t>
+  </si>
+  <si>
+    <t>135812315</t>
+  </si>
+  <si>
+    <t>135811117</t>
+  </si>
+  <si>
+    <t>135862092</t>
+  </si>
+  <si>
+    <t>135866772</t>
+  </si>
+  <si>
+    <t>135871496</t>
+  </si>
+  <si>
+    <t>135871623</t>
+  </si>
+  <si>
+    <t>135752257</t>
+  </si>
+  <si>
+    <t>135868110</t>
+  </si>
+  <si>
+    <t>135861776</t>
+  </si>
+  <si>
+    <t>135888226</t>
+  </si>
+  <si>
+    <t>135875849</t>
+  </si>
+  <si>
+    <t>135886383</t>
+  </si>
+  <si>
+    <t>135890986</t>
+  </si>
+  <si>
+    <t>135894834</t>
+  </si>
+  <si>
+    <t>135894378</t>
+  </si>
+  <si>
+    <t>135911447</t>
+  </si>
+  <si>
+    <t>135881322</t>
+  </si>
+  <si>
+    <t>135896317</t>
+  </si>
+  <si>
+    <t>135912171</t>
+  </si>
+  <si>
+    <t>135924259</t>
+  </si>
+  <si>
+    <t>135894649</t>
+  </si>
+  <si>
+    <t>135931820</t>
+  </si>
+  <si>
+    <t>135925147</t>
+  </si>
+  <si>
+    <t>135873601</t>
+  </si>
+  <si>
+    <t>135926970</t>
+  </si>
+  <si>
+    <t>135942800</t>
+  </si>
+  <si>
+    <t>135750474</t>
+  </si>
+  <si>
+    <t>135762373</t>
+  </si>
+  <si>
+    <t>135859177</t>
+  </si>
+  <si>
+    <t>135777470</t>
+  </si>
+  <si>
+    <t>135787457</t>
+  </si>
+  <si>
+    <t>135790032</t>
+  </si>
+  <si>
+    <t>135790996</t>
+  </si>
+  <si>
+    <t>135792794</t>
+  </si>
+  <si>
+    <t>135798684</t>
+  </si>
+  <si>
+    <t>135800468</t>
+  </si>
+  <si>
+    <t>135800568</t>
+  </si>
+  <si>
+    <t>135806463</t>
+  </si>
+  <si>
+    <t>135806730</t>
+  </si>
+  <si>
+    <t>135807335</t>
+  </si>
+  <si>
+    <t>135809115</t>
+  </si>
+  <si>
+    <t>135809266</t>
   </si>
 </sst>
 </file>
@@ -537,7 +588,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -569,16 +620,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135894726</v>
+        <v>135808481</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -587,16 +638,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -605,16 +656,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -623,16 +674,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -641,16 +692,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -659,16 +710,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -677,16 +728,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -695,16 +746,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -713,16 +764,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -731,16 +782,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -749,16 +800,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -767,16 +818,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -785,16 +836,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -803,16 +854,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -821,16 +872,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -839,16 +890,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -857,16 +908,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -875,16 +926,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -893,16 +944,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -911,16 +962,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -929,16 +980,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -947,16 +998,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -965,16 +1016,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -983,16 +1034,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1001,16 +1052,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1019,21 +1070,310 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F27"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1049,31 +1389,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E851263-075C-4342-B00F-668494AA3D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE86682-5A1F-49DE-96AF-01167E704ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="112">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,136 +54,316 @@
     <t>1070</t>
   </si>
   <si>
+    <t>Recusas Santander 25/12/2025</t>
+  </si>
+  <si>
+    <t>135800415</t>
+  </si>
+  <si>
+    <t>135834039</t>
+  </si>
+  <si>
+    <t>135830606</t>
+  </si>
+  <si>
+    <t>135824642</t>
+  </si>
+  <si>
+    <t>135833835</t>
+  </si>
+  <si>
+    <t>135824707</t>
+  </si>
+  <si>
+    <t>135835104</t>
+  </si>
+  <si>
+    <t>135826631</t>
+  </si>
+  <si>
+    <t>135839826</t>
+  </si>
+  <si>
+    <t>135843387</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 25.12.2025 a 31.12.2025</t>
+  </si>
+  <si>
+    <t>135800368</t>
+  </si>
+  <si>
+    <t>Recusas Santander 23 e 24/12/2025</t>
+  </si>
+  <si>
+    <t>135804374</t>
+  </si>
+  <si>
+    <t>135822352</t>
+  </si>
+  <si>
+    <t>135804209</t>
+  </si>
+  <si>
+    <t>135822468</t>
+  </si>
+  <si>
+    <t>135815199</t>
+  </si>
+  <si>
+    <t>135817939</t>
+  </si>
+  <si>
+    <t>135836190</t>
+  </si>
+  <si>
+    <t>135844482</t>
+  </si>
+  <si>
+    <t>135828853</t>
+  </si>
+  <si>
+    <t>135843502</t>
+  </si>
+  <si>
+    <t>135845344</t>
+  </si>
+  <si>
+    <t>135862426</t>
+  </si>
+  <si>
+    <t>135894268</t>
+  </si>
+  <si>
+    <t>135899287</t>
+  </si>
+  <si>
+    <t>135908714</t>
+  </si>
+  <si>
+    <t>135836307</t>
+  </si>
+  <si>
+    <t>135818945</t>
+  </si>
+  <si>
+    <t>135805722</t>
+  </si>
+  <si>
+    <t>135921411</t>
+  </si>
+  <si>
+    <t>135924328</t>
+  </si>
+  <si>
+    <t>135935530</t>
+  </si>
+  <si>
+    <t>135960647</t>
+  </si>
+  <si>
+    <t>135945091</t>
+  </si>
+  <si>
+    <t>135965205</t>
+  </si>
+  <si>
+    <t>135979980</t>
+  </si>
+  <si>
+    <t>135980242</t>
+  </si>
+  <si>
+    <t>135988240</t>
+  </si>
+  <si>
+    <t>135814543</t>
+  </si>
+  <si>
+    <t>135816530</t>
+  </si>
+  <si>
+    <t>135817976</t>
+  </si>
+  <si>
+    <t>135821428</t>
+  </si>
+  <si>
+    <t>135827714</t>
+  </si>
+  <si>
+    <t>135829029</t>
+  </si>
+  <si>
+    <t>135830164</t>
+  </si>
+  <si>
+    <t>135830883</t>
+  </si>
+  <si>
+    <t>135831939</t>
+  </si>
+  <si>
+    <t>135833533</t>
+  </si>
+  <si>
+    <t>135834818</t>
+  </si>
+  <si>
+    <t>135838192</t>
+  </si>
+  <si>
+    <t>135842597</t>
+  </si>
+  <si>
+    <t>135842945</t>
+  </si>
+  <si>
+    <t>135843465</t>
+  </si>
+  <si>
+    <t>135904139</t>
+  </si>
+  <si>
+    <t>135793523</t>
+  </si>
+  <si>
+    <t>135790142</t>
+  </si>
+  <si>
+    <t>135879826</t>
+  </si>
+  <si>
+    <t>135871670</t>
+  </si>
+  <si>
+    <t>135861676</t>
+  </si>
+  <si>
+    <t>135885250</t>
+  </si>
+  <si>
+    <t>135791615</t>
+  </si>
+  <si>
+    <t>135795351</t>
+  </si>
+  <si>
+    <t>135796461</t>
+  </si>
+  <si>
+    <t>135807959</t>
+  </si>
+  <si>
+    <t>135809645</t>
+  </si>
+  <si>
+    <t>135866286</t>
+  </si>
+  <si>
+    <t>136000391</t>
+  </si>
+  <si>
+    <t>135836302</t>
+  </si>
+  <si>
+    <t>135839419</t>
+  </si>
+  <si>
+    <t>135843092</t>
+  </si>
+  <si>
+    <t>135843995</t>
+  </si>
+  <si>
+    <t>135867237</t>
+  </si>
+  <si>
+    <t>135780061</t>
+  </si>
+  <si>
+    <t>135815367</t>
+  </si>
+  <si>
+    <t>135855577</t>
+  </si>
+  <si>
+    <t>135891902</t>
+  </si>
+  <si>
+    <t>135886513</t>
+  </si>
+  <si>
+    <t>135840558</t>
+  </si>
+  <si>
+    <t>135920677</t>
+  </si>
+  <si>
+    <t>135923012</t>
+  </si>
+  <si>
+    <t>135933003</t>
+  </si>
+  <si>
+    <t>135934388</t>
+  </si>
+  <si>
+    <t>135938263</t>
+  </si>
+  <si>
+    <t>135935964</t>
+  </si>
+  <si>
+    <t>135937920</t>
+  </si>
+  <si>
+    <t>135959691</t>
+  </si>
+  <si>
+    <t>135928783</t>
+  </si>
+  <si>
+    <t>135968030</t>
+  </si>
+  <si>
+    <t>135977998</t>
+  </si>
+  <si>
+    <t>135998362</t>
+  </si>
+  <si>
+    <t>135997220</t>
+  </si>
+  <si>
+    <t>135925497</t>
+  </si>
+  <si>
+    <t>135818220</t>
+  </si>
+  <si>
+    <t>135777294</t>
+  </si>
+  <si>
+    <t>135808265</t>
+  </si>
+  <si>
+    <t>135925662</t>
+  </si>
+  <si>
+    <t>135908428</t>
+  </si>
+  <si>
+    <t>135902709</t>
+  </si>
+  <si>
+    <t>135932515</t>
+  </si>
+  <si>
+    <t>135932745</t>
+  </si>
+  <si>
     <t>Relatório de Recusas 17.12.2025 a 24.12.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 22.12.2025</t>
-  </si>
-  <si>
-    <t>135812315</t>
-  </si>
-  <si>
-    <t>135811117</t>
-  </si>
-  <si>
-    <t>135862092</t>
-  </si>
-  <si>
-    <t>135866772</t>
-  </si>
-  <si>
-    <t>135871496</t>
-  </si>
-  <si>
-    <t>135871623</t>
-  </si>
-  <si>
-    <t>135752257</t>
-  </si>
-  <si>
-    <t>135868110</t>
-  </si>
-  <si>
-    <t>135861776</t>
-  </si>
-  <si>
-    <t>135888226</t>
-  </si>
-  <si>
-    <t>135875849</t>
-  </si>
-  <si>
-    <t>135886383</t>
-  </si>
-  <si>
-    <t>135890986</t>
-  </si>
-  <si>
-    <t>135894834</t>
-  </si>
-  <si>
-    <t>135894378</t>
-  </si>
-  <si>
-    <t>135911447</t>
-  </si>
-  <si>
-    <t>135881322</t>
-  </si>
-  <si>
-    <t>135896317</t>
-  </si>
-  <si>
-    <t>135912171</t>
-  </si>
-  <si>
-    <t>135924259</t>
-  </si>
-  <si>
-    <t>135894649</t>
-  </si>
-  <si>
-    <t>135931820</t>
-  </si>
-  <si>
-    <t>135925147</t>
-  </si>
-  <si>
-    <t>135873601</t>
-  </si>
-  <si>
-    <t>135926970</t>
-  </si>
-  <si>
-    <t>135942800</t>
-  </si>
-  <si>
-    <t>135750474</t>
-  </si>
-  <si>
-    <t>135762373</t>
-  </si>
-  <si>
-    <t>135859177</t>
-  </si>
-  <si>
-    <t>135777470</t>
-  </si>
-  <si>
-    <t>135787457</t>
-  </si>
-  <si>
-    <t>135790032</t>
-  </si>
-  <si>
-    <t>135790996</t>
-  </si>
-  <si>
-    <t>135792794</t>
-  </si>
-  <si>
-    <t>135798684</t>
-  </si>
-  <si>
-    <t>135800468</t>
-  </si>
-  <si>
-    <t>135800568</t>
-  </si>
-  <si>
-    <t>135806463</t>
-  </si>
-  <si>
-    <t>135806730</t>
-  </si>
-  <si>
-    <t>135807335</t>
-  </si>
-  <si>
-    <t>135809115</t>
-  </si>
-  <si>
-    <t>135809266</t>
   </si>
 </sst>
 </file>
@@ -588,7 +768,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -620,16 +800,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135808481</v>
+        <v>135784618</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -638,16 +818,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -656,16 +836,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -674,16 +854,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -692,16 +872,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -710,16 +890,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -728,16 +908,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -746,16 +926,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -764,16 +944,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -782,16 +962,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -800,16 +980,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -824,10 +1004,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -836,16 +1016,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -854,16 +1034,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -872,16 +1052,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -890,16 +1070,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -908,16 +1088,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -926,16 +1106,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -944,16 +1124,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -962,16 +1142,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -980,16 +1160,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -998,16 +1178,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1016,16 +1196,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1034,16 +1214,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1052,16 +1232,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1070,16 +1250,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1088,16 +1268,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1105,16 +1285,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1122,16 +1302,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1139,16 +1319,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1156,16 +1336,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1173,16 +1353,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1190,16 +1370,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1207,16 +1387,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1224,16 +1404,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1241,16 +1421,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1258,16 +1438,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1275,16 +1455,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1292,16 +1472,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1309,16 +1489,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1326,16 +1506,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1343,16 +1523,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1360,18 +1540,1004 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE86682-5A1F-49DE-96AF-01167E704ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D65D6F-215E-4CAA-A7EC-6070912CDAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="76">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,316 +54,208 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Recusas Santander 25/12/2025</t>
-  </si>
-  <si>
-    <t>135800415</t>
-  </si>
-  <si>
-    <t>135834039</t>
-  </si>
-  <si>
-    <t>135830606</t>
-  </si>
-  <si>
-    <t>135824642</t>
-  </si>
-  <si>
-    <t>135833835</t>
-  </si>
-  <si>
-    <t>135824707</t>
-  </si>
-  <si>
-    <t>135835104</t>
-  </si>
-  <si>
-    <t>135826631</t>
-  </si>
-  <si>
-    <t>135839826</t>
-  </si>
-  <si>
-    <t>135843387</t>
-  </si>
-  <si>
     <t>Relatório de Recusas 25.12.2025 a 31.12.2025</t>
   </si>
   <si>
-    <t>135800368</t>
-  </si>
-  <si>
-    <t>Recusas Santander 23 e 24/12/2025</t>
-  </si>
-  <si>
-    <t>135804374</t>
-  </si>
-  <si>
-    <t>135822352</t>
-  </si>
-  <si>
-    <t>135804209</t>
-  </si>
-  <si>
-    <t>135822468</t>
-  </si>
-  <si>
-    <t>135815199</t>
-  </si>
-  <si>
-    <t>135817939</t>
-  </si>
-  <si>
-    <t>135836190</t>
-  </si>
-  <si>
-    <t>135844482</t>
-  </si>
-  <si>
-    <t>135828853</t>
-  </si>
-  <si>
-    <t>135843502</t>
-  </si>
-  <si>
-    <t>135845344</t>
-  </si>
-  <si>
-    <t>135862426</t>
-  </si>
-  <si>
-    <t>135894268</t>
-  </si>
-  <si>
-    <t>135899287</t>
-  </si>
-  <si>
-    <t>135908714</t>
-  </si>
-  <si>
-    <t>135836307</t>
-  </si>
-  <si>
-    <t>135818945</t>
-  </si>
-  <si>
-    <t>135805722</t>
-  </si>
-  <si>
-    <t>135921411</t>
-  </si>
-  <si>
-    <t>135924328</t>
-  </si>
-  <si>
-    <t>135935530</t>
-  </si>
-  <si>
-    <t>135960647</t>
-  </si>
-  <si>
-    <t>135945091</t>
-  </si>
-  <si>
-    <t>135965205</t>
-  </si>
-  <si>
-    <t>135979980</t>
-  </si>
-  <si>
-    <t>135980242</t>
-  </si>
-  <si>
-    <t>135988240</t>
-  </si>
-  <si>
-    <t>135814543</t>
-  </si>
-  <si>
-    <t>135816530</t>
-  </si>
-  <si>
-    <t>135817976</t>
-  </si>
-  <si>
-    <t>135821428</t>
-  </si>
-  <si>
-    <t>135827714</t>
-  </si>
-  <si>
-    <t>135829029</t>
-  </si>
-  <si>
-    <t>135830164</t>
-  </si>
-  <si>
-    <t>135830883</t>
-  </si>
-  <si>
-    <t>135831939</t>
-  </si>
-  <si>
-    <t>135833533</t>
-  </si>
-  <si>
-    <t>135834818</t>
-  </si>
-  <si>
-    <t>135838192</t>
-  </si>
-  <si>
-    <t>135842597</t>
-  </si>
-  <si>
-    <t>135842945</t>
-  </si>
-  <si>
-    <t>135843465</t>
-  </si>
-  <si>
-    <t>135904139</t>
-  </si>
-  <si>
-    <t>135793523</t>
-  </si>
-  <si>
-    <t>135790142</t>
-  </si>
-  <si>
-    <t>135879826</t>
-  </si>
-  <si>
-    <t>135871670</t>
-  </si>
-  <si>
-    <t>135861676</t>
-  </si>
-  <si>
-    <t>135885250</t>
-  </si>
-  <si>
-    <t>135791615</t>
-  </si>
-  <si>
-    <t>135795351</t>
-  </si>
-  <si>
-    <t>135796461</t>
-  </si>
-  <si>
-    <t>135807959</t>
-  </si>
-  <si>
-    <t>135809645</t>
-  </si>
-  <si>
-    <t>135866286</t>
-  </si>
-  <si>
-    <t>136000391</t>
-  </si>
-  <si>
-    <t>135836302</t>
-  </si>
-  <si>
-    <t>135839419</t>
-  </si>
-  <si>
-    <t>135843092</t>
-  </si>
-  <si>
-    <t>135843995</t>
-  </si>
-  <si>
-    <t>135867237</t>
-  </si>
-  <si>
-    <t>135780061</t>
-  </si>
-  <si>
-    <t>135815367</t>
-  </si>
-  <si>
-    <t>135855577</t>
-  </si>
-  <si>
-    <t>135891902</t>
-  </si>
-  <si>
-    <t>135886513</t>
-  </si>
-  <si>
-    <t>135840558</t>
-  </si>
-  <si>
-    <t>135920677</t>
-  </si>
-  <si>
-    <t>135923012</t>
-  </si>
-  <si>
-    <t>135933003</t>
-  </si>
-  <si>
-    <t>135934388</t>
-  </si>
-  <si>
-    <t>135938263</t>
-  </si>
-  <si>
-    <t>135935964</t>
-  </si>
-  <si>
-    <t>135937920</t>
-  </si>
-  <si>
-    <t>135959691</t>
-  </si>
-  <si>
-    <t>135928783</t>
-  </si>
-  <si>
-    <t>135968030</t>
-  </si>
-  <si>
-    <t>135977998</t>
-  </si>
-  <si>
-    <t>135998362</t>
-  </si>
-  <si>
-    <t>135997220</t>
-  </si>
-  <si>
-    <t>135925497</t>
-  </si>
-  <si>
-    <t>135818220</t>
-  </si>
-  <si>
-    <t>135777294</t>
-  </si>
-  <si>
-    <t>135808265</t>
-  </si>
-  <si>
-    <t>135925662</t>
-  </si>
-  <si>
-    <t>135908428</t>
-  </si>
-  <si>
-    <t>135902709</t>
-  </si>
-  <si>
-    <t>135932515</t>
-  </si>
-  <si>
-    <t>135932745</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 17.12.2025 a 24.12.2025</t>
+    <t>Relatório de Recusas Santander - 26 e 27.12.2025</t>
+  </si>
+  <si>
+    <t>135862723</t>
+  </si>
+  <si>
+    <t>135881310</t>
+  </si>
+  <si>
+    <t>135894661</t>
+  </si>
+  <si>
+    <t>135890943</t>
+  </si>
+  <si>
+    <t>135894746</t>
+  </si>
+  <si>
+    <t>135890905</t>
+  </si>
+  <si>
+    <t>135926129</t>
+  </si>
+  <si>
+    <t>135931101</t>
+  </si>
+  <si>
+    <t>135934684</t>
+  </si>
+  <si>
+    <t>135946093</t>
+  </si>
+  <si>
+    <t>135947426</t>
+  </si>
+  <si>
+    <t>135957031</t>
+  </si>
+  <si>
+    <t>135959927</t>
+  </si>
+  <si>
+    <t>135962512</t>
+  </si>
+  <si>
+    <t>135943050</t>
+  </si>
+  <si>
+    <t>135965183</t>
+  </si>
+  <si>
+    <t>135981139</t>
+  </si>
+  <si>
+    <t>135999500</t>
+  </si>
+  <si>
+    <t>135948847</t>
+  </si>
+  <si>
+    <t>135867298</t>
+  </si>
+  <si>
+    <t>135997309</t>
+  </si>
+  <si>
+    <t>135889906</t>
+  </si>
+  <si>
+    <t>136014551</t>
+  </si>
+  <si>
+    <t>135862967</t>
+  </si>
+  <si>
+    <t>135904895</t>
+  </si>
+  <si>
+    <t>135894780</t>
+  </si>
+  <si>
+    <t>135905418</t>
+  </si>
+  <si>
+    <t>135850238</t>
+  </si>
+  <si>
+    <t>135850447</t>
+  </si>
+  <si>
+    <t>135856612</t>
+  </si>
+  <si>
+    <t>135858579</t>
+  </si>
+  <si>
+    <t>135858945</t>
+  </si>
+  <si>
+    <t>135860950</t>
+  </si>
+  <si>
+    <t>135869585</t>
+  </si>
+  <si>
+    <t>135870412</t>
+  </si>
+  <si>
+    <t>135871053</t>
+  </si>
+  <si>
+    <t>135871182</t>
+  </si>
+  <si>
+    <t>135871644</t>
+  </si>
+  <si>
+    <t>135882829</t>
+  </si>
+  <si>
+    <t>135882939</t>
+  </si>
+  <si>
+    <t>135893655</t>
+  </si>
+  <si>
+    <t>135894568</t>
+  </si>
+  <si>
+    <t>135894812</t>
+  </si>
+  <si>
+    <t>135839979</t>
+  </si>
+  <si>
+    <t>135842234</t>
+  </si>
+  <si>
+    <t>135831039</t>
+  </si>
+  <si>
+    <t>135894528</t>
+  </si>
+  <si>
+    <t>135894612</t>
+  </si>
+  <si>
+    <t>135844432</t>
+  </si>
+  <si>
+    <t>135830974</t>
+  </si>
+  <si>
+    <t>135833489</t>
+  </si>
+  <si>
+    <t>135847358</t>
+  </si>
+  <si>
+    <t>135850413</t>
+  </si>
+  <si>
+    <t>135838942</t>
+  </si>
+  <si>
+    <t>135841301</t>
+  </si>
+  <si>
+    <t>135842472</t>
+  </si>
+  <si>
+    <t>135845145</t>
+  </si>
+  <si>
+    <t>135845723</t>
+  </si>
+  <si>
+    <t>135850663</t>
+  </si>
+  <si>
+    <t>135856766</t>
+  </si>
+  <si>
+    <t>135867779</t>
+  </si>
+  <si>
+    <t>135866951</t>
+  </si>
+  <si>
+    <t>135889937</t>
+  </si>
+  <si>
+    <t>135890169</t>
+  </si>
+  <si>
+    <t>135894682</t>
+  </si>
+  <si>
+    <t>135894739</t>
   </si>
 </sst>
 </file>
@@ -768,7 +660,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -800,16 +692,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135784618</v>
+        <v>135836003</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -818,16 +710,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -836,16 +728,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -854,16 +746,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -872,16 +764,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -890,16 +782,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -908,16 +800,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -926,16 +818,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -944,16 +836,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -962,16 +854,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -980,16 +872,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -1004,10 +896,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -1016,16 +908,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -1034,16 +926,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -1052,16 +944,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -1070,16 +962,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1088,16 +980,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1106,16 +998,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1124,16 +1016,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1142,16 +1034,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1160,16 +1052,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1178,16 +1070,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1196,16 +1088,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1214,16 +1106,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1232,16 +1124,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1250,16 +1142,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1268,16 +1160,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1285,16 +1177,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1302,16 +1194,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1319,16 +1211,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1336,16 +1228,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1353,16 +1245,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1370,16 +1262,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1387,16 +1279,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1404,16 +1296,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1421,16 +1313,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1438,16 +1330,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1455,16 +1347,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1472,16 +1364,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1489,16 +1381,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1506,16 +1398,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1523,16 +1415,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1540,16 +1432,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1557,16 +1449,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1574,16 +1466,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1591,16 +1483,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1608,16 +1500,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1625,16 +1517,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1642,16 +1534,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1659,16 +1551,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1676,16 +1568,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1693,16 +1585,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1710,16 +1602,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1727,16 +1619,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1744,16 +1636,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1761,16 +1653,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
@@ -1778,16 +1670,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
@@ -1795,16 +1687,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
@@ -1812,16 +1704,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
@@ -1829,16 +1721,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
@@ -1846,16 +1738,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
@@ -1863,16 +1755,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
@@ -1880,16 +1772,16 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>6</v>
@@ -1897,16 +1789,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>6</v>
@@ -1914,16 +1806,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
@@ -1931,16 +1823,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>6</v>
@@ -1948,596 +1840,18 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E102" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2555,31 +1869,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D65D6F-215E-4CAA-A7EC-6070912CDAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815BA044-F018-4D25-A30B-D27365E004B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="69">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,205 +57,184 @@
     <t>Relatório de Recusas 25.12.2025 a 31.12.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 26 e 27.12.2025</t>
-  </si>
-  <si>
-    <t>135862723</t>
-  </si>
-  <si>
-    <t>135881310</t>
-  </si>
-  <si>
-    <t>135894661</t>
-  </si>
-  <si>
-    <t>135890943</t>
-  </si>
-  <si>
-    <t>135894746</t>
-  </si>
-  <si>
-    <t>135890905</t>
-  </si>
-  <si>
-    <t>135926129</t>
-  </si>
-  <si>
-    <t>135931101</t>
-  </si>
-  <si>
-    <t>135934684</t>
-  </si>
-  <si>
-    <t>135946093</t>
-  </si>
-  <si>
-    <t>135947426</t>
-  </si>
-  <si>
-    <t>135957031</t>
-  </si>
-  <si>
-    <t>135959927</t>
-  </si>
-  <si>
-    <t>135962512</t>
-  </si>
-  <si>
-    <t>135943050</t>
-  </si>
-  <si>
-    <t>135965183</t>
-  </si>
-  <si>
-    <t>135981139</t>
-  </si>
-  <si>
-    <t>135999500</t>
-  </si>
-  <si>
-    <t>135948847</t>
-  </si>
-  <si>
-    <t>135867298</t>
-  </si>
-  <si>
-    <t>135997309</t>
-  </si>
-  <si>
-    <t>135889906</t>
-  </si>
-  <si>
-    <t>136014551</t>
-  </si>
-  <si>
-    <t>135862967</t>
-  </si>
-  <si>
-    <t>135904895</t>
-  </si>
-  <si>
-    <t>135894780</t>
-  </si>
-  <si>
-    <t>135905418</t>
-  </si>
-  <si>
-    <t>135850238</t>
-  </si>
-  <si>
-    <t>135850447</t>
-  </si>
-  <si>
-    <t>135856612</t>
-  </si>
-  <si>
-    <t>135858579</t>
-  </si>
-  <si>
-    <t>135858945</t>
-  </si>
-  <si>
-    <t>135860950</t>
-  </si>
-  <si>
-    <t>135869585</t>
-  </si>
-  <si>
-    <t>135870412</t>
-  </si>
-  <si>
-    <t>135871053</t>
-  </si>
-  <si>
-    <t>135871182</t>
-  </si>
-  <si>
-    <t>135871644</t>
-  </si>
-  <si>
-    <t>135882829</t>
-  </si>
-  <si>
-    <t>135882939</t>
-  </si>
-  <si>
-    <t>135893655</t>
-  </si>
-  <si>
-    <t>135894568</t>
-  </si>
-  <si>
-    <t>135894812</t>
-  </si>
-  <si>
-    <t>135839979</t>
-  </si>
-  <si>
-    <t>135842234</t>
-  </si>
-  <si>
-    <t>135831039</t>
-  </si>
-  <si>
-    <t>135894528</t>
-  </si>
-  <si>
-    <t>135894612</t>
-  </si>
-  <si>
-    <t>135844432</t>
-  </si>
-  <si>
-    <t>135830974</t>
-  </si>
-  <si>
-    <t>135833489</t>
-  </si>
-  <si>
-    <t>135847358</t>
-  </si>
-  <si>
-    <t>135850413</t>
-  </si>
-  <si>
-    <t>135838942</t>
-  </si>
-  <si>
-    <t>135841301</t>
-  </si>
-  <si>
-    <t>135842472</t>
-  </si>
-  <si>
-    <t>135845145</t>
-  </si>
-  <si>
-    <t>135845723</t>
-  </si>
-  <si>
-    <t>135850663</t>
-  </si>
-  <si>
-    <t>135856766</t>
-  </si>
-  <si>
-    <t>135867779</t>
-  </si>
-  <si>
-    <t>135866951</t>
-  </si>
-  <si>
-    <t>135889937</t>
-  </si>
-  <si>
-    <t>135890169</t>
-  </si>
-  <si>
-    <t>135894682</t>
-  </si>
-  <si>
-    <t>135894739</t>
+    <t>Relatório de Recusas Santander - 29.12.2025</t>
+  </si>
+  <si>
+    <t>135893008</t>
+  </si>
+  <si>
+    <t>135892634</t>
+  </si>
+  <si>
+    <t>135932726</t>
+  </si>
+  <si>
+    <t>135935783</t>
+  </si>
+  <si>
+    <t>135977973</t>
+  </si>
+  <si>
+    <t>135983642</t>
+  </si>
+  <si>
+    <t>135981266</t>
+  </si>
+  <si>
+    <t>135972557</t>
+  </si>
+  <si>
+    <t>135975633</t>
+  </si>
+  <si>
+    <t>135977303</t>
+  </si>
+  <si>
+    <t>135978453</t>
+  </si>
+  <si>
+    <t>136000488</t>
+  </si>
+  <si>
+    <t>135999708</t>
+  </si>
+  <si>
+    <t>136002033</t>
+  </si>
+  <si>
+    <t>136007243</t>
+  </si>
+  <si>
+    <t>136002808</t>
+  </si>
+  <si>
+    <t>136000282</t>
+  </si>
+  <si>
+    <t>136001402</t>
+  </si>
+  <si>
+    <t>135998825</t>
+  </si>
+  <si>
+    <t>136003368</t>
+  </si>
+  <si>
+    <t>136007359</t>
+  </si>
+  <si>
+    <t>135900634</t>
+  </si>
+  <si>
+    <t>135900915</t>
+  </si>
+  <si>
+    <t>135903254</t>
+  </si>
+  <si>
+    <t>135905150</t>
+  </si>
+  <si>
+    <t>135905154</t>
+  </si>
+  <si>
+    <t>135909463</t>
+  </si>
+  <si>
+    <t>135910007</t>
+  </si>
+  <si>
+    <t>135911283</t>
+  </si>
+  <si>
+    <t>135986958</t>
+  </si>
+  <si>
+    <t>135891935</t>
+  </si>
+  <si>
+    <t>135919490</t>
+  </si>
+  <si>
+    <t>135921396</t>
+  </si>
+  <si>
+    <t>135921473</t>
+  </si>
+  <si>
+    <t>135924586</t>
+  </si>
+  <si>
+    <t>135925814</t>
+  </si>
+  <si>
+    <t>135928666</t>
+  </si>
+  <si>
+    <t>135931553</t>
+  </si>
+  <si>
+    <t>135932491</t>
+  </si>
+  <si>
+    <t>135933982</t>
+  </si>
+  <si>
+    <t>135934519</t>
+  </si>
+  <si>
+    <t>135938117</t>
+  </si>
+  <si>
+    <t>135943216</t>
+  </si>
+  <si>
+    <t>135944058</t>
+  </si>
+  <si>
+    <t>135948256</t>
+  </si>
+  <si>
+    <t>135948444</t>
+  </si>
+  <si>
+    <t>135949979</t>
+  </si>
+  <si>
+    <t>135949991</t>
+  </si>
+  <si>
+    <t>135951435</t>
+  </si>
+  <si>
+    <t>135951470</t>
+  </si>
+  <si>
+    <t>135951822</t>
+  </si>
+  <si>
+    <t>135953416</t>
+  </si>
+  <si>
+    <t>135959334</t>
+  </si>
+  <si>
+    <t>135959678</t>
+  </si>
+  <si>
+    <t>135960584</t>
+  </si>
+  <si>
+    <t>135961901</t>
+  </si>
+  <si>
+    <t>135962543</t>
+  </si>
+  <si>
+    <t>135976357</t>
+  </si>
+  <si>
+    <t>135980265</t>
   </si>
 </sst>
 </file>
@@ -660,7 +639,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -692,7 +671,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135836003</v>
+        <v>135871482</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1733,125 +1712,6 @@
         <v>8</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E68" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1869,31 +1729,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815BA044-F018-4D25-A30B-D27365E004B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C373E6A6-9D43-4DD5-ACFE-5EDCB4618E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="29">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,184 +57,64 @@
     <t>Relatório de Recusas 25.12.2025 a 31.12.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 29.12.2025</t>
-  </si>
-  <si>
-    <t>135893008</t>
-  </si>
-  <si>
-    <t>135892634</t>
-  </si>
-  <si>
-    <t>135932726</t>
-  </si>
-  <si>
-    <t>135935783</t>
-  </si>
-  <si>
-    <t>135977973</t>
-  </si>
-  <si>
-    <t>135983642</t>
-  </si>
-  <si>
-    <t>135981266</t>
-  </si>
-  <si>
-    <t>135972557</t>
-  </si>
-  <si>
-    <t>135975633</t>
-  </si>
-  <si>
-    <t>135977303</t>
-  </si>
-  <si>
-    <t>135978453</t>
-  </si>
-  <si>
-    <t>136000488</t>
-  </si>
-  <si>
-    <t>135999708</t>
-  </si>
-  <si>
-    <t>136002033</t>
-  </si>
-  <si>
-    <t>136007243</t>
-  </si>
-  <si>
-    <t>136002808</t>
-  </si>
-  <si>
-    <t>136000282</t>
-  </si>
-  <si>
-    <t>136001402</t>
-  </si>
-  <si>
-    <t>135998825</t>
-  </si>
-  <si>
-    <t>136003368</t>
-  </si>
-  <si>
-    <t>136007359</t>
-  </si>
-  <si>
-    <t>135900634</t>
-  </si>
-  <si>
-    <t>135900915</t>
-  </si>
-  <si>
-    <t>135903254</t>
-  </si>
-  <si>
-    <t>135905150</t>
-  </si>
-  <si>
-    <t>135905154</t>
-  </si>
-  <si>
-    <t>135909463</t>
-  </si>
-  <si>
-    <t>135910007</t>
-  </si>
-  <si>
-    <t>135911283</t>
-  </si>
-  <si>
-    <t>135986958</t>
-  </si>
-  <si>
-    <t>135891935</t>
-  </si>
-  <si>
-    <t>135919490</t>
-  </si>
-  <si>
-    <t>135921396</t>
-  </si>
-  <si>
-    <t>135921473</t>
-  </si>
-  <si>
-    <t>135924586</t>
-  </si>
-  <si>
-    <t>135925814</t>
-  </si>
-  <si>
-    <t>135928666</t>
-  </si>
-  <si>
-    <t>135931553</t>
-  </si>
-  <si>
-    <t>135932491</t>
-  </si>
-  <si>
-    <t>135933982</t>
-  </si>
-  <si>
-    <t>135934519</t>
-  </si>
-  <si>
-    <t>135938117</t>
-  </si>
-  <si>
-    <t>135943216</t>
-  </si>
-  <si>
-    <t>135944058</t>
-  </si>
-  <si>
-    <t>135948256</t>
-  </si>
-  <si>
-    <t>135948444</t>
-  </si>
-  <si>
-    <t>135949979</t>
-  </si>
-  <si>
-    <t>135949991</t>
-  </si>
-  <si>
-    <t>135951435</t>
-  </si>
-  <si>
-    <t>135951470</t>
-  </si>
-  <si>
-    <t>135951822</t>
-  </si>
-  <si>
-    <t>135953416</t>
-  </si>
-  <si>
-    <t>135959334</t>
-  </si>
-  <si>
-    <t>135959678</t>
-  </si>
-  <si>
-    <t>135960584</t>
-  </si>
-  <si>
-    <t>135961901</t>
-  </si>
-  <si>
-    <t>135962543</t>
-  </si>
-  <si>
-    <t>135976357</t>
-  </si>
-  <si>
-    <t>135980265</t>
+    <t>Relatório de Recusas Santander - 30 e 31.12.2025</t>
+  </si>
+  <si>
+    <t>135965212</t>
+  </si>
+  <si>
+    <t>135984847</t>
+  </si>
+  <si>
+    <t>135998768</t>
+  </si>
+  <si>
+    <t>136008653</t>
+  </si>
+  <si>
+    <t>136002462</t>
+  </si>
+  <si>
+    <t>135996761</t>
+  </si>
+  <si>
+    <t>136008062</t>
+  </si>
+  <si>
+    <t>135974989</t>
+  </si>
+  <si>
+    <t>136046389</t>
+  </si>
+  <si>
+    <t>136047874</t>
+  </si>
+  <si>
+    <t>136039676</t>
+  </si>
+  <si>
+    <t>135999204</t>
+  </si>
+  <si>
+    <t>135976722</t>
+  </si>
+  <si>
+    <t>136012034</t>
+  </si>
+  <si>
+    <t>136012471</t>
+  </si>
+  <si>
+    <t>135969408</t>
+  </si>
+  <si>
+    <t>135987613</t>
+  </si>
+  <si>
+    <t>135923203</t>
+  </si>
+  <si>
+    <t>135930466</t>
   </si>
 </sst>
 </file>
@@ -639,7 +519,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -671,7 +551,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135871482</v>
+        <v>135965207</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1030,15 +910,6 @@
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
       </c>
@@ -1048,15 +919,6 @@
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="D23" s="2" t="s">
         <v>8</v>
       </c>
@@ -1066,15 +928,6 @@
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="D24" s="2" t="s">
         <v>8</v>
       </c>
@@ -1084,15 +937,6 @@
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="D25" s="2" t="s">
         <v>8</v>
       </c>
@@ -1100,620 +944,6 @@
         <v>6</v>
       </c>
       <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1729,31 +959,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C373E6A6-9D43-4DD5-ACFE-5EDCB4618E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C74652B-B381-4511-8E02-21FB8F8510E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="76">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,67 +54,208 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas 25.12.2025 a 31.12.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 30 e 31.12.2025</t>
-  </si>
-  <si>
-    <t>135965212</t>
-  </si>
-  <si>
-    <t>135984847</t>
-  </si>
-  <si>
-    <t>135998768</t>
-  </si>
-  <si>
-    <t>136008653</t>
-  </si>
-  <si>
-    <t>136002462</t>
-  </si>
-  <si>
-    <t>135996761</t>
-  </si>
-  <si>
-    <t>136008062</t>
-  </si>
-  <si>
-    <t>135974989</t>
-  </si>
-  <si>
-    <t>136046389</t>
-  </si>
-  <si>
-    <t>136047874</t>
-  </si>
-  <si>
-    <t>136039676</t>
-  </si>
-  <si>
-    <t>135999204</t>
-  </si>
-  <si>
-    <t>135976722</t>
-  </si>
-  <si>
-    <t>136012034</t>
-  </si>
-  <si>
-    <t>136012471</t>
-  </si>
-  <si>
-    <t>135969408</t>
-  </si>
-  <si>
-    <t>135987613</t>
-  </si>
-  <si>
-    <t>135923203</t>
-  </si>
-  <si>
-    <t>135930466</t>
+    <t>Relatório de Recusas Santander - 02 e 03.01.2026</t>
+  </si>
+  <si>
+    <t>135975610</t>
+  </si>
+  <si>
+    <t>135984577</t>
+  </si>
+  <si>
+    <t>135984816</t>
+  </si>
+  <si>
+    <t>135972751</t>
+  </si>
+  <si>
+    <t>135981658</t>
+  </si>
+  <si>
+    <t>135983816</t>
+  </si>
+  <si>
+    <t>136027593</t>
+  </si>
+  <si>
+    <t>136021428</t>
+  </si>
+  <si>
+    <t>136033846</t>
+  </si>
+  <si>
+    <t>136029574</t>
+  </si>
+  <si>
+    <t>136027238</t>
+  </si>
+  <si>
+    <t>136008550</t>
+  </si>
+  <si>
+    <t>136035360</t>
+  </si>
+  <si>
+    <t>136043205</t>
+  </si>
+  <si>
+    <t>136068924</t>
+  </si>
+  <si>
+    <t>136067630</t>
+  </si>
+  <si>
+    <t>135949329</t>
+  </si>
+  <si>
+    <t>136032834</t>
+  </si>
+  <si>
+    <t>135977249</t>
+  </si>
+  <si>
+    <t>135973130</t>
+  </si>
+  <si>
+    <t>135977989</t>
+  </si>
+  <si>
+    <t>135981504</t>
+  </si>
+  <si>
+    <t>135982290</t>
+  </si>
+  <si>
+    <t>135983173</t>
+  </si>
+  <si>
+    <t>135986063</t>
+  </si>
+  <si>
+    <t>135986163</t>
+  </si>
+  <si>
+    <t>136024344</t>
+  </si>
+  <si>
+    <t>136075001</t>
+  </si>
+  <si>
+    <t>135806796</t>
+  </si>
+  <si>
+    <t>136023862</t>
+  </si>
+  <si>
+    <t>136024574</t>
+  </si>
+  <si>
+    <t>136025531</t>
+  </si>
+  <si>
+    <t>135986546</t>
+  </si>
+  <si>
+    <t>136000823</t>
+  </si>
+  <si>
+    <t>136007821</t>
+  </si>
+  <si>
+    <t>136007260</t>
+  </si>
+  <si>
+    <t>135991648</t>
+  </si>
+  <si>
+    <t>136010217</t>
+  </si>
+  <si>
+    <t>136008622</t>
+  </si>
+  <si>
+    <t>136002891</t>
+  </si>
+  <si>
+    <t>135998615</t>
+  </si>
+  <si>
+    <t>136008129</t>
+  </si>
+  <si>
+    <t>136001576</t>
+  </si>
+  <si>
+    <t>136001217</t>
+  </si>
+  <si>
+    <t>136009054</t>
+  </si>
+  <si>
+    <t>136009109</t>
+  </si>
+  <si>
+    <t>135981911</t>
+  </si>
+  <si>
+    <t>136002508</t>
+  </si>
+  <si>
+    <t>135992350</t>
+  </si>
+  <si>
+    <t>135998120</t>
+  </si>
+  <si>
+    <t>136002300</t>
+  </si>
+  <si>
+    <t>136003494</t>
+  </si>
+  <si>
+    <t>135998051</t>
+  </si>
+  <si>
+    <t>135998555</t>
+  </si>
+  <si>
+    <t>135998242</t>
+  </si>
+  <si>
+    <t>135998325</t>
+  </si>
+  <si>
+    <t>136000832</t>
+  </si>
+  <si>
+    <t>136001583</t>
+  </si>
+  <si>
+    <t>135997433</t>
+  </si>
+  <si>
+    <t>136004352</t>
+  </si>
+  <si>
+    <t>136004434</t>
+  </si>
+  <si>
+    <t>136008658</t>
+  </si>
+  <si>
+    <t>136001091</t>
+  </si>
+  <si>
+    <t>136002721</t>
+  </si>
+  <si>
+    <t>136008006</t>
+  </si>
+  <si>
+    <t>136008020</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 01.01.2026 a 04.01.2026</t>
   </si>
 </sst>
 </file>
@@ -519,7 +660,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -551,16 +692,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135965207</v>
+        <v>135986512</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -569,16 +710,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -587,16 +728,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -605,16 +746,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -623,16 +764,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -641,16 +782,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -659,16 +800,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -677,16 +818,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -695,16 +836,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -713,16 +854,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -731,16 +872,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -749,16 +890,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -767,16 +908,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -785,16 +926,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -803,16 +944,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -821,16 +962,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -839,16 +980,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -857,16 +998,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -875,16 +1016,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -893,25 +1034,34 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -919,8 +1069,17 @@
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -928,8 +1087,17 @@
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -937,13 +1105,753 @@
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2D57D1-5748-4108-A732-4B6FC119AE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D71B5B6-4CD3-4F58-84AD-FCB43E4E3897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,88 +54,133 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 05.01.2026</t>
-  </si>
-  <si>
-    <t>136050783</t>
-  </si>
-  <si>
-    <t>136040190</t>
-  </si>
-  <si>
-    <t>136044457</t>
-  </si>
-  <si>
-    <t>136055133</t>
-  </si>
-  <si>
-    <t>136042985</t>
-  </si>
-  <si>
-    <t>136066400</t>
-  </si>
-  <si>
-    <t>136070251</t>
-  </si>
-  <si>
-    <t>136056591</t>
-  </si>
-  <si>
-    <t>136073010</t>
-  </si>
-  <si>
-    <t>136060331</t>
-  </si>
-  <si>
-    <t>136073366</t>
-  </si>
-  <si>
-    <t>136048539</t>
-  </si>
-  <si>
-    <t>136069306</t>
-  </si>
-  <si>
-    <t>136066888</t>
-  </si>
-  <si>
-    <t>136065271</t>
-  </si>
-  <si>
-    <t>136063624</t>
-  </si>
-  <si>
-    <t>136043180</t>
-  </si>
-  <si>
-    <t>136062711</t>
-  </si>
-  <si>
-    <t>136053305</t>
-  </si>
-  <si>
-    <t>136045509</t>
-  </si>
-  <si>
-    <t>136044817</t>
-  </si>
-  <si>
-    <t>136042697</t>
-  </si>
-  <si>
-    <t>136052254</t>
-  </si>
-  <si>
-    <t>136064027</t>
-  </si>
-  <si>
-    <t>136073426</t>
-  </si>
-  <si>
-    <t>136051761</t>
-  </si>
-  <si>
     <t>Relatório de Recusas 05.01.2026 a 11.01.2026</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 06.01.2026</t>
+  </si>
+  <si>
+    <t>136018928</t>
+  </si>
+  <si>
+    <t>136019125</t>
+  </si>
+  <si>
+    <t>136020099</t>
+  </si>
+  <si>
+    <t>136022841</t>
+  </si>
+  <si>
+    <t>136027454</t>
+  </si>
+  <si>
+    <t>136022819</t>
+  </si>
+  <si>
+    <t>136029118</t>
+  </si>
+  <si>
+    <t>136030585</t>
+  </si>
+  <si>
+    <t>136032955</t>
+  </si>
+  <si>
+    <t>136012754</t>
+  </si>
+  <si>
+    <t>136025312</t>
+  </si>
+  <si>
+    <t>136015341</t>
+  </si>
+  <si>
+    <t>136078275</t>
+  </si>
+  <si>
+    <t>136084942</t>
+  </si>
+  <si>
+    <t>136042833</t>
+  </si>
+  <si>
+    <t>136085559</t>
+  </si>
+  <si>
+    <t>136095172</t>
+  </si>
+  <si>
+    <t>136097099</t>
+  </si>
+  <si>
+    <t>135996519</t>
+  </si>
+  <si>
+    <t>136000257</t>
+  </si>
+  <si>
+    <t>136013818</t>
+  </si>
+  <si>
+    <t>136014044</t>
+  </si>
+  <si>
+    <t>136014207</t>
+  </si>
+  <si>
+    <t>136014485</t>
+  </si>
+  <si>
+    <t>136014792</t>
+  </si>
+  <si>
+    <t>136014906</t>
+  </si>
+  <si>
+    <t>136015387</t>
+  </si>
+  <si>
+    <t>136046963</t>
+  </si>
+  <si>
+    <t>136020884</t>
+  </si>
+  <si>
+    <t>136021170</t>
+  </si>
+  <si>
+    <t>136022411</t>
+  </si>
+  <si>
+    <t>136023129</t>
+  </si>
+  <si>
+    <t>136023243</t>
+  </si>
+  <si>
+    <t>136026532</t>
+  </si>
+  <si>
+    <t>136027145</t>
+  </si>
+  <si>
+    <t>136028107</t>
+  </si>
+  <si>
+    <t>136028712</t>
+  </si>
+  <si>
+    <t>136030298</t>
+  </si>
+  <si>
+    <t>136031870</t>
+  </si>
+  <si>
+    <t>136031888</t>
+  </si>
+  <si>
+    <t>136032495</t>
   </si>
 </sst>
 </file>
@@ -540,7 +585,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -572,16 +617,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136039316</v>
+        <v>136011043</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -590,16 +635,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -608,16 +653,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -626,16 +671,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -644,16 +689,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -662,16 +707,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -680,16 +725,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -698,16 +743,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -716,16 +761,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -734,16 +779,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -752,16 +797,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -770,16 +815,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -788,16 +833,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -806,16 +851,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -824,16 +869,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -842,16 +887,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -860,16 +905,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -878,16 +923,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -896,16 +941,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -914,16 +959,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -932,16 +977,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -950,16 +995,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -968,16 +1013,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -986,16 +1031,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1004,16 +1049,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1021,16 +1066,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1038,18 +1083,273 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1067,31 +1367,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BBC4591-FA06-46C5-BB0E-C7B0D5726407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CCC502-740C-49E0-81C3-A6ED23E21C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="23">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,22 +57,46 @@
     <t>Relatório de Recusas 05.01.2026 a 11.01.2026</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 07.01.2026</t>
-  </si>
-  <si>
-    <t>136104023</t>
-  </si>
-  <si>
-    <t>136102206</t>
-  </si>
-  <si>
-    <t>136103065</t>
-  </si>
-  <si>
-    <t>136118256</t>
-  </si>
-  <si>
-    <t>136125785</t>
+    <t>Relatório de Recusas Santander - 08.01.2026</t>
+  </si>
+  <si>
+    <t>136063224</t>
+  </si>
+  <si>
+    <t>136084074</t>
+  </si>
+  <si>
+    <t>136088637</t>
+  </si>
+  <si>
+    <t>136086765</t>
+  </si>
+  <si>
+    <t>136081473</t>
+  </si>
+  <si>
+    <t>136086449</t>
+  </si>
+  <si>
+    <t>136103486</t>
+  </si>
+  <si>
+    <t>136048050</t>
+  </si>
+  <si>
+    <t>136022545</t>
+  </si>
+  <si>
+    <t>136027335</t>
+  </si>
+  <si>
+    <t>136058792</t>
+  </si>
+  <si>
+    <t>136075706</t>
+  </si>
+  <si>
+    <t>136082620</t>
   </si>
 </sst>
 </file>
@@ -477,7 +501,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,7 +533,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136060851</v>
+        <v>136048418</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -614,6 +638,142 @@
         <v>6</v>
       </c>
       <c r="F7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -629,31 +789,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CCC502-740C-49E0-81C3-A6ED23E21C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E727B9E-0F3B-4B70-9A8F-95466972F78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="111">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,49 +54,313 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas 05.01.2026 a 11.01.2026</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 08.01.2026</t>
-  </si>
-  <si>
-    <t>136063224</t>
-  </si>
-  <si>
-    <t>136084074</t>
-  </si>
-  <si>
     <t>136088637</t>
   </si>
   <si>
-    <t>136086765</t>
-  </si>
-  <si>
-    <t>136081473</t>
-  </si>
-  <si>
-    <t>136086449</t>
-  </si>
-  <si>
-    <t>136103486</t>
-  </si>
-  <si>
-    <t>136048050</t>
-  </si>
-  <si>
-    <t>136022545</t>
-  </si>
-  <si>
-    <t>136027335</t>
-  </si>
-  <si>
-    <t>136058792</t>
-  </si>
-  <si>
-    <t>136075706</t>
-  </si>
-  <si>
-    <t>136082620</t>
+    <t>Relatório de Recusas Santander - 09 e 10.01.2026</t>
+  </si>
+  <si>
+    <t>136060293</t>
+  </si>
+  <si>
+    <t>136062331</t>
+  </si>
+  <si>
+    <t>136063718</t>
+  </si>
+  <si>
+    <t>136066164</t>
+  </si>
+  <si>
+    <t>136066747</t>
+  </si>
+  <si>
+    <t>136063944</t>
+  </si>
+  <si>
+    <t>136057278</t>
+  </si>
+  <si>
+    <t>136073458</t>
+  </si>
+  <si>
+    <t>136089344</t>
+  </si>
+  <si>
+    <t>136091104</t>
+  </si>
+  <si>
+    <t>136092750</t>
+  </si>
+  <si>
+    <t>136096456</t>
+  </si>
+  <si>
+    <t>136119522</t>
+  </si>
+  <si>
+    <t>136102596</t>
+  </si>
+  <si>
+    <t>136123344</t>
+  </si>
+  <si>
+    <t>136113139</t>
+  </si>
+  <si>
+    <t>136135631</t>
+  </si>
+  <si>
+    <t>136134446</t>
+  </si>
+  <si>
+    <t>136048497</t>
+  </si>
+  <si>
+    <t>136055897</t>
+  </si>
+  <si>
+    <t>136056990</t>
+  </si>
+  <si>
+    <t>136057496</t>
+  </si>
+  <si>
+    <t>136057772</t>
+  </si>
+  <si>
+    <t>136058196</t>
+  </si>
+  <si>
+    <t>136060054</t>
+  </si>
+  <si>
+    <t>136060761</t>
+  </si>
+  <si>
+    <t>136060926</t>
+  </si>
+  <si>
+    <t>136061079</t>
+  </si>
+  <si>
+    <t>136062922</t>
+  </si>
+  <si>
+    <t>136062935</t>
+  </si>
+  <si>
+    <t>136064468</t>
+  </si>
+  <si>
+    <t>136067657</t>
+  </si>
+  <si>
+    <t>136067883</t>
+  </si>
+  <si>
+    <t>136067928</t>
+  </si>
+  <si>
+    <t>136068366</t>
+  </si>
+  <si>
+    <t>136069359</t>
+  </si>
+  <si>
+    <t>136069514</t>
+  </si>
+  <si>
+    <t>136070654</t>
+  </si>
+  <si>
+    <t>136070786</t>
+  </si>
+  <si>
+    <t>136070963</t>
+  </si>
+  <si>
+    <t>136071073</t>
+  </si>
+  <si>
+    <t>136071215</t>
+  </si>
+  <si>
+    <t>136071240</t>
+  </si>
+  <si>
+    <t>136071857</t>
+  </si>
+  <si>
+    <t>136072423</t>
+  </si>
+  <si>
+    <t>136072452</t>
+  </si>
+  <si>
+    <t>136073410</t>
+  </si>
+  <si>
+    <t>136072897</t>
+  </si>
+  <si>
+    <t>136073023</t>
+  </si>
+  <si>
+    <t>136073335</t>
+  </si>
+  <si>
+    <t>136073388</t>
+  </si>
+  <si>
+    <t>136011892</t>
+  </si>
+  <si>
+    <t>136040419</t>
+  </si>
+  <si>
+    <t>136044613</t>
+  </si>
+  <si>
+    <t>136044771</t>
+  </si>
+  <si>
+    <t>136047135</t>
+  </si>
+  <si>
+    <t>136048672</t>
+  </si>
+  <si>
+    <t>136054832</t>
+  </si>
+  <si>
+    <t>136055164</t>
+  </si>
+  <si>
+    <t>136055517</t>
+  </si>
+  <si>
+    <t>136043480</t>
+  </si>
+  <si>
+    <t>136073206</t>
+  </si>
+  <si>
+    <t>136069032</t>
+  </si>
+  <si>
+    <t>136067271</t>
+  </si>
+  <si>
+    <t>136047505</t>
+  </si>
+  <si>
+    <t>136050696</t>
+  </si>
+  <si>
+    <t>136042405</t>
+  </si>
+  <si>
+    <t>136040406</t>
+  </si>
+  <si>
+    <t>136038950</t>
+  </si>
+  <si>
+    <t>136039536</t>
+  </si>
+  <si>
+    <t>136039688</t>
+  </si>
+  <si>
+    <t>136039771</t>
+  </si>
+  <si>
+    <t>136039932</t>
+  </si>
+  <si>
+    <t>136040595</t>
+  </si>
+  <si>
+    <t>136042430</t>
+  </si>
+  <si>
+    <t>136042681</t>
+  </si>
+  <si>
+    <t>136043292</t>
+  </si>
+  <si>
+    <t>136043467</t>
+  </si>
+  <si>
+    <t>136043529</t>
+  </si>
+  <si>
+    <t>136044447</t>
+  </si>
+  <si>
+    <t>136044737</t>
+  </si>
+  <si>
+    <t>136052414</t>
+  </si>
+  <si>
+    <t>136054139</t>
+  </si>
+  <si>
+    <t>136045987</t>
+  </si>
+  <si>
+    <t>136047618</t>
+  </si>
+  <si>
+    <t>136050314</t>
+  </si>
+  <si>
+    <t>136047396</t>
+  </si>
+  <si>
+    <t>136049977</t>
+  </si>
+  <si>
+    <t>136072701</t>
+  </si>
+  <si>
+    <t>136050795</t>
+  </si>
+  <si>
+    <t>136049184</t>
+  </si>
+  <si>
+    <t>136050047</t>
+  </si>
+  <si>
+    <t>136049564</t>
+  </si>
+  <si>
+    <t>136051497</t>
+  </si>
+  <si>
+    <t>136047660</t>
+  </si>
+  <si>
+    <t>136072485</t>
+  </si>
+  <si>
+    <t>136054864</t>
+  </si>
+  <si>
+    <t>136054669</t>
+  </si>
+  <si>
+    <t>136054774</t>
+  </si>
+  <si>
+    <t>136100314</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 05.01.2026 a 11.01.2026 (1)</t>
   </si>
 </sst>
 </file>
@@ -501,7 +765,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -533,7 +797,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136048418</v>
+        <v>136058608</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -542,7 +806,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -560,7 +824,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -578,7 +842,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -596,7 +860,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -614,7 +878,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -632,7 +896,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -650,7 +914,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -667,7 +931,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -675,7 +939,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
@@ -684,7 +948,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -692,7 +956,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -701,7 +965,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -709,7 +973,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -718,7 +982,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -726,7 +990,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
@@ -735,7 +999,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -743,7 +1007,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
@@ -752,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -760,18 +1024,1514 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -789,31 +2549,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A351F515-1DF9-46A4-A57F-AF5FC45643AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F577A29E-EE76-4E62-8219-F87F1F6D089C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="27">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,37 +54,61 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 12.01.2026</t>
-  </si>
-  <si>
-    <t>136097889</t>
-  </si>
-  <si>
-    <t>136097912</t>
-  </si>
-  <si>
-    <t>136118420</t>
-  </si>
-  <si>
-    <t>136141649</t>
-  </si>
-  <si>
-    <t>136182419</t>
-  </si>
-  <si>
-    <t>136124406</t>
-  </si>
-  <si>
-    <t>136127880</t>
-  </si>
-  <si>
-    <t>136125004</t>
-  </si>
-  <si>
-    <t>136098289</t>
-  </si>
-  <si>
     <t>Relatório de Recusas 12.01.2026 a 18.01.2026</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 13.01.2026</t>
+  </si>
+  <si>
+    <t>136088990</t>
+  </si>
+  <si>
+    <t>136078456</t>
+  </si>
+  <si>
+    <t>136098801</t>
+  </si>
+  <si>
+    <t>136104011</t>
+  </si>
+  <si>
+    <t>136110987</t>
+  </si>
+  <si>
+    <t>136170856</t>
+  </si>
+  <si>
+    <t>136140036</t>
+  </si>
+  <si>
+    <t>136184781</t>
+  </si>
+  <si>
+    <t>136170601</t>
+  </si>
+  <si>
+    <t>136074390</t>
+  </si>
+  <si>
+    <t>136075052</t>
+  </si>
+  <si>
+    <t>136075688</t>
+  </si>
+  <si>
+    <t>136078295</t>
+  </si>
+  <si>
+    <t>136081242</t>
+  </si>
+  <si>
+    <t>136083127</t>
+  </si>
+  <si>
+    <t>136085372</t>
+  </si>
+  <si>
+    <t>136188472</t>
   </si>
 </sst>
 </file>
@@ -489,7 +513,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -521,16 +545,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136096806</v>
+        <v>136076382</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -539,16 +563,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -557,16 +581,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -575,16 +599,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -593,16 +617,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -611,16 +635,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -629,16 +653,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -646,16 +670,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -663,16 +687,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -680,18 +704,154 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -709,31 +869,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F577A29E-EE76-4E62-8219-F87F1F6D089C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9ACA39-8DE1-4E37-8A65-5E7FA8EF2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="41">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,58 +57,100 @@
     <t>Relatório de Recusas 12.01.2026 a 18.01.2026</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 13.01.2026</t>
-  </si>
-  <si>
-    <t>136088990</t>
-  </si>
-  <si>
-    <t>136078456</t>
-  </si>
-  <si>
-    <t>136098801</t>
-  </si>
-  <si>
-    <t>136104011</t>
-  </si>
-  <si>
-    <t>136110987</t>
-  </si>
-  <si>
-    <t>136170856</t>
-  </si>
-  <si>
-    <t>136140036</t>
-  </si>
-  <si>
-    <t>136184781</t>
-  </si>
-  <si>
-    <t>136170601</t>
-  </si>
-  <si>
-    <t>136074390</t>
-  </si>
-  <si>
-    <t>136075052</t>
-  </si>
-  <si>
-    <t>136075688</t>
-  </si>
-  <si>
-    <t>136078295</t>
-  </si>
-  <si>
-    <t>136081242</t>
-  </si>
-  <si>
-    <t>136083127</t>
-  </si>
-  <si>
-    <t>136085372</t>
-  </si>
-  <si>
-    <t>136188472</t>
+    <t>Relatório de Recusas Santander - 14.01.2026</t>
+  </si>
+  <si>
+    <t>136140208</t>
+  </si>
+  <si>
+    <t>136136791</t>
+  </si>
+  <si>
+    <t>136139896</t>
+  </si>
+  <si>
+    <t>136167514</t>
+  </si>
+  <si>
+    <t>136165719</t>
+  </si>
+  <si>
+    <t>136168912</t>
+  </si>
+  <si>
+    <t>136190707</t>
+  </si>
+  <si>
+    <t>136183161</t>
+  </si>
+  <si>
+    <t>136154789</t>
+  </si>
+  <si>
+    <t>136195999</t>
+  </si>
+  <si>
+    <t>136200707</t>
+  </si>
+  <si>
+    <t>136201925</t>
+  </si>
+  <si>
+    <t>136208398</t>
+  </si>
+  <si>
+    <t>136195940</t>
+  </si>
+  <si>
+    <t>136222069</t>
+  </si>
+  <si>
+    <t>136056633</t>
+  </si>
+  <si>
+    <t>136141351</t>
+  </si>
+  <si>
+    <t>136134337</t>
+  </si>
+  <si>
+    <t>136130857</t>
+  </si>
+  <si>
+    <t>136118482</t>
+  </si>
+  <si>
+    <t>136138272</t>
+  </si>
+  <si>
+    <t>136155426</t>
+  </si>
+  <si>
+    <t>136162298</t>
+  </si>
+  <si>
+    <t>136161496</t>
+  </si>
+  <si>
+    <t>136155957</t>
+  </si>
+  <si>
+    <t>136160145</t>
+  </si>
+  <si>
+    <t>136123401</t>
+  </si>
+  <si>
+    <t>136166789</t>
+  </si>
+  <si>
+    <t>136115013</t>
+  </si>
+  <si>
+    <t>136163758</t>
+  </si>
+  <si>
+    <t>136120283</t>
   </si>
 </sst>
 </file>
@@ -513,7 +555,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -545,7 +587,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136076382</v>
+        <v>136120926</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -852,6 +894,244 @@
         <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -869,31 +1149,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9ACA39-8DE1-4E37-8A65-5E7FA8EF2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39F828C-3F57-45EF-9946-241E4657BA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,108 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>1070</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 12.01.2026 a 18.01.2026</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 14.01.2026</t>
-  </si>
-  <si>
-    <t>136140208</t>
-  </si>
-  <si>
-    <t>136136791</t>
-  </si>
-  <si>
-    <t>136139896</t>
-  </si>
-  <si>
-    <t>136167514</t>
-  </si>
-  <si>
-    <t>136165719</t>
-  </si>
-  <si>
-    <t>136168912</t>
-  </si>
-  <si>
-    <t>136190707</t>
-  </si>
-  <si>
-    <t>136183161</t>
-  </si>
-  <si>
-    <t>136154789</t>
-  </si>
-  <si>
-    <t>136195999</t>
-  </si>
-  <si>
-    <t>136200707</t>
-  </si>
-  <si>
-    <t>136201925</t>
-  </si>
-  <si>
-    <t>136208398</t>
-  </si>
-  <si>
-    <t>136195940</t>
-  </si>
-  <si>
-    <t>136222069</t>
-  </si>
-  <si>
-    <t>136056633</t>
-  </si>
-  <si>
-    <t>136141351</t>
-  </si>
-  <si>
-    <t>136134337</t>
-  </si>
-  <si>
-    <t>136130857</t>
-  </si>
-  <si>
-    <t>136118482</t>
-  </si>
-  <si>
-    <t>136138272</t>
-  </si>
-  <si>
-    <t>136155426</t>
-  </si>
-  <si>
-    <t>136162298</t>
-  </si>
-  <si>
-    <t>136161496</t>
-  </si>
-  <si>
-    <t>136155957</t>
-  </si>
-  <si>
-    <t>136160145</t>
-  </si>
-  <si>
-    <t>136123401</t>
-  </si>
-  <si>
-    <t>136166789</t>
-  </si>
-  <si>
-    <t>136115013</t>
-  </si>
-  <si>
-    <t>136163758</t>
-  </si>
-  <si>
-    <t>136120283</t>
   </si>
 </sst>
 </file>
@@ -555,7 +453,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -586,552 +484,225 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>136120926</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A2" s="6"/>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E20" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F20"/>
+    </row>
+    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E21" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E22" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F27"/>
+    </row>
+    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F28"/>
+    </row>
+    <row r="29" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
+    <row r="30" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
+    <row r="31" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E31" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
+    <row r="32" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
+    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E40" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1149,31 +720,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39F828C-3F57-45EF-9946-241E4657BA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D4D769-59D2-4539-892C-30D34C610329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,84 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 15.01.2026</t>
+  </si>
+  <si>
+    <t>136131248</t>
+  </si>
+  <si>
+    <t>136173813</t>
+  </si>
+  <si>
+    <t>136176143</t>
+  </si>
+  <si>
+    <t>136184415</t>
+  </si>
+  <si>
+    <t>136187853</t>
+  </si>
+  <si>
+    <t>136171933</t>
+  </si>
+  <si>
+    <t>136182606</t>
+  </si>
+  <si>
+    <t>136173324</t>
+  </si>
+  <si>
+    <t>136181083</t>
+  </si>
+  <si>
+    <t>136187107</t>
+  </si>
+  <si>
+    <t>136182833</t>
+  </si>
+  <si>
+    <t>136215360</t>
+  </si>
+  <si>
+    <t>136159153</t>
+  </si>
+  <si>
+    <t>136176732</t>
+  </si>
+  <si>
+    <t>136178204</t>
+  </si>
+  <si>
+    <t>136143625</t>
+  </si>
+  <si>
+    <t>136191079</t>
+  </si>
+  <si>
+    <t>136158945</t>
+  </si>
+  <si>
+    <t>136178629</t>
+  </si>
+  <si>
+    <t>136172442</t>
+  </si>
+  <si>
+    <t>136112186</t>
+  </si>
+  <si>
+    <t>136082371</t>
+  </si>
+  <si>
+    <t>136096638</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 12.01.2026 a 18.01.2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +531,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,227 +562,445 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136100597</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F26"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F27"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F28"/>
-    </row>
-    <row r="29" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -720,31 +1016,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D4D769-59D2-4539-892C-30D34C610329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD84C97C-5E92-46CD-BD42-F2EFDFCC077C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="38">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,76 +54,91 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 15.01.2026</t>
-  </si>
-  <si>
-    <t>136131248</t>
-  </si>
-  <si>
-    <t>136173813</t>
-  </si>
-  <si>
-    <t>136176143</t>
-  </si>
-  <si>
-    <t>136184415</t>
-  </si>
-  <si>
-    <t>136187853</t>
-  </si>
-  <si>
-    <t>136171933</t>
-  </si>
-  <si>
-    <t>136182606</t>
-  </si>
-  <si>
-    <t>136173324</t>
-  </si>
-  <si>
-    <t>136181083</t>
-  </si>
-  <si>
-    <t>136187107</t>
-  </si>
-  <si>
-    <t>136182833</t>
-  </si>
-  <si>
-    <t>136215360</t>
-  </si>
-  <si>
-    <t>136159153</t>
-  </si>
-  <si>
-    <t>136176732</t>
-  </si>
-  <si>
-    <t>136178204</t>
-  </si>
-  <si>
-    <t>136143625</t>
-  </si>
-  <si>
-    <t>136191079</t>
-  </si>
-  <si>
-    <t>136158945</t>
-  </si>
-  <si>
-    <t>136178629</t>
-  </si>
-  <si>
-    <t>136172442</t>
-  </si>
-  <si>
-    <t>136112186</t>
-  </si>
-  <si>
-    <t>136082371</t>
-  </si>
-  <si>
-    <t>136096638</t>
+    <t>Relatório de Recusas Santander - 16 e 17.01.2026</t>
+  </si>
+  <si>
+    <t>136115565</t>
+  </si>
+  <si>
+    <t>136124453</t>
+  </si>
+  <si>
+    <t>136171595</t>
+  </si>
+  <si>
+    <t>136075685</t>
+  </si>
+  <si>
+    <t>136115665</t>
+  </si>
+  <si>
+    <t>136111315</t>
+  </si>
+  <si>
+    <t>136285137</t>
+  </si>
+  <si>
+    <t>136111630</t>
+  </si>
+  <si>
+    <t>136112461</t>
+  </si>
+  <si>
+    <t>136114533</t>
+  </si>
+  <si>
+    <t>136117096</t>
+  </si>
+  <si>
+    <t>136117581</t>
+  </si>
+  <si>
+    <t>136117639</t>
+  </si>
+  <si>
+    <t>136118025</t>
+  </si>
+  <si>
+    <t>136118847</t>
+  </si>
+  <si>
+    <t>136119373</t>
+  </si>
+  <si>
+    <t>136119560</t>
+  </si>
+  <si>
+    <t>136119772</t>
+  </si>
+  <si>
+    <t>136123384</t>
+  </si>
+  <si>
+    <t>136124351</t>
+  </si>
+  <si>
+    <t>136124863</t>
+  </si>
+  <si>
+    <t>136127371</t>
+  </si>
+  <si>
+    <t>136127429</t>
+  </si>
+  <si>
+    <t>136199917</t>
+  </si>
+  <si>
+    <t>136092756</t>
+  </si>
+  <si>
+    <t>136111947</t>
+  </si>
+  <si>
+    <t>136119826</t>
+  </si>
+  <si>
+    <t>136106331</t>
   </si>
   <si>
     <t>Relatório de Recusas 12.01.2026 a 18.01.2026</t>
@@ -531,7 +546,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -563,7 +578,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136100597</v>
+        <v>136090894</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -572,7 +587,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -590,7 +605,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -608,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -626,7 +641,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -644,7 +659,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -662,7 +677,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -680,7 +695,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -698,7 +713,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -716,7 +731,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -734,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -752,7 +767,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -770,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -788,7 +803,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -806,7 +821,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -824,7 +839,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -842,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -860,7 +875,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -878,7 +893,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -896,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -914,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -932,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -950,7 +965,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -968,7 +983,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -986,21 +1001,100 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD84C97C-5E92-46CD-BD42-F2EFDFCC077C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9C4E72-5AA0-4F2B-8864-BB9243274F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="80">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,94 +54,220 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 16 e 17.01.2026</t>
-  </si>
-  <si>
-    <t>136115565</t>
-  </si>
-  <si>
-    <t>136124453</t>
-  </si>
-  <si>
-    <t>136171595</t>
-  </si>
-  <si>
-    <t>136075685</t>
-  </si>
-  <si>
-    <t>136115665</t>
-  </si>
-  <si>
-    <t>136111315</t>
-  </si>
-  <si>
-    <t>136285137</t>
-  </si>
-  <si>
-    <t>136111630</t>
-  </si>
-  <si>
-    <t>136112461</t>
-  </si>
-  <si>
-    <t>136114533</t>
-  </si>
-  <si>
-    <t>136117096</t>
-  </si>
-  <si>
-    <t>136117581</t>
-  </si>
-  <si>
-    <t>136117639</t>
-  </si>
-  <si>
-    <t>136118025</t>
-  </si>
-  <si>
-    <t>136118847</t>
-  </si>
-  <si>
-    <t>136119373</t>
-  </si>
-  <si>
-    <t>136119560</t>
-  </si>
-  <si>
-    <t>136119772</t>
-  </si>
-  <si>
-    <t>136123384</t>
-  </si>
-  <si>
-    <t>136124351</t>
-  </si>
-  <si>
-    <t>136124863</t>
-  </si>
-  <si>
-    <t>136127371</t>
-  </si>
-  <si>
-    <t>136127429</t>
-  </si>
-  <si>
-    <t>136199917</t>
-  </si>
-  <si>
-    <t>136092756</t>
-  </si>
-  <si>
-    <t>136111947</t>
-  </si>
-  <si>
-    <t>136119826</t>
-  </si>
-  <si>
-    <t>136106331</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 12.01.2026 a 18.01.2026</t>
+    <t>Relatório de Recusas Santander - 19.01.2026</t>
+  </si>
+  <si>
+    <t>136162103</t>
+  </si>
+  <si>
+    <t>136162072</t>
+  </si>
+  <si>
+    <t>136167809</t>
+  </si>
+  <si>
+    <t>136166035</t>
+  </si>
+  <si>
+    <t>136174298</t>
+  </si>
+  <si>
+    <t>136175680</t>
+  </si>
+  <si>
+    <t>136164243</t>
+  </si>
+  <si>
+    <t>136198766</t>
+  </si>
+  <si>
+    <t>136201029</t>
+  </si>
+  <si>
+    <t>136161353</t>
+  </si>
+  <si>
+    <t>136209773</t>
+  </si>
+  <si>
+    <t>136203437</t>
+  </si>
+  <si>
+    <t>136209760</t>
+  </si>
+  <si>
+    <t>136227274</t>
+  </si>
+  <si>
+    <t>136220573</t>
+  </si>
+  <si>
+    <t>136216117</t>
+  </si>
+  <si>
+    <t>136196673</t>
+  </si>
+  <si>
+    <t>136227805</t>
+  </si>
+  <si>
+    <t>136239888</t>
+  </si>
+  <si>
+    <t>136220049</t>
+  </si>
+  <si>
+    <t>136264765</t>
+  </si>
+  <si>
+    <t>136266207</t>
+  </si>
+  <si>
+    <t>136181906</t>
+  </si>
+  <si>
+    <t>136126331</t>
+  </si>
+  <si>
+    <t>136203766</t>
+  </si>
+  <si>
+    <t>136284827</t>
+  </si>
+  <si>
+    <t>136238433</t>
+  </si>
+  <si>
+    <t>136115118</t>
+  </si>
+  <si>
+    <t>136220894</t>
+  </si>
+  <si>
+    <t>136216946</t>
+  </si>
+  <si>
+    <t>136209535</t>
+  </si>
+  <si>
+    <t>136229601</t>
+  </si>
+  <si>
+    <t>136121181</t>
+  </si>
+  <si>
+    <t>136117926</t>
+  </si>
+  <si>
+    <t>136120139</t>
+  </si>
+  <si>
+    <t>136121993</t>
+  </si>
+  <si>
+    <t>136219683</t>
+  </si>
+  <si>
+    <t>136124148</t>
+  </si>
+  <si>
+    <t>136127037</t>
+  </si>
+  <si>
+    <t>136225063</t>
+  </si>
+  <si>
+    <t>136130942</t>
+  </si>
+  <si>
+    <t>136131146</t>
+  </si>
+  <si>
+    <t>136132033</t>
+  </si>
+  <si>
+    <t>136133116</t>
+  </si>
+  <si>
+    <t>136134361</t>
+  </si>
+  <si>
+    <t>136137429</t>
+  </si>
+  <si>
+    <t>136137680</t>
+  </si>
+  <si>
+    <t>136140242</t>
+  </si>
+  <si>
+    <t>136150239</t>
+  </si>
+  <si>
+    <t>136153470</t>
+  </si>
+  <si>
+    <t>136155363</t>
+  </si>
+  <si>
+    <t>136158177</t>
+  </si>
+  <si>
+    <t>136159061</t>
+  </si>
+  <si>
+    <t>136159572</t>
+  </si>
+  <si>
+    <t>136160934</t>
+  </si>
+  <si>
+    <t>136161602</t>
+  </si>
+  <si>
+    <t>136163135</t>
+  </si>
+  <si>
+    <t>136166168</t>
+  </si>
+  <si>
+    <t>136167576</t>
+  </si>
+  <si>
+    <t>136170190</t>
+  </si>
+  <si>
+    <t>136173186</t>
+  </si>
+  <si>
+    <t>136177988</t>
+  </si>
+  <si>
+    <t>136178449</t>
+  </si>
+  <si>
+    <t>136178689</t>
+  </si>
+  <si>
+    <t>136181166</t>
+  </si>
+  <si>
+    <t>136186468</t>
+  </si>
+  <si>
+    <t>136187002</t>
+  </si>
+  <si>
+    <t>136189995</t>
+  </si>
+  <si>
+    <t>136190185</t>
+  </si>
+  <si>
+    <t>136191230</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 19.01.2026 a 25.01.2026</t>
   </si>
 </sst>
 </file>
@@ -546,7 +672,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -578,7 +704,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136090894</v>
+        <v>136105116</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -587,7 +713,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -605,7 +731,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -623,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -641,7 +767,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -659,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -677,7 +803,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -695,7 +821,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -713,7 +839,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -731,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -749,7 +875,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -767,7 +893,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -785,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -803,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -821,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -839,7 +965,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -857,7 +983,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -875,7 +1001,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -893,7 +1019,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -911,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -929,7 +1055,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -947,7 +1073,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -965,7 +1091,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -983,7 +1109,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1001,7 +1127,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1019,7 +1145,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1037,7 +1163,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1055,7 +1181,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1073,7 +1199,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1090,9 +1216,723 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9C4E72-5AA0-4F2B-8864-BB9243274F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494CFE9F-7446-49A3-8918-8CDAA9D0B05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,217 +54,97 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 19.01.2026</t>
-  </si>
-  <si>
-    <t>136162103</t>
-  </si>
-  <si>
-    <t>136162072</t>
-  </si>
-  <si>
-    <t>136167809</t>
-  </si>
-  <si>
-    <t>136166035</t>
-  </si>
-  <si>
-    <t>136174298</t>
-  </si>
-  <si>
-    <t>136175680</t>
-  </si>
-  <si>
-    <t>136164243</t>
-  </si>
-  <si>
-    <t>136198766</t>
-  </si>
-  <si>
-    <t>136201029</t>
-  </si>
-  <si>
-    <t>136161353</t>
-  </si>
-  <si>
-    <t>136209773</t>
-  </si>
-  <si>
-    <t>136203437</t>
-  </si>
-  <si>
-    <t>136209760</t>
-  </si>
-  <si>
-    <t>136227274</t>
-  </si>
-  <si>
-    <t>136220573</t>
-  </si>
-  <si>
-    <t>136216117</t>
-  </si>
-  <si>
-    <t>136196673</t>
-  </si>
-  <si>
-    <t>136227805</t>
-  </si>
-  <si>
-    <t>136239888</t>
-  </si>
-  <si>
-    <t>136220049</t>
-  </si>
-  <si>
-    <t>136264765</t>
-  </si>
-  <si>
-    <t>136266207</t>
-  </si>
-  <si>
-    <t>136181906</t>
-  </si>
-  <si>
-    <t>136126331</t>
-  </si>
-  <si>
-    <t>136203766</t>
-  </si>
-  <si>
-    <t>136284827</t>
-  </si>
-  <si>
-    <t>136238433</t>
-  </si>
-  <si>
-    <t>136115118</t>
-  </si>
-  <si>
-    <t>136220894</t>
-  </si>
-  <si>
-    <t>136216946</t>
-  </si>
-  <si>
-    <t>136209535</t>
-  </si>
-  <si>
-    <t>136229601</t>
-  </si>
-  <si>
-    <t>136121181</t>
-  </si>
-  <si>
-    <t>136117926</t>
-  </si>
-  <si>
-    <t>136120139</t>
-  </si>
-  <si>
-    <t>136121993</t>
-  </si>
-  <si>
-    <t>136219683</t>
-  </si>
-  <si>
-    <t>136124148</t>
-  </si>
-  <si>
-    <t>136127037</t>
-  </si>
-  <si>
-    <t>136225063</t>
-  </si>
-  <si>
-    <t>136130942</t>
-  </si>
-  <si>
-    <t>136131146</t>
-  </si>
-  <si>
-    <t>136132033</t>
-  </si>
-  <si>
-    <t>136133116</t>
-  </si>
-  <si>
-    <t>136134361</t>
-  </si>
-  <si>
-    <t>136137429</t>
-  </si>
-  <si>
-    <t>136137680</t>
-  </si>
-  <si>
-    <t>136140242</t>
-  </si>
-  <si>
-    <t>136150239</t>
-  </si>
-  <si>
-    <t>136153470</t>
-  </si>
-  <si>
-    <t>136155363</t>
-  </si>
-  <si>
-    <t>136158177</t>
-  </si>
-  <si>
-    <t>136159061</t>
-  </si>
-  <si>
-    <t>136159572</t>
-  </si>
-  <si>
-    <t>136160934</t>
-  </si>
-  <si>
-    <t>136161602</t>
-  </si>
-  <si>
-    <t>136163135</t>
-  </si>
-  <si>
-    <t>136166168</t>
-  </si>
-  <si>
-    <t>136167576</t>
-  </si>
-  <si>
-    <t>136170190</t>
-  </si>
-  <si>
-    <t>136173186</t>
-  </si>
-  <si>
-    <t>136177988</t>
-  </si>
-  <si>
-    <t>136178449</t>
-  </si>
-  <si>
-    <t>136178689</t>
-  </si>
-  <si>
-    <t>136181166</t>
-  </si>
-  <si>
-    <t>136186468</t>
-  </si>
-  <si>
-    <t>136187002</t>
-  </si>
-  <si>
-    <t>136189995</t>
-  </si>
-  <si>
-    <t>136190185</t>
-  </si>
-  <si>
-    <t>136191230</t>
+    <t>Relatório de Recusas Santander - 20.01.2026</t>
+  </si>
+  <si>
+    <t>136205150</t>
+  </si>
+  <si>
+    <t>136236485</t>
+  </si>
+  <si>
+    <t>136242492</t>
+  </si>
+  <si>
+    <t>136237016</t>
+  </si>
+  <si>
+    <t>136237898</t>
+  </si>
+  <si>
+    <t>136245655</t>
+  </si>
+  <si>
+    <t>136249313</t>
+  </si>
+  <si>
+    <t>136251637</t>
+  </si>
+  <si>
+    <t>136258778</t>
+  </si>
+  <si>
+    <t>136197660</t>
+  </si>
+  <si>
+    <t>136263011</t>
+  </si>
+  <si>
+    <t>136256269</t>
+  </si>
+  <si>
+    <t>136192409</t>
+  </si>
+  <si>
+    <t>136241303</t>
+  </si>
+  <si>
+    <t>136295931</t>
+  </si>
+  <si>
+    <t>136310665</t>
+  </si>
+  <si>
+    <t>136078351</t>
+  </si>
+  <si>
+    <t>136142232</t>
+  </si>
+  <si>
+    <t>136143250</t>
+  </si>
+  <si>
+    <t>136248476</t>
+  </si>
+  <si>
+    <t>136135971</t>
+  </si>
+  <si>
+    <t>136137403</t>
+  </si>
+  <si>
+    <t>136100653</t>
+  </si>
+  <si>
+    <t>136131576</t>
+  </si>
+  <si>
+    <t>136134008</t>
+  </si>
+  <si>
+    <t>136245494</t>
+  </si>
+  <si>
+    <t>136143609</t>
+  </si>
+  <si>
+    <t>136204550</t>
+  </si>
+  <si>
+    <t>136206999</t>
+  </si>
+  <si>
+    <t>136283913</t>
   </si>
   <si>
     <t>Relatório de Recusas 19.01.2026 a 25.01.2026</t>
@@ -672,7 +552,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -704,7 +584,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136105116</v>
+        <v>136138608</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -713,7 +593,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -731,7 +611,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -749,7 +629,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -767,7 +647,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -785,7 +665,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -803,7 +683,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -821,7 +701,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -839,7 +719,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -857,7 +737,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -875,7 +755,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -893,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -911,7 +791,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -929,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -947,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -965,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -983,7 +863,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1001,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1019,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1037,7 +917,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1055,7 +935,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1073,7 +953,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1091,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1109,7 +989,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1127,7 +1007,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1145,7 +1025,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1163,7 +1043,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1181,7 +1061,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1199,7 +1079,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1216,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1233,7 +1113,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1250,689 +1130,9 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E72" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494CFE9F-7446-49A3-8918-8CDAA9D0B05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BD58D0-A671-485E-BE47-E70D483AD4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="32">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,97 +54,73 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 20.01.2026</t>
-  </si>
-  <si>
-    <t>136205150</t>
-  </si>
-  <si>
-    <t>136236485</t>
-  </si>
-  <si>
-    <t>136242492</t>
-  </si>
-  <si>
-    <t>136237016</t>
-  </si>
-  <si>
-    <t>136237898</t>
-  </si>
-  <si>
-    <t>136245655</t>
-  </si>
-  <si>
-    <t>136249313</t>
-  </si>
-  <si>
-    <t>136251637</t>
-  </si>
-  <si>
-    <t>136258778</t>
-  </si>
-  <si>
-    <t>136197660</t>
-  </si>
-  <si>
-    <t>136263011</t>
-  </si>
-  <si>
-    <t>136256269</t>
-  </si>
-  <si>
-    <t>136192409</t>
-  </si>
-  <si>
-    <t>136241303</t>
-  </si>
-  <si>
-    <t>136295931</t>
-  </si>
-  <si>
-    <t>136310665</t>
-  </si>
-  <si>
-    <t>136078351</t>
-  </si>
-  <si>
-    <t>136142232</t>
-  </si>
-  <si>
-    <t>136143250</t>
-  </si>
-  <si>
-    <t>136248476</t>
-  </si>
-  <si>
-    <t>136135971</t>
-  </si>
-  <si>
-    <t>136137403</t>
-  </si>
-  <si>
-    <t>136100653</t>
-  </si>
-  <si>
-    <t>136131576</t>
-  </si>
-  <si>
-    <t>136134008</t>
-  </si>
-  <si>
-    <t>136245494</t>
-  </si>
-  <si>
-    <t>136143609</t>
-  </si>
-  <si>
-    <t>136204550</t>
-  </si>
-  <si>
-    <t>136206999</t>
-  </si>
-  <si>
-    <t>136283913</t>
+    <t>Relatório de Recusas Santander - 21.01.2026</t>
+  </si>
+  <si>
+    <t>136235650</t>
+  </si>
+  <si>
+    <t>136240866</t>
+  </si>
+  <si>
+    <t>136259760</t>
+  </si>
+  <si>
+    <t>136272873</t>
+  </si>
+  <si>
+    <t>136267964</t>
+  </si>
+  <si>
+    <t>136247223</t>
+  </si>
+  <si>
+    <t>136285232</t>
+  </si>
+  <si>
+    <t>136328294</t>
+  </si>
+  <si>
+    <t>136204484</t>
+  </si>
+  <si>
+    <t>136261498</t>
+  </si>
+  <si>
+    <t>136155031</t>
+  </si>
+  <si>
+    <t>136268608</t>
+  </si>
+  <si>
+    <t>136161590</t>
+  </si>
+  <si>
+    <t>136263581</t>
+  </si>
+  <si>
+    <t>136156332</t>
+  </si>
+  <si>
+    <t>136237446</t>
+  </si>
+  <si>
+    <t>136250722</t>
+  </si>
+  <si>
+    <t>136343395</t>
+  </si>
+  <si>
+    <t>136267310</t>
+  </si>
+  <si>
+    <t>136157001</t>
+  </si>
+  <si>
+    <t>136241493</t>
+  </si>
+  <si>
+    <t>136239432</t>
   </si>
   <si>
     <t>Relatório de Recusas 19.01.2026 a 25.01.2026</t>
@@ -552,7 +528,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -584,7 +560,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136138608</v>
+        <v>136168042</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -593,7 +569,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -611,7 +587,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -629,7 +605,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -647,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -665,7 +641,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -683,7 +659,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -701,7 +677,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -719,7 +695,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -737,7 +713,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -755,7 +731,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -773,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -791,7 +767,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -809,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -827,7 +803,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -845,7 +821,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -863,7 +839,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -881,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -899,7 +875,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -917,7 +893,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -935,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -953,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -971,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -989,152 +965,12 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F24"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BD58D0-A671-485E-BE47-E70D483AD4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3312E6-FBFF-4072-94A4-C583CA2964EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="24">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,73 +54,49 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 21.01.2026</t>
-  </si>
-  <si>
-    <t>136235650</t>
-  </si>
-  <si>
-    <t>136240866</t>
-  </si>
-  <si>
-    <t>136259760</t>
-  </si>
-  <si>
-    <t>136272873</t>
-  </si>
-  <si>
-    <t>136267964</t>
-  </si>
-  <si>
-    <t>136247223</t>
-  </si>
-  <si>
-    <t>136285232</t>
-  </si>
-  <si>
-    <t>136328294</t>
-  </si>
-  <si>
-    <t>136204484</t>
-  </si>
-  <si>
-    <t>136261498</t>
-  </si>
-  <si>
-    <t>136155031</t>
-  </si>
-  <si>
-    <t>136268608</t>
-  </si>
-  <si>
-    <t>136161590</t>
-  </si>
-  <si>
-    <t>136263581</t>
-  </si>
-  <si>
-    <t>136156332</t>
-  </si>
-  <si>
-    <t>136237446</t>
-  </si>
-  <si>
-    <t>136250722</t>
-  </si>
-  <si>
-    <t>136343395</t>
-  </si>
-  <si>
-    <t>136267310</t>
-  </si>
-  <si>
-    <t>136157001</t>
-  </si>
-  <si>
-    <t>136241493</t>
-  </si>
-  <si>
-    <t>136239432</t>
+    <t>Relatório de Recusas Santander - 22.01.2026</t>
+  </si>
+  <si>
+    <t>136265038</t>
+  </si>
+  <si>
+    <t>136268873</t>
+  </si>
+  <si>
+    <t>136323633</t>
+  </si>
+  <si>
+    <t>136346545</t>
+  </si>
+  <si>
+    <t>136283841</t>
+  </si>
+  <si>
+    <t>136189133</t>
+  </si>
+  <si>
+    <t>136190909</t>
+  </si>
+  <si>
+    <t>136284770</t>
+  </si>
+  <si>
+    <t>136187231</t>
+  </si>
+  <si>
+    <t>136279831</t>
+  </si>
+  <si>
+    <t>136258212</t>
+  </si>
+  <si>
+    <t>136180926</t>
+  </si>
+  <si>
+    <t>136276674</t>
+  </si>
+  <si>
+    <t>136261227</t>
   </si>
   <si>
     <t>Relatório de Recusas 19.01.2026 a 25.01.2026</t>
@@ -528,7 +504,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -560,7 +536,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136168042</v>
+        <v>136259803</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -569,7 +545,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -587,7 +563,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -605,7 +581,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -623,7 +599,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -641,7 +617,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -659,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -677,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -695,7 +671,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -713,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -731,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -749,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -767,7 +743,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -785,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -803,7 +779,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -821,156 +797,12 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3312E6-FBFF-4072-94A4-C583CA2964EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C44185-8A68-47A9-9C2D-FCE187385AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="55">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,49 +54,142 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 22.01.2026</t>
-  </si>
-  <si>
-    <t>136265038</t>
-  </si>
-  <si>
-    <t>136268873</t>
-  </si>
-  <si>
-    <t>136323633</t>
-  </si>
-  <si>
-    <t>136346545</t>
-  </si>
-  <si>
-    <t>136283841</t>
-  </si>
-  <si>
-    <t>136189133</t>
-  </si>
-  <si>
-    <t>136190909</t>
-  </si>
-  <si>
-    <t>136284770</t>
-  </si>
-  <si>
-    <t>136187231</t>
-  </si>
-  <si>
-    <t>136279831</t>
-  </si>
-  <si>
-    <t>136258212</t>
-  </si>
-  <si>
-    <t>136180926</t>
-  </si>
-  <si>
-    <t>136276674</t>
-  </si>
-  <si>
-    <t>136261227</t>
+    <t>Relatório de Recusas Santander - 23 e 24.01.2026</t>
+  </si>
+  <si>
+    <t>136204083</t>
+  </si>
+  <si>
+    <t>136210420</t>
+  </si>
+  <si>
+    <t>136217497</t>
+  </si>
+  <si>
+    <t>136222466</t>
+  </si>
+  <si>
+    <t>136229051</t>
+  </si>
+  <si>
+    <t>136298386</t>
+  </si>
+  <si>
+    <t>136308843</t>
+  </si>
+  <si>
+    <t>136331715</t>
+  </si>
+  <si>
+    <t>136347242</t>
+  </si>
+  <si>
+    <t>136364491</t>
+  </si>
+  <si>
+    <t>136370351</t>
+  </si>
+  <si>
+    <t>136172680</t>
+  </si>
+  <si>
+    <t>136195579</t>
+  </si>
+  <si>
+    <t>136197359</t>
+  </si>
+  <si>
+    <t>136197589</t>
+  </si>
+  <si>
+    <t>136197799</t>
+  </si>
+  <si>
+    <t>136199140</t>
+  </si>
+  <si>
+    <t>136204512</t>
+  </si>
+  <si>
+    <t>136205901</t>
+  </si>
+  <si>
+    <t>136209337</t>
+  </si>
+  <si>
+    <t>136212010</t>
+  </si>
+  <si>
+    <t>136212633</t>
+  </si>
+  <si>
+    <t>136251023</t>
+  </si>
+  <si>
+    <t>136273446</t>
+  </si>
+  <si>
+    <t>136220882</t>
+  </si>
+  <si>
+    <t>136222733</t>
+  </si>
+  <si>
+    <t>136222970</t>
+  </si>
+  <si>
+    <t>136227006</t>
+  </si>
+  <si>
+    <t>136231067</t>
+  </si>
+  <si>
+    <t>136232394</t>
+  </si>
+  <si>
+    <t>136196463</t>
+  </si>
+  <si>
+    <t>136248629</t>
+  </si>
+  <si>
+    <t>136250076</t>
+  </si>
+  <si>
+    <t>136247155</t>
+  </si>
+  <si>
+    <t>136252158</t>
+  </si>
+  <si>
+    <t>136200431</t>
+  </si>
+  <si>
+    <t>136221889</t>
+  </si>
+  <si>
+    <t>136237144</t>
+  </si>
+  <si>
+    <t>136237408</t>
+  </si>
+  <si>
+    <t>136239635</t>
+  </si>
+  <si>
+    <t>136240177</t>
+  </si>
+  <si>
+    <t>136241410</t>
+  </si>
+  <si>
+    <t>136248577</t>
+  </si>
+  <si>
+    <t>136249013</t>
+  </si>
+  <si>
+    <t>136249524</t>
   </si>
   <si>
     <t>Relatório de Recusas 19.01.2026 a 25.01.2026</t>
@@ -504,7 +597,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -536,7 +629,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136259803</v>
+        <v>136201349</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -545,7 +638,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -563,7 +656,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -581,7 +674,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -599,7 +692,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -617,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -635,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -653,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -671,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -689,7 +782,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -707,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -725,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -743,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -761,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -779,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -797,12 +890,551 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16"/>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{50D4D769-59D2-4539-892C-30D34C610329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B714D943-E536-453A-BA81-C35EED699EB5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3170F4-3C44-4DBC-93B1-3921A3389481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="44">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,117 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 26.01.2026</t>
+  </si>
+  <si>
+    <t>136220387</t>
+  </si>
+  <si>
+    <t>136227830</t>
+  </si>
+  <si>
+    <t>136228192</t>
+  </si>
+  <si>
+    <t>136230170</t>
+  </si>
+  <si>
+    <t>136230598</t>
+  </si>
+  <si>
+    <t>136255805</t>
+  </si>
+  <si>
+    <t>136259591</t>
+  </si>
+  <si>
+    <t>136216099</t>
+  </si>
+  <si>
+    <t>136300559</t>
+  </si>
+  <si>
+    <t>136302684</t>
+  </si>
+  <si>
+    <t>136306186</t>
+  </si>
+  <si>
+    <t>136308029</t>
+  </si>
+  <si>
+    <t>136318258</t>
+  </si>
+  <si>
+    <t>136322481</t>
+  </si>
+  <si>
+    <t>136305826</t>
+  </si>
+  <si>
+    <t>136333509</t>
+  </si>
+  <si>
+    <t>136304716</t>
+  </si>
+  <si>
+    <t>136315367</t>
+  </si>
+  <si>
+    <t>136328002</t>
+  </si>
+  <si>
+    <t>136338477</t>
+  </si>
+  <si>
+    <t>136335272</t>
+  </si>
+  <si>
+    <t>136354445</t>
+  </si>
+  <si>
+    <t>136308579</t>
+  </si>
+  <si>
+    <t>136360372</t>
+  </si>
+  <si>
+    <t>136394438</t>
+  </si>
+  <si>
+    <t>136400551</t>
+  </si>
+  <si>
+    <t>136198975</t>
+  </si>
+  <si>
+    <t>136225295</t>
+  </si>
+  <si>
+    <t>136313592</t>
+  </si>
+  <si>
+    <t>136231084</t>
+  </si>
+  <si>
+    <t>136263397</t>
+  </si>
+  <si>
+    <t>136325831</t>
+  </si>
+  <si>
+    <t>136318119</t>
+  </si>
+  <si>
+    <t>136221382</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 26.01.2026 a 01.02.2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +564,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,140 +595,626 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136212396</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -633,31 +1230,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{50D4D769-59D2-4539-892C-30D34C610329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B714D943-E536-453A-BA81-C35EED699EB5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76184A0A-E8F5-4096-B30C-D012CA93DB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="61">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,168 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 27.01.2026</t>
+  </si>
+  <si>
+    <t>136260477</t>
+  </si>
+  <si>
+    <t>136242732</t>
+  </si>
+  <si>
+    <t>136287697</t>
+  </si>
+  <si>
+    <t>136292249</t>
+  </si>
+  <si>
+    <t>136273270</t>
+  </si>
+  <si>
+    <t>136287593</t>
+  </si>
+  <si>
+    <t>136340803</t>
+  </si>
+  <si>
+    <t>136347294</t>
+  </si>
+  <si>
+    <t>136348208</t>
+  </si>
+  <si>
+    <t>136270632</t>
+  </si>
+  <si>
+    <t>136343008</t>
+  </si>
+  <si>
+    <t>136284069</t>
+  </si>
+  <si>
+    <t>136366672</t>
+  </si>
+  <si>
+    <t>136413290</t>
+  </si>
+  <si>
+    <t>136413481</t>
+  </si>
+  <si>
+    <t>136260233</t>
+  </si>
+  <si>
+    <t>136262951</t>
+  </si>
+  <si>
+    <t>136263322</t>
+  </si>
+  <si>
+    <t>136266846</t>
+  </si>
+  <si>
+    <t>136273043</t>
+  </si>
+  <si>
+    <t>136266045</t>
+  </si>
+  <si>
+    <t>136263610</t>
+  </si>
+  <si>
+    <t>136261409</t>
+  </si>
+  <si>
+    <t>136264032</t>
+  </si>
+  <si>
+    <t>136274090</t>
+  </si>
+  <si>
+    <t>136270483</t>
+  </si>
+  <si>
+    <t>136264571</t>
+  </si>
+  <si>
+    <t>136264995</t>
+  </si>
+  <si>
+    <t>136346369</t>
+  </si>
+  <si>
+    <t>136241606</t>
+  </si>
+  <si>
+    <t>136241976</t>
+  </si>
+  <si>
+    <t>136241993</t>
+  </si>
+  <si>
+    <t>136242345</t>
+  </si>
+  <si>
+    <t>136346132</t>
+  </si>
+  <si>
+    <t>136242410</t>
+  </si>
+  <si>
+    <t>136242868</t>
+  </si>
+  <si>
+    <t>136243081</t>
+  </si>
+  <si>
+    <t>136247141</t>
+  </si>
+  <si>
+    <t>136249442</t>
+  </si>
+  <si>
+    <t>136354969</t>
+  </si>
+  <si>
+    <t>136263225</t>
+  </si>
+  <si>
+    <t>136283613</t>
+  </si>
+  <si>
+    <t>136283757</t>
+  </si>
+  <si>
+    <t>136284425</t>
+  </si>
+  <si>
+    <t>136284557</t>
+  </si>
+  <si>
+    <t>136289064</t>
+  </si>
+  <si>
+    <t>136291474</t>
+  </si>
+  <si>
+    <t>136291832</t>
+  </si>
+  <si>
+    <t>136292532</t>
+  </si>
+  <si>
+    <t>136293814</t>
+  </si>
+  <si>
+    <t>136294618</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 26.01.2026 a 01.02.2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +615,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,140 +646,915 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136260706</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -633,31 +1570,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76184A0A-E8F5-4096-B30C-D012CA93DB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0869B9A-E100-452C-8286-9A427DA61BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="46">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,160 +54,115 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 27.01.2026</t>
-  </si>
-  <si>
-    <t>136260477</t>
-  </si>
-  <si>
-    <t>136242732</t>
-  </si>
-  <si>
-    <t>136287697</t>
-  </si>
-  <si>
-    <t>136292249</t>
-  </si>
-  <si>
-    <t>136273270</t>
-  </si>
-  <si>
-    <t>136287593</t>
-  </si>
-  <si>
-    <t>136340803</t>
-  </si>
-  <si>
-    <t>136347294</t>
-  </si>
-  <si>
-    <t>136348208</t>
-  </si>
-  <si>
-    <t>136270632</t>
-  </si>
-  <si>
-    <t>136343008</t>
-  </si>
-  <si>
-    <t>136284069</t>
-  </si>
-  <si>
-    <t>136366672</t>
-  </si>
-  <si>
-    <t>136413290</t>
-  </si>
-  <si>
-    <t>136413481</t>
-  </si>
-  <si>
-    <t>136260233</t>
-  </si>
-  <si>
-    <t>136262951</t>
-  </si>
-  <si>
-    <t>136263322</t>
-  </si>
-  <si>
-    <t>136266846</t>
-  </si>
-  <si>
-    <t>136273043</t>
-  </si>
-  <si>
-    <t>136266045</t>
-  </si>
-  <si>
-    <t>136263610</t>
-  </si>
-  <si>
-    <t>136261409</t>
-  </si>
-  <si>
-    <t>136264032</t>
-  </si>
-  <si>
-    <t>136274090</t>
-  </si>
-  <si>
-    <t>136270483</t>
-  </si>
-  <si>
-    <t>136264571</t>
-  </si>
-  <si>
-    <t>136264995</t>
-  </si>
-  <si>
-    <t>136346369</t>
-  </si>
-  <si>
-    <t>136241606</t>
-  </si>
-  <si>
-    <t>136241976</t>
-  </si>
-  <si>
-    <t>136241993</t>
-  </si>
-  <si>
-    <t>136242345</t>
-  </si>
-  <si>
-    <t>136346132</t>
-  </si>
-  <si>
-    <t>136242410</t>
-  </si>
-  <si>
-    <t>136242868</t>
-  </si>
-  <si>
-    <t>136243081</t>
-  </si>
-  <si>
-    <t>136247141</t>
-  </si>
-  <si>
-    <t>136249442</t>
-  </si>
-  <si>
-    <t>136354969</t>
-  </si>
-  <si>
-    <t>136263225</t>
-  </si>
-  <si>
-    <t>136283613</t>
-  </si>
-  <si>
-    <t>136283757</t>
-  </si>
-  <si>
-    <t>136284425</t>
-  </si>
-  <si>
-    <t>136284557</t>
-  </si>
-  <si>
-    <t>136289064</t>
-  </si>
-  <si>
-    <t>136291474</t>
-  </si>
-  <si>
-    <t>136291832</t>
-  </si>
-  <si>
-    <t>136292532</t>
-  </si>
-  <si>
-    <t>136293814</t>
-  </si>
-  <si>
-    <t>136294618</t>
+    <t>Relatório de Recusas Santander - 28.01.2026</t>
+  </si>
+  <si>
+    <t>136348722</t>
+  </si>
+  <si>
+    <t>136355676</t>
+  </si>
+  <si>
+    <t>136355567</t>
+  </si>
+  <si>
+    <t>136364079</t>
+  </si>
+  <si>
+    <t>136366453</t>
+  </si>
+  <si>
+    <t>136366808</t>
+  </si>
+  <si>
+    <t>136368326</t>
+  </si>
+  <si>
+    <t>136367932</t>
+  </si>
+  <si>
+    <t>136376326</t>
+  </si>
+  <si>
+    <t>136372112</t>
+  </si>
+  <si>
+    <t>136374664</t>
+  </si>
+  <si>
+    <t>136386252</t>
+  </si>
+  <si>
+    <t>136304193</t>
+  </si>
+  <si>
+    <t>136269380</t>
+  </si>
+  <si>
+    <t>136368575</t>
+  </si>
+  <si>
+    <t>136263250</t>
+  </si>
+  <si>
+    <t>136263518</t>
+  </si>
+  <si>
+    <t>136264017</t>
+  </si>
+  <si>
+    <t>136264607</t>
+  </si>
+  <si>
+    <t>136259294</t>
+  </si>
+  <si>
+    <t>136259505</t>
+  </si>
+  <si>
+    <t>136260297</t>
+  </si>
+  <si>
+    <t>136260554</t>
+  </si>
+  <si>
+    <t>136262149</t>
+  </si>
+  <si>
+    <t>136262878</t>
+  </si>
+  <si>
+    <t>136363334</t>
+  </si>
+  <si>
+    <t>136265017</t>
+  </si>
+  <si>
+    <t>136265290</t>
+  </si>
+  <si>
+    <t>136266581</t>
+  </si>
+  <si>
+    <t>136268365</t>
+  </si>
+  <si>
+    <t>136269775</t>
+  </si>
+  <si>
+    <t>136268692</t>
+  </si>
+  <si>
+    <t>136284082</t>
+  </si>
+  <si>
+    <t>136317936</t>
+  </si>
+  <si>
+    <t>136370920</t>
+  </si>
+  <si>
+    <t>136375283</t>
   </si>
   <si>
     <t>Relatório de Recusas 26.01.2026 a 01.02.2026</t>
@@ -615,7 +570,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -647,7 +602,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136260706</v>
+        <v>136319087</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -656,7 +611,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -674,7 +629,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -692,7 +647,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -710,7 +665,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -728,7 +683,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -746,7 +701,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -764,7 +719,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -782,7 +737,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -800,7 +755,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -818,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -836,7 +791,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -854,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -872,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -890,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -908,7 +863,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -926,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -944,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -962,7 +917,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -980,7 +935,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -998,7 +953,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1016,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1034,7 +989,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1052,7 +1007,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1070,7 +1025,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1088,7 +1043,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1106,7 +1061,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1124,7 +1079,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1142,7 +1097,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1159,7 +1114,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1176,7 +1131,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1193,7 +1148,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1210,7 +1165,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1227,7 +1182,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1244,7 +1199,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1261,7 +1216,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1278,7 +1233,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1295,264 +1250,9 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E53" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{50D4D769-59D2-4539-892C-30D34C610329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B714D943-E536-453A-BA81-C35EED699EB5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42E8F95-9081-4E24-B048-A8C6DD2910E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="30">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,75 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 29.01.2026</t>
+  </si>
+  <si>
+    <t>136390097</t>
+  </si>
+  <si>
+    <t>136391359</t>
+  </si>
+  <si>
+    <t>136395847</t>
+  </si>
+  <si>
+    <t>136276835</t>
+  </si>
+  <si>
+    <t>136282579</t>
+  </si>
+  <si>
+    <t>136288897</t>
+  </si>
+  <si>
+    <t>136375978</t>
+  </si>
+  <si>
+    <t>136348957</t>
+  </si>
+  <si>
+    <t>136393811</t>
+  </si>
+  <si>
+    <t>136319137</t>
+  </si>
+  <si>
+    <t>136351962</t>
+  </si>
+  <si>
+    <t>136365225</t>
+  </si>
+  <si>
+    <t>136350874</t>
+  </si>
+  <si>
+    <t>136302274</t>
+  </si>
+  <si>
+    <t>136307389</t>
+  </si>
+  <si>
+    <t>136307794</t>
+  </si>
+  <si>
+    <t>136311064</t>
+  </si>
+  <si>
+    <t>136312626</t>
+  </si>
+  <si>
+    <t>136315853</t>
+  </si>
+  <si>
+    <t>136318651</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 26.01.2026 a 01.02.2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +522,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,140 +553,382 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136396691</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
-    </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="F23"/>
-    </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="F26"/>
-    </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="F27"/>
-    </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="F28"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -633,31 +944,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42E8F95-9081-4E24-B048-A8C6DD2910E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3BD26C-5361-430F-A2C1-02C54AC973DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,70 +54,79 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 29.01.2026</t>
-  </si>
-  <si>
-    <t>136390097</t>
-  </si>
-  <si>
-    <t>136391359</t>
-  </si>
-  <si>
-    <t>136395847</t>
-  </si>
-  <si>
-    <t>136276835</t>
-  </si>
-  <si>
-    <t>136282579</t>
-  </si>
-  <si>
-    <t>136288897</t>
-  </si>
-  <si>
-    <t>136375978</t>
-  </si>
-  <si>
-    <t>136348957</t>
-  </si>
-  <si>
-    <t>136393811</t>
-  </si>
-  <si>
-    <t>136319137</t>
-  </si>
-  <si>
-    <t>136351962</t>
-  </si>
-  <si>
-    <t>136365225</t>
-  </si>
-  <si>
-    <t>136350874</t>
-  </si>
-  <si>
-    <t>136302274</t>
-  </si>
-  <si>
-    <t>136307389</t>
-  </si>
-  <si>
-    <t>136307794</t>
-  </si>
-  <si>
-    <t>136311064</t>
-  </si>
-  <si>
-    <t>136312626</t>
-  </si>
-  <si>
-    <t>136315853</t>
-  </si>
-  <si>
-    <t>136318651</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 26.01.2026 a 01.02.2026</t>
+    <t>Relatório de Recusas Santander - 30 e 31.01.2026</t>
+  </si>
+  <si>
+    <t>136335619</t>
+  </si>
+  <si>
+    <t>136322602</t>
+  </si>
+  <si>
+    <t>136333272</t>
+  </si>
+  <si>
+    <t>136365576</t>
+  </si>
+  <si>
+    <t>136326114</t>
+  </si>
+  <si>
+    <t>136395359</t>
+  </si>
+  <si>
+    <t>136382669</t>
+  </si>
+  <si>
+    <t>136399851</t>
+  </si>
+  <si>
+    <t>136400382</t>
+  </si>
+  <si>
+    <t>136407819</t>
+  </si>
+  <si>
+    <t>136441969</t>
+  </si>
+  <si>
+    <t>136445291</t>
+  </si>
+  <si>
+    <t>136446096</t>
+  </si>
+  <si>
+    <t>136448122</t>
+  </si>
+  <si>
+    <t>136300280</t>
+  </si>
+  <si>
+    <t>136305689</t>
+  </si>
+  <si>
+    <t>136394151</t>
+  </si>
+  <si>
+    <t>136326627</t>
+  </si>
+  <si>
+    <t>136387228</t>
+  </si>
+  <si>
+    <t>136317064</t>
+  </si>
+  <si>
+    <t>136464933</t>
+  </si>
+  <si>
+    <t>136483872</t>
+  </si>
+  <si>
+    <t>136449735</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 26.01.2026 a 01.02.2026 (2)</t>
   </si>
 </sst>
 </file>
@@ -522,7 +531,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -554,7 +563,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136396691</v>
+        <v>136328396</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -563,7 +572,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -581,7 +590,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -599,7 +608,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -617,7 +626,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -635,7 +644,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -653,7 +662,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -671,7 +680,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -689,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -707,7 +716,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -725,7 +734,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -743,7 +752,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -761,7 +770,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -779,7 +788,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -797,7 +806,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -815,7 +824,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -833,7 +842,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -851,7 +860,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -869,7 +878,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -887,7 +896,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -905,7 +914,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -923,12 +932,66 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22"/>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3BD26C-5361-430F-A2C1-02C54AC973DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB93B50-B129-43E3-90B6-C43F905CBE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="24">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,79 +54,52 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 30 e 31.01.2026</t>
-  </si>
-  <si>
-    <t>136335619</t>
-  </si>
-  <si>
-    <t>136322602</t>
-  </si>
-  <si>
-    <t>136333272</t>
-  </si>
-  <si>
-    <t>136365576</t>
-  </si>
-  <si>
-    <t>136326114</t>
-  </si>
-  <si>
-    <t>136395359</t>
-  </si>
-  <si>
-    <t>136382669</t>
-  </si>
-  <si>
-    <t>136399851</t>
-  </si>
-  <si>
-    <t>136400382</t>
-  </si>
-  <si>
-    <t>136407819</t>
-  </si>
-  <si>
-    <t>136441969</t>
-  </si>
-  <si>
-    <t>136445291</t>
-  </si>
-  <si>
-    <t>136446096</t>
-  </si>
-  <si>
-    <t>136448122</t>
-  </si>
-  <si>
-    <t>136300280</t>
-  </si>
-  <si>
-    <t>136305689</t>
-  </si>
-  <si>
-    <t>136394151</t>
-  </si>
-  <si>
-    <t>136326627</t>
-  </si>
-  <si>
-    <t>136387228</t>
-  </si>
-  <si>
-    <t>136317064</t>
-  </si>
-  <si>
-    <t>136464933</t>
-  </si>
-  <si>
-    <t>136483872</t>
-  </si>
-  <si>
-    <t>136449735</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 26.01.2026 a 01.02.2026 (2)</t>
+    <t>Relatório de Recusas Santander - 02.02.2026</t>
+  </si>
+  <si>
+    <t>136372291</t>
+  </si>
+  <si>
+    <t>136370085</t>
+  </si>
+  <si>
+    <t>136374261</t>
+  </si>
+  <si>
+    <t>136375328</t>
+  </si>
+  <si>
+    <t>136401355</t>
+  </si>
+  <si>
+    <t>136404356</t>
+  </si>
+  <si>
+    <t>136407947</t>
+  </si>
+  <si>
+    <t>136409565</t>
+  </si>
+  <si>
+    <t>136410644</t>
+  </si>
+  <si>
+    <t>136426683</t>
+  </si>
+  <si>
+    <t>136434085</t>
+  </si>
+  <si>
+    <t>136414652</t>
+  </si>
+  <si>
+    <t>136415341</t>
+  </si>
+  <si>
+    <t>136427242</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 02.02.2026 a 08.02.2026</t>
   </si>
 </sst>
 </file>
@@ -531,7 +504,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -563,7 +536,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136328396</v>
+        <v>136364056</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -572,7 +545,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -590,7 +563,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -608,7 +581,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -626,7 +599,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -644,7 +617,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -662,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -680,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -698,7 +671,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -716,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -734,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -752,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -770,7 +743,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -788,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -806,7 +779,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -824,174 +797,12 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB93B50-B129-43E3-90B6-C43F905CBE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945DAFAF-FF66-4CC6-A900-E03CC6315A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,49 +54,82 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 02.02.2026</t>
-  </si>
-  <si>
-    <t>136372291</t>
-  </si>
-  <si>
-    <t>136370085</t>
-  </si>
-  <si>
-    <t>136374261</t>
-  </si>
-  <si>
-    <t>136375328</t>
-  </si>
-  <si>
-    <t>136401355</t>
-  </si>
-  <si>
-    <t>136404356</t>
-  </si>
-  <si>
-    <t>136407947</t>
-  </si>
-  <si>
-    <t>136409565</t>
-  </si>
-  <si>
-    <t>136410644</t>
-  </si>
-  <si>
-    <t>136426683</t>
-  </si>
-  <si>
-    <t>136434085</t>
-  </si>
-  <si>
-    <t>136414652</t>
-  </si>
-  <si>
-    <t>136415341</t>
-  </si>
-  <si>
-    <t>136427242</t>
+    <t>Relatório de Recusas Santander - 03.02.2026</t>
+  </si>
+  <si>
+    <t>136382428</t>
+  </si>
+  <si>
+    <t>136442657</t>
+  </si>
+  <si>
+    <t>136445906</t>
+  </si>
+  <si>
+    <t>136452550</t>
+  </si>
+  <si>
+    <t>136465056</t>
+  </si>
+  <si>
+    <t>136471630</t>
+  </si>
+  <si>
+    <t>136465949</t>
+  </si>
+  <si>
+    <t>136468154</t>
+  </si>
+  <si>
+    <t>136466617</t>
+  </si>
+  <si>
+    <t>136477003</t>
+  </si>
+  <si>
+    <t>136369261</t>
+  </si>
+  <si>
+    <t>136440560</t>
+  </si>
+  <si>
+    <t>136388552</t>
+  </si>
+  <si>
+    <t>136440124</t>
+  </si>
+  <si>
+    <t>136448221</t>
+  </si>
+  <si>
+    <t>136453096</t>
+  </si>
+  <si>
+    <t>136382326</t>
+  </si>
+  <si>
+    <t>136387100</t>
+  </si>
+  <si>
+    <t>136388457</t>
+  </si>
+  <si>
+    <t>136390303</t>
+  </si>
+  <si>
+    <t>136391159</t>
+  </si>
+  <si>
+    <t>136394737</t>
+  </si>
+  <si>
+    <t>136395864</t>
+  </si>
+  <si>
+    <t>136398875</t>
+  </si>
+  <si>
+    <t>136399912</t>
   </si>
   <si>
     <t>Relatório de Recusas 02.02.2026 a 08.02.2026</t>
@@ -504,7 +537,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -536,7 +569,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136364056</v>
+        <v>136393265</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -545,7 +578,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -563,7 +596,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -581,7 +614,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -599,7 +632,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -617,7 +650,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -635,7 +668,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -653,7 +686,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -671,7 +704,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -689,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -707,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -725,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -743,7 +776,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -761,7 +794,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -779,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -797,12 +830,210 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16"/>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945DAFAF-FF66-4CC6-A900-E03CC6315A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B15DE79-6CAF-4FDA-8AE4-0CEC33536DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,85 +54,106 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 03.02.2026</t>
-  </si>
-  <si>
-    <t>136382428</t>
-  </si>
-  <si>
-    <t>136442657</t>
-  </si>
-  <si>
-    <t>136445906</t>
-  </si>
-  <si>
-    <t>136452550</t>
-  </si>
-  <si>
-    <t>136465056</t>
-  </si>
-  <si>
-    <t>136471630</t>
-  </si>
-  <si>
-    <t>136465949</t>
-  </si>
-  <si>
-    <t>136468154</t>
-  </si>
-  <si>
-    <t>136466617</t>
-  </si>
-  <si>
-    <t>136477003</t>
-  </si>
-  <si>
-    <t>136369261</t>
-  </si>
-  <si>
-    <t>136440560</t>
-  </si>
-  <si>
-    <t>136388552</t>
-  </si>
-  <si>
-    <t>136440124</t>
-  </si>
-  <si>
-    <t>136448221</t>
-  </si>
-  <si>
-    <t>136453096</t>
-  </si>
-  <si>
-    <t>136382326</t>
-  </si>
-  <si>
-    <t>136387100</t>
-  </si>
-  <si>
-    <t>136388457</t>
-  </si>
-  <si>
-    <t>136390303</t>
-  </si>
-  <si>
-    <t>136391159</t>
-  </si>
-  <si>
-    <t>136394737</t>
-  </si>
-  <si>
-    <t>136395864</t>
-  </si>
-  <si>
-    <t>136398875</t>
-  </si>
-  <si>
-    <t>136399912</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 02.02.2026 a 08.02.2026</t>
+    <t>Relatório de Recusas Santander - 04.02.2026</t>
+  </si>
+  <si>
+    <t>136375544</t>
+  </si>
+  <si>
+    <t>136411283</t>
+  </si>
+  <si>
+    <t>136450780</t>
+  </si>
+  <si>
+    <t>136458401</t>
+  </si>
+  <si>
+    <t>136474591</t>
+  </si>
+  <si>
+    <t>136464170</t>
+  </si>
+  <si>
+    <t>136465255</t>
+  </si>
+  <si>
+    <t>136465096</t>
+  </si>
+  <si>
+    <t>136473937</t>
+  </si>
+  <si>
+    <t>136465181</t>
+  </si>
+  <si>
+    <t>136471752</t>
+  </si>
+  <si>
+    <t>136464852</t>
+  </si>
+  <si>
+    <t>136487454</t>
+  </si>
+  <si>
+    <t>136493445</t>
+  </si>
+  <si>
+    <t>136479102</t>
+  </si>
+  <si>
+    <t>136496332</t>
+  </si>
+  <si>
+    <t>136489061</t>
+  </si>
+  <si>
+    <t>136346750</t>
+  </si>
+  <si>
+    <t>136507408</t>
+  </si>
+  <si>
+    <t>136479422</t>
+  </si>
+  <si>
+    <t>136514818</t>
+  </si>
+  <si>
+    <t>136527056</t>
+  </si>
+  <si>
+    <t>136343043</t>
+  </si>
+  <si>
+    <t>136344713</t>
+  </si>
+  <si>
+    <t>136353661</t>
+  </si>
+  <si>
+    <t>136471655</t>
+  </si>
+  <si>
+    <t>136342040</t>
+  </si>
+  <si>
+    <t>136353205</t>
+  </si>
+  <si>
+    <t>136530705</t>
+  </si>
+  <si>
+    <t>136464512</t>
+  </si>
+  <si>
+    <t>136451468</t>
+  </si>
+  <si>
+    <t>136464463</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 02.02.2026 a 08.02.2026 (1)</t>
   </si>
 </sst>
 </file>
@@ -537,7 +558,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -569,7 +590,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136393265</v>
+        <v>136357409</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -578,7 +599,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -596,7 +617,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -614,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -632,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -650,7 +671,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -668,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -686,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -704,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -722,7 +743,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -740,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -758,7 +779,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -776,7 +797,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -794,7 +815,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -812,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -830,7 +851,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -848,7 +869,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -866,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -884,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -902,7 +923,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -920,7 +941,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -938,7 +959,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -956,7 +977,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -974,7 +995,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -992,7 +1013,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1010,7 +1031,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1028,12 +1049,132 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27"/>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B15DE79-6CAF-4FDA-8AE4-0CEC33536DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{50D4D769-59D2-4539-892C-30D34C610329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B714D943-E536-453A-BA81-C35EED699EB5}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,111 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>1070</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 04.02.2026</t>
-  </si>
-  <si>
-    <t>136375544</t>
-  </si>
-  <si>
-    <t>136411283</t>
-  </si>
-  <si>
-    <t>136450780</t>
-  </si>
-  <si>
-    <t>136458401</t>
-  </si>
-  <si>
-    <t>136474591</t>
-  </si>
-  <si>
-    <t>136464170</t>
-  </si>
-  <si>
-    <t>136465255</t>
-  </si>
-  <si>
-    <t>136465096</t>
-  </si>
-  <si>
-    <t>136473937</t>
-  </si>
-  <si>
-    <t>136465181</t>
-  </si>
-  <si>
-    <t>136471752</t>
-  </si>
-  <si>
-    <t>136464852</t>
-  </si>
-  <si>
-    <t>136487454</t>
-  </si>
-  <si>
-    <t>136493445</t>
-  </si>
-  <si>
-    <t>136479102</t>
-  </si>
-  <si>
-    <t>136496332</t>
-  </si>
-  <si>
-    <t>136489061</t>
-  </si>
-  <si>
-    <t>136346750</t>
-  </si>
-  <si>
-    <t>136507408</t>
-  </si>
-  <si>
-    <t>136479422</t>
-  </si>
-  <si>
-    <t>136514818</t>
-  </si>
-  <si>
-    <t>136527056</t>
-  </si>
-  <si>
-    <t>136343043</t>
-  </si>
-  <si>
-    <t>136344713</t>
-  </si>
-  <si>
-    <t>136353661</t>
-  </si>
-  <si>
-    <t>136471655</t>
-  </si>
-  <si>
-    <t>136342040</t>
-  </si>
-  <si>
-    <t>136353205</t>
-  </si>
-  <si>
-    <t>136530705</t>
-  </si>
-  <si>
-    <t>136464512</t>
-  </si>
-  <si>
-    <t>136451468</t>
-  </si>
-  <si>
-    <t>136464463</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 02.02.2026 a 08.02.2026 (1)</t>
   </si>
 </sst>
 </file>
@@ -558,7 +453,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -589,592 +484,140 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>136357409</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="A2" s="6"/>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>41</v>
-      </c>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>41</v>
-      </c>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>41</v>
-      </c>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F20"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F22"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F23"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F24"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F25"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F26"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F27"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F28"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1190,31 +633,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{50D4D769-59D2-4539-892C-30D34C610329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B714D943-E536-453A-BA81-C35EED699EB5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A172CB86-7DA5-42CC-9C6C-8570B28E8FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,90 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 05.02.2026</t>
+  </si>
+  <si>
+    <t>136457939</t>
+  </si>
+  <si>
+    <t>136471107</t>
+  </si>
+  <si>
+    <t>136480400</t>
+  </si>
+  <si>
+    <t>136480845</t>
+  </si>
+  <si>
+    <t>136483174</t>
+  </si>
+  <si>
+    <t>136491426</t>
+  </si>
+  <si>
+    <t>136492138</t>
+  </si>
+  <si>
+    <t>136494955</t>
+  </si>
+  <si>
+    <t>136494531</t>
+  </si>
+  <si>
+    <t>136477170</t>
+  </si>
+  <si>
+    <t>136487155</t>
+  </si>
+  <si>
+    <t>136490933</t>
+  </si>
+  <si>
+    <t>136491341</t>
+  </si>
+  <si>
+    <t>136494857</t>
+  </si>
+  <si>
+    <t>136505741</t>
+  </si>
+  <si>
+    <t>136508214</t>
+  </si>
+  <si>
+    <t>136545742</t>
+  </si>
+  <si>
+    <t>136555173</t>
+  </si>
+  <si>
+    <t>136361533</t>
+  </si>
+  <si>
+    <t>136432105</t>
+  </si>
+  <si>
+    <t>136464388</t>
+  </si>
+  <si>
+    <t>136490384</t>
+  </si>
+  <si>
+    <t>136449849</t>
+  </si>
+  <si>
+    <t>136401544</t>
+  </si>
+  <si>
+    <t>136492769</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 02.02.2026 a 08.02.2026</t>
   </si>
 </sst>
 </file>
@@ -484,139 +568,474 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136430571</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F28"/>
     </row>
   </sheetData>
@@ -633,31 +1052,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A172CB86-7DA5-42CC-9C6C-8570B28E8FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E5A313-EF43-4C1E-A32D-6A13545D252F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="41">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,82 +54,100 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 05.02.2026</t>
-  </si>
-  <si>
-    <t>136457939</t>
-  </si>
-  <si>
-    <t>136471107</t>
-  </si>
-  <si>
-    <t>136480400</t>
-  </si>
-  <si>
-    <t>136480845</t>
-  </si>
-  <si>
-    <t>136483174</t>
-  </si>
-  <si>
-    <t>136491426</t>
-  </si>
-  <si>
-    <t>136492138</t>
-  </si>
-  <si>
-    <t>136494955</t>
-  </si>
-  <si>
-    <t>136494531</t>
-  </si>
-  <si>
-    <t>136477170</t>
-  </si>
-  <si>
-    <t>136487155</t>
-  </si>
-  <si>
-    <t>136490933</t>
-  </si>
-  <si>
-    <t>136491341</t>
-  </si>
-  <si>
-    <t>136494857</t>
-  </si>
-  <si>
-    <t>136505741</t>
-  </si>
-  <si>
-    <t>136508214</t>
-  </si>
-  <si>
-    <t>136545742</t>
-  </si>
-  <si>
-    <t>136555173</t>
-  </si>
-  <si>
-    <t>136361533</t>
-  </si>
-  <si>
-    <t>136432105</t>
-  </si>
-  <si>
-    <t>136464388</t>
-  </si>
-  <si>
-    <t>136490384</t>
-  </si>
-  <si>
-    <t>136449849</t>
-  </si>
-  <si>
-    <t>136401544</t>
-  </si>
-  <si>
-    <t>136492769</t>
+    <t>Relatório de Recusas Santander - 06 e 07.02.2026</t>
+  </si>
+  <si>
+    <t>136422602</t>
+  </si>
+  <si>
+    <t>136499722</t>
+  </si>
+  <si>
+    <t>136500176</t>
+  </si>
+  <si>
+    <t>136498096</t>
+  </si>
+  <si>
+    <t>136537250</t>
+  </si>
+  <si>
+    <t>136499664</t>
+  </si>
+  <si>
+    <t>136556944</t>
+  </si>
+  <si>
+    <t>136575042</t>
+  </si>
+  <si>
+    <t>136576778</t>
+  </si>
+  <si>
+    <t>136573520</t>
+  </si>
+  <si>
+    <t>136399342</t>
+  </si>
+  <si>
+    <t>136449074</t>
+  </si>
+  <si>
+    <t>136473015</t>
+  </si>
+  <si>
+    <t>136424014</t>
+  </si>
+  <si>
+    <t>136480143</t>
+  </si>
+  <si>
+    <t>136484935</t>
+  </si>
+  <si>
+    <t>136422367</t>
+  </si>
+  <si>
+    <t>136422868</t>
+  </si>
+  <si>
+    <t>136425177</t>
+  </si>
+  <si>
+    <t>136425594</t>
+  </si>
+  <si>
+    <t>136426215</t>
+  </si>
+  <si>
+    <t>136426234</t>
+  </si>
+  <si>
+    <t>136426571</t>
+  </si>
+  <si>
+    <t>136426694</t>
+  </si>
+  <si>
+    <t>136427067</t>
+  </si>
+  <si>
+    <t>136428683</t>
+  </si>
+  <si>
+    <t>136430360</t>
+  </si>
+  <si>
+    <t>136433937</t>
+  </si>
+  <si>
+    <t>136435029</t>
+  </si>
+  <si>
+    <t>136435842</t>
+  </si>
+  <si>
+    <t>136424431</t>
   </si>
   <si>
     <t>Relatório de Recusas 02.02.2026 a 08.02.2026</t>
@@ -537,7 +555,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -569,7 +587,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136430571</v>
+        <v>136419479</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -578,7 +596,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -596,7 +614,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -614,7 +632,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -632,7 +650,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -650,7 +668,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -668,7 +686,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -686,7 +704,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -704,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -722,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -740,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -758,7 +776,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -776,7 +794,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -794,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -812,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -830,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -848,7 +866,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -866,7 +884,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -884,7 +902,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -902,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -920,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -938,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -956,7 +974,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -974,7 +992,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -992,7 +1010,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1010,7 +1028,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1028,15 +1046,115 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E5A313-EF43-4C1E-A32D-6A13545D252F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{50D4D769-59D2-4539-892C-30D34C610329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B714D943-E536-453A-BA81-C35EED699EB5}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,108 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>1070</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 06 e 07.02.2026</t>
-  </si>
-  <si>
-    <t>136422602</t>
-  </si>
-  <si>
-    <t>136499722</t>
-  </si>
-  <si>
-    <t>136500176</t>
-  </si>
-  <si>
-    <t>136498096</t>
-  </si>
-  <si>
-    <t>136537250</t>
-  </si>
-  <si>
-    <t>136499664</t>
-  </si>
-  <si>
-    <t>136556944</t>
-  </si>
-  <si>
-    <t>136575042</t>
-  </si>
-  <si>
-    <t>136576778</t>
-  </si>
-  <si>
-    <t>136573520</t>
-  </si>
-  <si>
-    <t>136399342</t>
-  </si>
-  <si>
-    <t>136449074</t>
-  </si>
-  <si>
-    <t>136473015</t>
-  </si>
-  <si>
-    <t>136424014</t>
-  </si>
-  <si>
-    <t>136480143</t>
-  </si>
-  <si>
-    <t>136484935</t>
-  </si>
-  <si>
-    <t>136422367</t>
-  </si>
-  <si>
-    <t>136422868</t>
-  </si>
-  <si>
-    <t>136425177</t>
-  </si>
-  <si>
-    <t>136425594</t>
-  </si>
-  <si>
-    <t>136426215</t>
-  </si>
-  <si>
-    <t>136426234</t>
-  </si>
-  <si>
-    <t>136426571</t>
-  </si>
-  <si>
-    <t>136426694</t>
-  </si>
-  <si>
-    <t>136427067</t>
-  </si>
-  <si>
-    <t>136428683</t>
-  </si>
-  <si>
-    <t>136430360</t>
-  </si>
-  <si>
-    <t>136433937</t>
-  </si>
-  <si>
-    <t>136435029</t>
-  </si>
-  <si>
-    <t>136435842</t>
-  </si>
-  <si>
-    <t>136424431</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 02.02.2026 a 08.02.2026</t>
   </si>
 </sst>
 </file>
@@ -555,7 +453,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -586,575 +484,140 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>136419479</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="A2" s="6"/>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>40</v>
-      </c>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>40</v>
-      </c>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>40</v>
-      </c>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F20"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F22"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F23"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F24"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F25"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F26"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F27"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
       <c r="F28"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1170,31 +633,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{50D4D769-59D2-4539-892C-30D34C610329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B714D943-E536-453A-BA81-C35EED699EB5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233A56FC-10E7-4FE9-A845-297C4EB0FD09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="109">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,312 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 09.02.2026</t>
+  </si>
+  <si>
+    <t>136465260</t>
+  </si>
+  <si>
+    <t>136471203</t>
+  </si>
+  <si>
+    <t>136473444</t>
+  </si>
+  <si>
+    <t>136458429</t>
+  </si>
+  <si>
+    <t>136461389</t>
+  </si>
+  <si>
+    <t>136474453</t>
+  </si>
+  <si>
+    <t>136475756</t>
+  </si>
+  <si>
+    <t>136472176</t>
+  </si>
+  <si>
+    <t>136482435</t>
+  </si>
+  <si>
+    <t>136482788</t>
+  </si>
+  <si>
+    <t>136492609</t>
+  </si>
+  <si>
+    <t>136493802</t>
+  </si>
+  <si>
+    <t>136492072</t>
+  </si>
+  <si>
+    <t>136493898</t>
+  </si>
+  <si>
+    <t>136495966</t>
+  </si>
+  <si>
+    <t>136494395</t>
+  </si>
+  <si>
+    <t>136497331</t>
+  </si>
+  <si>
+    <t>136496525</t>
+  </si>
+  <si>
+    <t>136478940</t>
+  </si>
+  <si>
+    <t>136484224</t>
+  </si>
+  <si>
+    <t>136495664</t>
+  </si>
+  <si>
+    <t>136517042</t>
+  </si>
+  <si>
+    <t>136507603</t>
+  </si>
+  <si>
+    <t>136529840</t>
+  </si>
+  <si>
+    <t>136532121</t>
+  </si>
+  <si>
+    <t>136530866</t>
+  </si>
+  <si>
+    <t>136537723</t>
+  </si>
+  <si>
+    <t>136530551</t>
+  </si>
+  <si>
+    <t>136532327</t>
+  </si>
+  <si>
+    <t>136473711</t>
+  </si>
+  <si>
+    <t>136528085</t>
+  </si>
+  <si>
+    <t>136483835</t>
+  </si>
+  <si>
+    <t>136485047</t>
+  </si>
+  <si>
+    <t>136570165</t>
+  </si>
+  <si>
+    <t>136576941</t>
+  </si>
+  <si>
+    <t>136522475</t>
+  </si>
+  <si>
+    <t>136572095</t>
+  </si>
+  <si>
+    <t>136496014</t>
+  </si>
+  <si>
+    <t>136510993</t>
+  </si>
+  <si>
+    <t>136445487</t>
+  </si>
+  <si>
+    <t>136448051</t>
+  </si>
+  <si>
+    <t>136440998</t>
+  </si>
+  <si>
+    <t>136448132</t>
+  </si>
+  <si>
+    <t>136448415</t>
+  </si>
+  <si>
+    <t>136453329</t>
+  </si>
+  <si>
+    <t>136446494</t>
+  </si>
+  <si>
+    <t>136448763</t>
+  </si>
+  <si>
+    <t>136443035</t>
+  </si>
+  <si>
+    <t>136449209</t>
+  </si>
+  <si>
+    <t>136450518</t>
+  </si>
+  <si>
+    <t>136451363</t>
+  </si>
+  <si>
+    <t>136451835</t>
+  </si>
+  <si>
+    <t>136439942</t>
+  </si>
+  <si>
+    <t>136448511</t>
+  </si>
+  <si>
+    <t>136440268</t>
+  </si>
+  <si>
+    <t>136454528</t>
+  </si>
+  <si>
+    <t>136438866</t>
+  </si>
+  <si>
+    <t>136446064</t>
+  </si>
+  <si>
+    <t>136446666</t>
+  </si>
+  <si>
+    <t>136524659</t>
+  </si>
+  <si>
+    <t>136502518</t>
+  </si>
+  <si>
+    <t>136512787</t>
+  </si>
+  <si>
+    <t>136509527</t>
+  </si>
+  <si>
+    <t>136521624</t>
+  </si>
+  <si>
+    <t>136528050</t>
+  </si>
+  <si>
+    <t>136534170</t>
+  </si>
+  <si>
+    <t>136528029</t>
+  </si>
+  <si>
+    <t>136525701</t>
+  </si>
+  <si>
+    <t>136465176</t>
+  </si>
+  <si>
+    <t>136469438</t>
+  </si>
+  <si>
+    <t>136472331</t>
+  </si>
+  <si>
+    <t>136472778</t>
+  </si>
+  <si>
+    <t>136479528</t>
+  </si>
+  <si>
+    <t>136525845</t>
+  </si>
+  <si>
+    <t>136482268</t>
+  </si>
+  <si>
+    <t>136482553</t>
+  </si>
+  <si>
+    <t>136483031</t>
+  </si>
+  <si>
+    <t>136484642</t>
+  </si>
+  <si>
+    <t>136484917</t>
+  </si>
+  <si>
+    <t>136485282</t>
+  </si>
+  <si>
+    <t>136485305</t>
+  </si>
+  <si>
+    <t>136487849</t>
+  </si>
+  <si>
+    <t>136487918</t>
+  </si>
+  <si>
+    <t>136488238</t>
+  </si>
+  <si>
+    <t>136490067</t>
+  </si>
+  <si>
+    <t>136490793</t>
+  </si>
+  <si>
+    <t>136491557</t>
+  </si>
+  <si>
+    <t>136492002</t>
+  </si>
+  <si>
+    <t>136493107</t>
+  </si>
+  <si>
+    <t>136493127</t>
+  </si>
+  <si>
+    <t>136493169</t>
+  </si>
+  <si>
+    <t>136493285</t>
+  </si>
+  <si>
+    <t>136493306</t>
+  </si>
+  <si>
+    <t>136493892</t>
+  </si>
+  <si>
+    <t>136494260</t>
+  </si>
+  <si>
+    <t>136494819</t>
+  </si>
+  <si>
+    <t>136495125</t>
+  </si>
+  <si>
+    <t>136496179</t>
+  </si>
+  <si>
+    <t>136495243</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 09.02.2026 a 15.02.2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +759,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,140 +790,1731 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136458414</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -633,31 +2530,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9280F3-3260-4A6B-8E8F-3A1A1D20F20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC9A6F5-ECDB-44BB-88DE-23647014955A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="32">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,94 +54,73 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 10.02.2026</t>
-  </si>
-  <si>
-    <t>136544694</t>
-  </si>
-  <si>
-    <t>136546740</t>
-  </si>
-  <si>
-    <t>136556983</t>
-  </si>
-  <si>
-    <t>136549649</t>
-  </si>
-  <si>
-    <t>136545020</t>
-  </si>
-  <si>
-    <t>136550615</t>
-  </si>
-  <si>
-    <t>136554112</t>
-  </si>
-  <si>
-    <t>136547307</t>
-  </si>
-  <si>
-    <t>136577555</t>
-  </si>
-  <si>
-    <t>136574106</t>
-  </si>
-  <si>
-    <t>136569897</t>
-  </si>
-  <si>
-    <t>136590604</t>
-  </si>
-  <si>
-    <t>136605541</t>
-  </si>
-  <si>
-    <t>136589134</t>
-  </si>
-  <si>
-    <t>136551257</t>
-  </si>
-  <si>
-    <t>136432160</t>
-  </si>
-  <si>
-    <t>136556297</t>
-  </si>
-  <si>
-    <t>136548776</t>
-  </si>
-  <si>
-    <t>136463403</t>
-  </si>
-  <si>
-    <t>136549076</t>
-  </si>
-  <si>
-    <t>136526134</t>
-  </si>
-  <si>
-    <t>136513461</t>
-  </si>
-  <si>
-    <t>136580070</t>
-  </si>
-  <si>
-    <t>136524183</t>
-  </si>
-  <si>
-    <t>136500753</t>
-  </si>
-  <si>
-    <t>136512866</t>
-  </si>
-  <si>
-    <t>136498050</t>
-  </si>
-  <si>
-    <t>136499606</t>
-  </si>
-  <si>
-    <t>136499685</t>
+    <t>Relatório de Recusas Santander - 11.02.2026</t>
+  </si>
+  <si>
+    <t>136524492</t>
+  </si>
+  <si>
+    <t>136546937</t>
+  </si>
+  <si>
+    <t>136543214</t>
+  </si>
+  <si>
+    <t>136569445</t>
+  </si>
+  <si>
+    <t>136571337</t>
+  </si>
+  <si>
+    <t>136572246</t>
+  </si>
+  <si>
+    <t>136514831</t>
+  </si>
+  <si>
+    <t>136576510</t>
+  </si>
+  <si>
+    <t>136569102</t>
+  </si>
+  <si>
+    <t>136590176</t>
+  </si>
+  <si>
+    <t>136595018</t>
+  </si>
+  <si>
+    <t>136601750</t>
+  </si>
+  <si>
+    <t>136601805</t>
+  </si>
+  <si>
+    <t>136636095</t>
+  </si>
+  <si>
+    <t>136639628</t>
+  </si>
+  <si>
+    <t>136644047</t>
+  </si>
+  <si>
+    <t>136694699</t>
+  </si>
+  <si>
+    <t>136453696</t>
+  </si>
+  <si>
+    <t>136551234</t>
+  </si>
+  <si>
+    <t>136547472</t>
+  </si>
+  <si>
+    <t>136700316</t>
+  </si>
+  <si>
+    <t>136704748</t>
   </si>
   <si>
     <t>Relatório de Recusas 09.02.2026 a 15.02.2026</t>
@@ -549,7 +528,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -581,7 +560,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136466416</v>
+        <v>136455879</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -590,7 +569,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -608,7 +587,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -626,7 +605,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -644,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -662,7 +641,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -680,7 +659,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -698,7 +677,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -716,7 +695,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -734,7 +713,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -752,7 +731,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -770,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -788,7 +767,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -806,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -824,7 +803,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -842,7 +821,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -860,7 +839,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -878,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -896,7 +875,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -914,7 +893,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -932,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -950,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -968,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -986,135 +965,12 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F24"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC9A6F5-ECDB-44BB-88DE-23647014955A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAB9B35-8C99-4BC3-943D-3DB5ECD7587C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="41">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,73 +54,100 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 11.02.2026</t>
-  </si>
-  <si>
-    <t>136524492</t>
-  </si>
-  <si>
-    <t>136546937</t>
-  </si>
-  <si>
-    <t>136543214</t>
-  </si>
-  <si>
-    <t>136569445</t>
-  </si>
-  <si>
-    <t>136571337</t>
-  </si>
-  <si>
-    <t>136572246</t>
-  </si>
-  <si>
-    <t>136514831</t>
-  </si>
-  <si>
-    <t>136576510</t>
-  </si>
-  <si>
-    <t>136569102</t>
-  </si>
-  <si>
-    <t>136590176</t>
-  </si>
-  <si>
-    <t>136595018</t>
-  </si>
-  <si>
-    <t>136601750</t>
-  </si>
-  <si>
-    <t>136601805</t>
-  </si>
-  <si>
-    <t>136636095</t>
-  </si>
-  <si>
-    <t>136639628</t>
-  </si>
-  <si>
-    <t>136644047</t>
-  </si>
-  <si>
-    <t>136694699</t>
-  </si>
-  <si>
-    <t>136453696</t>
-  </si>
-  <si>
-    <t>136551234</t>
-  </si>
-  <si>
-    <t>136547472</t>
-  </si>
-  <si>
-    <t>136700316</t>
-  </si>
-  <si>
-    <t>136704748</t>
+    <t>Relatório de Recusas Santander - 12.02.2026</t>
+  </si>
+  <si>
+    <t>136474860</t>
+  </si>
+  <si>
+    <t>136463642</t>
+  </si>
+  <si>
+    <t>136518849</t>
+  </si>
+  <si>
+    <t>136553134</t>
+  </si>
+  <si>
+    <t>136551076</t>
+  </si>
+  <si>
+    <t>136558474</t>
+  </si>
+  <si>
+    <t>136547735</t>
+  </si>
+  <si>
+    <t>136576164</t>
+  </si>
+  <si>
+    <t>136591578</t>
+  </si>
+  <si>
+    <t>136593052</t>
+  </si>
+  <si>
+    <t>136597563</t>
+  </si>
+  <si>
+    <t>136593973</t>
+  </si>
+  <si>
+    <t>136595745</t>
+  </si>
+  <si>
+    <t>136605571</t>
+  </si>
+  <si>
+    <t>136615073</t>
+  </si>
+  <si>
+    <t>136648173</t>
+  </si>
+  <si>
+    <t>136653408</t>
+  </si>
+  <si>
+    <t>136651167</t>
+  </si>
+  <si>
+    <t>136669032</t>
+  </si>
+  <si>
+    <t>136689621</t>
+  </si>
+  <si>
+    <t>136694836</t>
+  </si>
+  <si>
+    <t>136699378</t>
+  </si>
+  <si>
+    <t>136570057</t>
+  </si>
+  <si>
+    <t>136528200</t>
+  </si>
+  <si>
+    <t>136541423</t>
+  </si>
+  <si>
+    <t>136515044</t>
+  </si>
+  <si>
+    <t>136491409</t>
+  </si>
+  <si>
+    <t>136494552</t>
+  </si>
+  <si>
+    <t>136726323</t>
+  </si>
+  <si>
+    <t>136604000</t>
+  </si>
+  <si>
+    <t>136588781</t>
   </si>
   <si>
     <t>Relatório de Recusas 09.02.2026 a 15.02.2026</t>
@@ -528,7 +555,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -560,7 +587,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136455879</v>
+        <v>136465591</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -569,7 +596,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -587,7 +614,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -605,7 +632,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -623,7 +650,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -641,7 +668,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -659,7 +686,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -677,7 +704,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -695,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -713,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -731,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -749,7 +776,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -767,7 +794,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -785,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -803,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -821,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -839,7 +866,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -857,7 +884,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -875,7 +902,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -893,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -911,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -929,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -947,7 +974,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -965,12 +992,169 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24"/>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{50D4D769-59D2-4539-892C-30D34C610329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B714D943-E536-453A-BA81-C35EED699EB5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2390B7-98F5-4376-8D15-509A1F4F2DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="150">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,435 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 13, 14 e 15.02.2026</t>
+  </si>
+  <si>
+    <t>136564443</t>
+  </si>
+  <si>
+    <t>136603934</t>
+  </si>
+  <si>
+    <t>136598352</t>
+  </si>
+  <si>
+    <t>136605790</t>
+  </si>
+  <si>
+    <t>136595596</t>
+  </si>
+  <si>
+    <t>136674851</t>
+  </si>
+  <si>
+    <t>136683092</t>
+  </si>
+  <si>
+    <t>136702073</t>
+  </si>
+  <si>
+    <t>136575506</t>
+  </si>
+  <si>
+    <t>136477117</t>
+  </si>
+  <si>
+    <t>136588337</t>
+  </si>
+  <si>
+    <t>136569395</t>
+  </si>
+  <si>
+    <t>136525346</t>
+  </si>
+  <si>
+    <t>136550848</t>
+  </si>
+  <si>
+    <t>136750739</t>
+  </si>
+  <si>
+    <t>136516381</t>
+  </si>
+  <si>
+    <t>136515721</t>
+  </si>
+  <si>
+    <t>136703630</t>
+  </si>
+  <si>
+    <t>136700188</t>
+  </si>
+  <si>
+    <t>136501725</t>
+  </si>
+  <si>
+    <t>136504318</t>
+  </si>
+  <si>
+    <t>136506422</t>
+  </si>
+  <si>
+    <t>136524991</t>
+  </si>
+  <si>
+    <t>136529802</t>
+  </si>
+  <si>
+    <t>136533925</t>
+  </si>
+  <si>
+    <t>136536291</t>
+  </si>
+  <si>
+    <t>136536867</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 09.02.2026 a 15.02.2026</t>
+  </si>
+  <si>
+    <t>136542902</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 16, 17 e 18.02.2026</t>
+  </si>
+  <si>
+    <t>136557207</t>
+  </si>
+  <si>
+    <t>136547441</t>
+  </si>
+  <si>
+    <t>136548421</t>
+  </si>
+  <si>
+    <t>136686595</t>
+  </si>
+  <si>
+    <t>136686647</t>
+  </si>
+  <si>
+    <t>136686865</t>
+  </si>
+  <si>
+    <t>136701065</t>
+  </si>
+  <si>
+    <t>136711054</t>
+  </si>
+  <si>
+    <t>136687804</t>
+  </si>
+  <si>
+    <t>136725142</t>
+  </si>
+  <si>
+    <t>136701052</t>
+  </si>
+  <si>
+    <t>136736079</t>
+  </si>
+  <si>
+    <t>136696105</t>
+  </si>
+  <si>
+    <t>136514573</t>
+  </si>
+  <si>
+    <t>136549558</t>
+  </si>
+  <si>
+    <t>136554174</t>
+  </si>
+  <si>
+    <t>136554343</t>
+  </si>
+  <si>
+    <t>136550120</t>
+  </si>
+  <si>
+    <t>136554222</t>
+  </si>
+  <si>
+    <t>136554481</t>
+  </si>
+  <si>
+    <t>136541688</t>
+  </si>
+  <si>
+    <t>136542246</t>
+  </si>
+  <si>
+    <t>136552889</t>
+  </si>
+  <si>
+    <t>136558288</t>
+  </si>
+  <si>
+    <t>136557020</t>
+  </si>
+  <si>
+    <t>136548180</t>
+  </si>
+  <si>
+    <t>136548954</t>
+  </si>
+  <si>
+    <t>136549583</t>
+  </si>
+  <si>
+    <t>136671706</t>
+  </si>
+  <si>
+    <t>136681885</t>
+  </si>
+  <si>
+    <t>136703302</t>
+  </si>
+  <si>
+    <t>136682631</t>
+  </si>
+  <si>
+    <t>136702745</t>
+  </si>
+  <si>
+    <t>136571096</t>
+  </si>
+  <si>
+    <t>136675029</t>
+  </si>
+  <si>
+    <t>136687148</t>
+  </si>
+  <si>
+    <t>136686959</t>
+  </si>
+  <si>
+    <t>136683782</t>
+  </si>
+  <si>
+    <t>136670378</t>
+  </si>
+  <si>
+    <t>136683716</t>
+  </si>
+  <si>
+    <t>136708579</t>
+  </si>
+  <si>
+    <t>136696709</t>
+  </si>
+  <si>
+    <t>136707767</t>
+  </si>
+  <si>
+    <t>136733342</t>
+  </si>
+  <si>
+    <t>136724116</t>
+  </si>
+  <si>
+    <t>136748802</t>
+  </si>
+  <si>
+    <t>136710324</t>
+  </si>
+  <si>
+    <t>136686242</t>
+  </si>
+  <si>
+    <t>136572459</t>
+  </si>
+  <si>
+    <t>136569056</t>
+  </si>
+  <si>
+    <t>136569386</t>
+  </si>
+  <si>
+    <t>136570438</t>
+  </si>
+  <si>
+    <t>136571192</t>
+  </si>
+  <si>
+    <t>136572723</t>
+  </si>
+  <si>
+    <t>136573627</t>
+  </si>
+  <si>
+    <t>136575156</t>
+  </si>
+  <si>
+    <t>136573032</t>
+  </si>
+  <si>
+    <t>136569235</t>
+  </si>
+  <si>
+    <t>136575978</t>
+  </si>
+  <si>
+    <t>136574171</t>
+  </si>
+  <si>
+    <t>136687461</t>
+  </si>
+  <si>
+    <t>136686689</t>
+  </si>
+  <si>
+    <t>136684622</t>
+  </si>
+  <si>
+    <t>136722545</t>
+  </si>
+  <si>
+    <t>136724329</t>
+  </si>
+  <si>
+    <t>136724918</t>
+  </si>
+  <si>
+    <t>136728841</t>
+  </si>
+  <si>
+    <t>136730227</t>
+  </si>
+  <si>
+    <t>136739187</t>
+  </si>
+  <si>
+    <t>136747666</t>
+  </si>
+  <si>
+    <t>136749195</t>
+  </si>
+  <si>
+    <t>136744044</t>
+  </si>
+  <si>
+    <t>136748213</t>
+  </si>
+  <si>
+    <t>136748379</t>
+  </si>
+  <si>
+    <t>136748867</t>
+  </si>
+  <si>
+    <t>136761482</t>
+  </si>
+  <si>
+    <t>136741385</t>
+  </si>
+  <si>
+    <t>136755051</t>
+  </si>
+  <si>
+    <t>136745088</t>
+  </si>
+  <si>
+    <t>136721452</t>
+  </si>
+  <si>
+    <t>136755908</t>
+  </si>
+  <si>
+    <t>136740515</t>
+  </si>
+  <si>
+    <t>136739587</t>
+  </si>
+  <si>
+    <t>136549549</t>
+  </si>
+  <si>
+    <t>136752033</t>
+  </si>
+  <si>
+    <t>136543826</t>
+  </si>
+  <si>
+    <t>136545172</t>
+  </si>
+  <si>
+    <t>136545819</t>
+  </si>
+  <si>
+    <t>136549891</t>
+  </si>
+  <si>
+    <t>136604273</t>
+  </si>
+  <si>
+    <t>136544042</t>
+  </si>
+  <si>
+    <t>136558887</t>
+  </si>
+  <si>
+    <t>136595307</t>
+  </si>
+  <si>
+    <t>136596976</t>
+  </si>
+  <si>
+    <t>136545719</t>
+  </si>
+  <si>
+    <t>136602127</t>
+  </si>
+  <si>
+    <t>136593178</t>
+  </si>
+  <si>
+    <t>136596150</t>
+  </si>
+  <si>
+    <t>136588070</t>
+  </si>
+  <si>
+    <t>136588326</t>
+  </si>
+  <si>
+    <t>136602284</t>
+  </si>
+  <si>
+    <t>136595818</t>
+  </si>
+  <si>
+    <t>136594179</t>
+  </si>
+  <si>
+    <t>136592823</t>
+  </si>
+  <si>
+    <t>136600847</t>
+  </si>
+  <si>
+    <t>136601877</t>
+  </si>
+  <si>
+    <t>136605337</t>
+  </si>
+  <si>
+    <t>136606322</t>
+  </si>
+  <si>
+    <t>136779703</t>
+  </si>
+  <si>
+    <t>136669857</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 16.02.2026 a 22.02.2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +882,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,140 +913,2394 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136509608</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2390B7-98F5-4376-8D15-509A1F4F2DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87ACD473-D92B-4D80-B3B2-52B9B326E2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="153">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -478,6 +478,15 @@
   </si>
   <si>
     <t>Relatório de Recusas 16.02.2026 a 22.02.2026</t>
+  </si>
+  <si>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; Relatório de Recusas 09.02.2026 a 15.02.2026.xlsx.</t>
+  </si>
+  <si>
+    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; Relatório de Recusas 16.02.2026 a 22.02.2026.xlsx.</t>
   </si>
 </sst>
 </file>
@@ -926,9 +935,11 @@
         <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2"/>
+        <v>150</v>
+      </c>
+      <c r="F2" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -944,9 +955,11 @@
         <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3"/>
+        <v>150</v>
+      </c>
+      <c r="F3" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -962,9 +975,11 @@
         <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4"/>
+        <v>150</v>
+      </c>
+      <c r="F4" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -980,9 +995,11 @@
         <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5"/>
+        <v>150</v>
+      </c>
+      <c r="F5" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -998,9 +1015,11 @@
         <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6"/>
+        <v>150</v>
+      </c>
+      <c r="F6" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -1016,9 +1035,11 @@
         <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7"/>
+        <v>150</v>
+      </c>
+      <c r="F7" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1034,9 +1055,11 @@
         <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8"/>
+        <v>150</v>
+      </c>
+      <c r="F8" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -1052,9 +1075,11 @@
         <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9"/>
+        <v>150</v>
+      </c>
+      <c r="F9" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1070,9 +1095,11 @@
         <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10"/>
+        <v>150</v>
+      </c>
+      <c r="F10" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1088,9 +1115,11 @@
         <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11"/>
+        <v>150</v>
+      </c>
+      <c r="F11" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -1106,9 +1135,11 @@
         <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12"/>
+        <v>150</v>
+      </c>
+      <c r="F12" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1124,9 +1155,11 @@
         <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13"/>
+        <v>150</v>
+      </c>
+      <c r="F13" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1142,9 +1175,11 @@
         <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14"/>
+        <v>150</v>
+      </c>
+      <c r="F14" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1160,9 +1195,11 @@
         <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15"/>
+        <v>150</v>
+      </c>
+      <c r="F15" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1178,9 +1215,11 @@
         <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16"/>
+        <v>150</v>
+      </c>
+      <c r="F16" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -1196,9 +1235,11 @@
         <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17"/>
+        <v>150</v>
+      </c>
+      <c r="F17" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -1214,9 +1255,11 @@
         <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18"/>
+        <v>150</v>
+      </c>
+      <c r="F18" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -1232,9 +1275,11 @@
         <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19"/>
+        <v>150</v>
+      </c>
+      <c r="F19" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -1250,9 +1295,11 @@
         <v>36</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20"/>
+        <v>150</v>
+      </c>
+      <c r="F20" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -1268,9 +1315,11 @@
         <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21"/>
+        <v>150</v>
+      </c>
+      <c r="F21" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -1286,9 +1335,11 @@
         <v>36</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22"/>
+        <v>150</v>
+      </c>
+      <c r="F22" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -1304,9 +1355,11 @@
         <v>36</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23"/>
+        <v>150</v>
+      </c>
+      <c r="F23" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -1322,9 +1375,11 @@
         <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24"/>
+        <v>150</v>
+      </c>
+      <c r="F24" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -1340,9 +1395,11 @@
         <v>36</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
+        <v>150</v>
+      </c>
+      <c r="F25" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -1358,9 +1415,11 @@
         <v>36</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26"/>
+        <v>150</v>
+      </c>
+      <c r="F26" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -1376,9 +1435,11 @@
         <v>36</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27"/>
+        <v>150</v>
+      </c>
+      <c r="F27" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -1394,9 +1455,11 @@
         <v>36</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28"/>
+        <v>150</v>
+      </c>
+      <c r="F28" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -1412,7 +1475,10 @@
         <v>36</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>6</v>
+        <v>150</v>
+      </c>
+      <c r="F29" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1429,7 +1495,10 @@
         <v>149</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>6</v>
+        <v>150</v>
+      </c>
+      <c r="F30" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1446,7 +1515,10 @@
         <v>149</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>6</v>
+        <v>150</v>
+      </c>
+      <c r="F31" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1463,10 +1535,13 @@
         <v>149</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F32" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
@@ -1480,10 +1555,13 @@
         <v>149</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F33" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>42</v>
       </c>
@@ -1497,10 +1575,13 @@
         <v>149</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F34" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>43</v>
       </c>
@@ -1514,10 +1595,13 @@
         <v>149</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F35" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>44</v>
       </c>
@@ -1531,10 +1615,13 @@
         <v>149</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>45</v>
       </c>
@@ -1548,10 +1635,13 @@
         <v>149</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F37" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
@@ -1565,10 +1655,13 @@
         <v>149</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F38" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>47</v>
       </c>
@@ -1582,10 +1675,13 @@
         <v>149</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F39" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
@@ -1599,10 +1695,13 @@
         <v>149</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F40" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>49</v>
       </c>
@@ -1616,10 +1715,13 @@
         <v>149</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F41" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>50</v>
       </c>
@@ -1633,10 +1735,13 @@
         <v>149</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F42" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>51</v>
       </c>
@@ -1650,10 +1755,13 @@
         <v>149</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F43" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>52</v>
       </c>
@@ -1667,10 +1775,13 @@
         <v>149</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F44" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>53</v>
       </c>
@@ -1684,10 +1795,13 @@
         <v>149</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F45" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>54</v>
       </c>
@@ -1701,10 +1815,13 @@
         <v>149</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F46" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>55</v>
       </c>
@@ -1718,10 +1835,13 @@
         <v>149</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F47" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>56</v>
       </c>
@@ -1735,10 +1855,13 @@
         <v>149</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F48" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>57</v>
       </c>
@@ -1752,10 +1875,13 @@
         <v>149</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F49" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>58</v>
       </c>
@@ -1769,10 +1895,13 @@
         <v>149</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F50" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>59</v>
       </c>
@@ -1786,10 +1915,13 @@
         <v>149</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F51" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>60</v>
       </c>
@@ -1803,10 +1935,13 @@
         <v>149</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F52" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>61</v>
       </c>
@@ -1820,10 +1955,13 @@
         <v>149</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F53" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>62</v>
       </c>
@@ -1837,10 +1975,13 @@
         <v>149</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F54" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>63</v>
       </c>
@@ -1854,10 +1995,13 @@
         <v>149</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F55" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>64</v>
       </c>
@@ -1871,10 +2015,13 @@
         <v>149</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F56" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>65</v>
       </c>
@@ -1888,10 +2035,13 @@
         <v>149</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F57" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>66</v>
       </c>
@@ -1905,10 +2055,13 @@
         <v>149</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F58" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>67</v>
       </c>
@@ -1922,10 +2075,13 @@
         <v>149</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F59" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>68</v>
       </c>
@@ -1939,10 +2095,13 @@
         <v>149</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F60" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>69</v>
       </c>
@@ -1956,10 +2115,13 @@
         <v>149</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F61" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>70</v>
       </c>
@@ -1973,10 +2135,13 @@
         <v>149</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F62" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>71</v>
       </c>
@@ -1990,10 +2155,13 @@
         <v>149</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F63" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>72</v>
       </c>
@@ -2007,10 +2175,13 @@
         <v>149</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F64" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>73</v>
       </c>
@@ -2024,10 +2195,13 @@
         <v>149</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F65" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>74</v>
       </c>
@@ -2041,10 +2215,13 @@
         <v>149</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F66" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>75</v>
       </c>
@@ -2058,10 +2235,13 @@
         <v>149</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F67" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>76</v>
       </c>
@@ -2075,10 +2255,13 @@
         <v>149</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F68" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>77</v>
       </c>
@@ -2092,10 +2275,13 @@
         <v>149</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F69" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>78</v>
       </c>
@@ -2109,10 +2295,13 @@
         <v>149</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F70" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>79</v>
       </c>
@@ -2126,10 +2315,13 @@
         <v>149</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F71" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>80</v>
       </c>
@@ -2143,10 +2335,13 @@
         <v>149</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F72" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>81</v>
       </c>
@@ -2160,10 +2355,13 @@
         <v>149</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F73" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>82</v>
       </c>
@@ -2177,10 +2375,13 @@
         <v>149</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F74" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>83</v>
       </c>
@@ -2194,10 +2395,13 @@
         <v>149</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F75" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>84</v>
       </c>
@@ -2211,10 +2415,13 @@
         <v>149</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F76" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>85</v>
       </c>
@@ -2228,10 +2435,13 @@
         <v>149</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F77" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>86</v>
       </c>
@@ -2245,10 +2455,13 @@
         <v>149</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F78" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>87</v>
       </c>
@@ -2262,10 +2475,13 @@
         <v>149</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F79" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>88</v>
       </c>
@@ -2279,10 +2495,13 @@
         <v>149</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F80" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>89</v>
       </c>
@@ -2296,10 +2515,13 @@
         <v>149</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F81" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>90</v>
       </c>
@@ -2313,10 +2535,13 @@
         <v>149</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F82" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>91</v>
       </c>
@@ -2330,10 +2555,13 @@
         <v>149</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F83" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>92</v>
       </c>
@@ -2347,10 +2575,13 @@
         <v>149</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F84" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>93</v>
       </c>
@@ -2364,10 +2595,13 @@
         <v>149</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F85" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>94</v>
       </c>
@@ -2381,10 +2615,13 @@
         <v>149</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F86" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>95</v>
       </c>
@@ -2398,10 +2635,13 @@
         <v>149</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F87" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>96</v>
       </c>
@@ -2415,10 +2655,13 @@
         <v>149</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F88" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>97</v>
       </c>
@@ -2432,10 +2675,13 @@
         <v>149</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F89" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>98</v>
       </c>
@@ -2449,10 +2695,13 @@
         <v>149</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F90" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>99</v>
       </c>
@@ -2466,10 +2715,13 @@
         <v>149</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F91" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>100</v>
       </c>
@@ -2483,10 +2735,13 @@
         <v>149</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F92" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>101</v>
       </c>
@@ -2500,10 +2755,13 @@
         <v>149</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F93" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>102</v>
       </c>
@@ -2517,10 +2775,13 @@
         <v>149</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F94" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>103</v>
       </c>
@@ -2534,10 +2795,13 @@
         <v>149</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F95" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>104</v>
       </c>
@@ -2551,10 +2815,13 @@
         <v>149</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F96" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>105</v>
       </c>
@@ -2568,10 +2835,13 @@
         <v>149</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F97" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>106</v>
       </c>
@@ -2585,10 +2855,13 @@
         <v>149</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F98" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>107</v>
       </c>
@@ -2602,10 +2875,13 @@
         <v>149</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F99" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>108</v>
       </c>
@@ -2619,10 +2895,13 @@
         <v>149</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F100" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>109</v>
       </c>
@@ -2636,10 +2915,13 @@
         <v>149</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F101" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>110</v>
       </c>
@@ -2653,10 +2935,13 @@
         <v>149</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F102" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>111</v>
       </c>
@@ -2670,10 +2955,13 @@
         <v>149</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F103" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>112</v>
       </c>
@@ -2687,10 +2975,13 @@
         <v>149</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F104" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>113</v>
       </c>
@@ -2704,10 +2995,13 @@
         <v>149</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F105" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>114</v>
       </c>
@@ -2721,10 +3015,13 @@
         <v>149</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F106" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>115</v>
       </c>
@@ -2738,10 +3035,13 @@
         <v>149</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F107" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>116</v>
       </c>
@@ -2755,10 +3055,13 @@
         <v>149</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F108" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>117</v>
       </c>
@@ -2772,10 +3075,13 @@
         <v>149</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F109" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>118</v>
       </c>
@@ -2789,10 +3095,13 @@
         <v>149</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F110" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>119</v>
       </c>
@@ -2808,8 +3117,9 @@
       <c r="E111" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F111"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>120</v>
       </c>
@@ -2823,10 +3133,13 @@
         <v>149</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F112" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>121</v>
       </c>
@@ -2840,10 +3153,13 @@
         <v>149</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F113" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>122</v>
       </c>
@@ -2857,10 +3173,13 @@
         <v>149</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F114" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>123</v>
       </c>
@@ -2874,10 +3193,13 @@
         <v>149</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F115" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>124</v>
       </c>
@@ -2891,10 +3213,13 @@
         <v>149</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F116" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>125</v>
       </c>
@@ -2908,10 +3233,13 @@
         <v>149</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F117" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>126</v>
       </c>
@@ -2925,10 +3253,13 @@
         <v>149</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F118" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>127</v>
       </c>
@@ -2942,10 +3273,13 @@
         <v>149</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F119" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>128</v>
       </c>
@@ -2959,10 +3293,13 @@
         <v>149</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F120" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>129</v>
       </c>
@@ -2976,10 +3313,13 @@
         <v>149</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F121" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>130</v>
       </c>
@@ -2993,10 +3333,13 @@
         <v>149</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F122" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>131</v>
       </c>
@@ -3010,10 +3353,13 @@
         <v>149</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F123" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>132</v>
       </c>
@@ -3027,10 +3373,13 @@
         <v>149</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F124" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>133</v>
       </c>
@@ -3044,10 +3393,13 @@
         <v>149</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F125" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>134</v>
       </c>
@@ -3061,10 +3413,13 @@
         <v>149</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F126" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>135</v>
       </c>
@@ -3078,10 +3433,13 @@
         <v>149</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F127" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>136</v>
       </c>
@@ -3095,10 +3453,13 @@
         <v>149</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F128" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>137</v>
       </c>
@@ -3112,10 +3473,13 @@
         <v>149</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F129" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>138</v>
       </c>
@@ -3129,10 +3493,13 @@
         <v>149</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F130" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>139</v>
       </c>
@@ -3146,10 +3513,13 @@
         <v>149</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F131" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>140</v>
       </c>
@@ -3163,10 +3533,13 @@
         <v>149</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F132" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>141</v>
       </c>
@@ -3180,10 +3553,13 @@
         <v>149</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F133" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>142</v>
       </c>
@@ -3197,10 +3573,13 @@
         <v>149</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F134" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>143</v>
       </c>
@@ -3214,10 +3593,13 @@
         <v>149</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F135" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>144</v>
       </c>
@@ -3231,10 +3613,13 @@
         <v>149</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F136" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>145</v>
       </c>
@@ -3248,10 +3633,13 @@
         <v>149</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F137" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>146</v>
       </c>
@@ -3265,10 +3653,13 @@
         <v>149</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F138" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>147</v>
       </c>
@@ -3282,10 +3673,13 @@
         <v>149</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="F139" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>148</v>
       </c>
@@ -3299,7 +3693,10 @@
         <v>149</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>6</v>
+        <v>150</v>
+      </c>
+      <c r="F140" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -3316,31 +3713,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{50D4D769-59D2-4539-892C-30D34C610329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B714D943-E536-453A-BA81-C35EED699EB5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7644B96D-B87C-437F-B4C7-A0C013621230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="56">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,153 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 19.02.2026</t>
+  </si>
+  <si>
+    <t>136621478</t>
+  </si>
+  <si>
+    <t>136658089</t>
+  </si>
+  <si>
+    <t>136682550</t>
+  </si>
+  <si>
+    <t>136721957</t>
+  </si>
+  <si>
+    <t>136762538</t>
+  </si>
+  <si>
+    <t>136757501</t>
+  </si>
+  <si>
+    <t>136755253</t>
+  </si>
+  <si>
+    <t>136753540</t>
+  </si>
+  <si>
+    <t>136748187</t>
+  </si>
+  <si>
+    <t>136758012</t>
+  </si>
+  <si>
+    <t>136766053</t>
+  </si>
+  <si>
+    <t>136788956</t>
+  </si>
+  <si>
+    <t>136569496</t>
+  </si>
+  <si>
+    <t>136569527</t>
+  </si>
+  <si>
+    <t>136569553</t>
+  </si>
+  <si>
+    <t>136569567</t>
+  </si>
+  <si>
+    <t>136570256</t>
+  </si>
+  <si>
+    <t>136570599</t>
+  </si>
+  <si>
+    <t>136570660</t>
+  </si>
+  <si>
+    <t>136571129</t>
+  </si>
+  <si>
+    <t>136571317</t>
+  </si>
+  <si>
+    <t>136571602</t>
+  </si>
+  <si>
+    <t>136577670</t>
+  </si>
+  <si>
+    <t>136578716</t>
+  </si>
+  <si>
+    <t>136578778</t>
+  </si>
+  <si>
+    <t>136619406</t>
+  </si>
+  <si>
+    <t>136749654</t>
+  </si>
+  <si>
+    <t>136739997</t>
+  </si>
+  <si>
+    <t>136569878</t>
+  </si>
+  <si>
+    <t>136572495</t>
+  </si>
+  <si>
+    <t>136577440</t>
+  </si>
+  <si>
+    <t>136571743</t>
+  </si>
+  <si>
+    <t>136576445</t>
+  </si>
+  <si>
+    <t>136577715</t>
+  </si>
+  <si>
+    <t>136579286</t>
+  </si>
+  <si>
+    <t>136577078</t>
+  </si>
+  <si>
+    <t>136579946</t>
+  </si>
+  <si>
+    <t>136754106</t>
+  </si>
+  <si>
+    <t>136795187</t>
+  </si>
+  <si>
+    <t>136627284</t>
+  </si>
+  <si>
+    <t>136744434</t>
+  </si>
+  <si>
+    <t>136619608</t>
+  </si>
+  <si>
+    <t>136593917</t>
+  </si>
+  <si>
+    <t>136798716</t>
+  </si>
+  <si>
+    <t>136685344</t>
+  </si>
+  <si>
+    <t>136606688</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 16.02.2026 a 22.02.2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +600,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,140 +631,830 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136606089</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -633,31 +1470,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{50D4D769-59D2-4539-892C-30D34C610329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B714D943-E536-453A-BA81-C35EED699EB5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159EC9D4-BE91-4994-8A1A-E52DAA3706A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="74">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,207 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 23.02.2026</t>
+  </si>
+  <si>
+    <t>136703723</t>
+  </si>
+  <si>
+    <t>136702771</t>
+  </si>
+  <si>
+    <t>136709355</t>
+  </si>
+  <si>
+    <t>136711910</t>
+  </si>
+  <si>
+    <t>136650596</t>
+  </si>
+  <si>
+    <t>136653043</t>
+  </si>
+  <si>
+    <t>136695554</t>
+  </si>
+  <si>
+    <t>136696152</t>
+  </si>
+  <si>
+    <t>136698227</t>
+  </si>
+  <si>
+    <t>136699763</t>
+  </si>
+  <si>
+    <t>136701112</t>
+  </si>
+  <si>
+    <t>136701862</t>
+  </si>
+  <si>
+    <t>136702698</t>
+  </si>
+  <si>
+    <t>136703294</t>
+  </si>
+  <si>
+    <t>136703949</t>
+  </si>
+  <si>
+    <t>136705066</t>
+  </si>
+  <si>
+    <t>136706584</t>
+  </si>
+  <si>
+    <t>136709051</t>
+  </si>
+  <si>
+    <t>136709458</t>
+  </si>
+  <si>
+    <t>136710590</t>
+  </si>
+  <si>
+    <t>136712058</t>
+  </si>
+  <si>
+    <t>136712893</t>
+  </si>
+  <si>
+    <t>136713212</t>
+  </si>
+  <si>
+    <t>136713293</t>
+  </si>
+  <si>
+    <t>136780424</t>
+  </si>
+  <si>
+    <t>136757725</t>
+  </si>
+  <si>
+    <t>136793836</t>
+  </si>
+  <si>
+    <t>136726098</t>
+  </si>
+  <si>
+    <t>136751753</t>
+  </si>
+  <si>
+    <t>136741623</t>
+  </si>
+  <si>
+    <t>136741773</t>
+  </si>
+  <si>
+    <t>136743307</t>
+  </si>
+  <si>
+    <t>136745446</t>
+  </si>
+  <si>
+    <t>136745892</t>
+  </si>
+  <si>
+    <t>136746253</t>
+  </si>
+  <si>
+    <t>136747220</t>
+  </si>
+  <si>
+    <t>136747223</t>
+  </si>
+  <si>
+    <t>136747238</t>
+  </si>
+  <si>
+    <t>136748548</t>
+  </si>
+  <si>
+    <t>136748679</t>
+  </si>
+  <si>
+    <t>136749016</t>
+  </si>
+  <si>
+    <t>136749185</t>
+  </si>
+  <si>
+    <t>136749240</t>
+  </si>
+  <si>
+    <t>136749297</t>
+  </si>
+  <si>
+    <t>136749595</t>
+  </si>
+  <si>
+    <t>136749625</t>
+  </si>
+  <si>
+    <t>136750369</t>
+  </si>
+  <si>
+    <t>136751442</t>
+  </si>
+  <si>
+    <t>136752831</t>
+  </si>
+  <si>
+    <t>136754474</t>
+  </si>
+  <si>
+    <t>136754971</t>
+  </si>
+  <si>
+    <t>136755061</t>
+  </si>
+  <si>
+    <t>136756419</t>
+  </si>
+  <si>
+    <t>136756531</t>
+  </si>
+  <si>
+    <t>136759573</t>
+  </si>
+  <si>
+    <t>136759623</t>
+  </si>
+  <si>
+    <t>136760271</t>
+  </si>
+  <si>
+    <t>136760300</t>
+  </si>
+  <si>
+    <t>136761612</t>
+  </si>
+  <si>
+    <t>136761764</t>
+  </si>
+  <si>
+    <t>136761926</t>
+  </si>
+  <si>
+    <t>136761966</t>
+  </si>
+  <si>
+    <t>136762270</t>
+  </si>
+  <si>
+    <t>136762890</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 23.02.2026 a 01.03.2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +654,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,140 +685,1136 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136644540</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -633,31 +1830,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159EC9D4-BE91-4994-8A1A-E52DAA3706A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82BFEBE-AD9F-4879-8812-3E21CBEF77F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="59">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,199 +54,154 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 23.02.2026</t>
-  </si>
-  <si>
-    <t>136703723</t>
-  </si>
-  <si>
-    <t>136702771</t>
-  </si>
-  <si>
-    <t>136709355</t>
-  </si>
-  <si>
-    <t>136711910</t>
-  </si>
-  <si>
-    <t>136650596</t>
-  </si>
-  <si>
-    <t>136653043</t>
-  </si>
-  <si>
-    <t>136695554</t>
-  </si>
-  <si>
-    <t>136696152</t>
-  </si>
-  <si>
-    <t>136698227</t>
-  </si>
-  <si>
-    <t>136699763</t>
-  </si>
-  <si>
-    <t>136701112</t>
-  </si>
-  <si>
-    <t>136701862</t>
-  </si>
-  <si>
-    <t>136702698</t>
-  </si>
-  <si>
-    <t>136703294</t>
-  </si>
-  <si>
-    <t>136703949</t>
-  </si>
-  <si>
-    <t>136705066</t>
-  </si>
-  <si>
-    <t>136706584</t>
-  </si>
-  <si>
-    <t>136709051</t>
-  </si>
-  <si>
-    <t>136709458</t>
-  </si>
-  <si>
-    <t>136710590</t>
-  </si>
-  <si>
-    <t>136712058</t>
-  </si>
-  <si>
-    <t>136712893</t>
-  </si>
-  <si>
-    <t>136713212</t>
-  </si>
-  <si>
-    <t>136713293</t>
-  </si>
-  <si>
-    <t>136780424</t>
-  </si>
-  <si>
-    <t>136757725</t>
-  </si>
-  <si>
-    <t>136793836</t>
-  </si>
-  <si>
-    <t>136726098</t>
-  </si>
-  <si>
-    <t>136751753</t>
-  </si>
-  <si>
-    <t>136741623</t>
-  </si>
-  <si>
-    <t>136741773</t>
-  </si>
-  <si>
-    <t>136743307</t>
-  </si>
-  <si>
-    <t>136745446</t>
-  </si>
-  <si>
-    <t>136745892</t>
-  </si>
-  <si>
-    <t>136746253</t>
-  </si>
-  <si>
-    <t>136747220</t>
-  </si>
-  <si>
-    <t>136747223</t>
-  </si>
-  <si>
-    <t>136747238</t>
-  </si>
-  <si>
-    <t>136748548</t>
-  </si>
-  <si>
-    <t>136748679</t>
-  </si>
-  <si>
-    <t>136749016</t>
-  </si>
-  <si>
-    <t>136749185</t>
-  </si>
-  <si>
-    <t>136749240</t>
-  </si>
-  <si>
-    <t>136749297</t>
-  </si>
-  <si>
-    <t>136749595</t>
-  </si>
-  <si>
-    <t>136749625</t>
-  </si>
-  <si>
-    <t>136750369</t>
-  </si>
-  <si>
-    <t>136751442</t>
-  </si>
-  <si>
-    <t>136752831</t>
-  </si>
-  <si>
-    <t>136754474</t>
-  </si>
-  <si>
-    <t>136754971</t>
-  </si>
-  <si>
-    <t>136755061</t>
-  </si>
-  <si>
-    <t>136756419</t>
-  </si>
-  <si>
-    <t>136756531</t>
-  </si>
-  <si>
-    <t>136759573</t>
-  </si>
-  <si>
-    <t>136759623</t>
-  </si>
-  <si>
-    <t>136760271</t>
-  </si>
-  <si>
-    <t>136760300</t>
-  </si>
-  <si>
-    <t>136761612</t>
-  </si>
-  <si>
-    <t>136761764</t>
-  </si>
-  <si>
-    <t>136761926</t>
-  </si>
-  <si>
-    <t>136761966</t>
-  </si>
-  <si>
-    <t>136762270</t>
-  </si>
-  <si>
-    <t>136762890</t>
+    <t>Relatório de Recusas Santander - 24.02.2026</t>
+  </si>
+  <si>
+    <t>136728307</t>
+  </si>
+  <si>
+    <t>136734997</t>
+  </si>
+  <si>
+    <t>136722223</t>
+  </si>
+  <si>
+    <t>136724519</t>
+  </si>
+  <si>
+    <t>136735180</t>
+  </si>
+  <si>
+    <t>136723934</t>
+  </si>
+  <si>
+    <t>136729172</t>
+  </si>
+  <si>
+    <t>136725270</t>
+  </si>
+  <si>
+    <t>136723951</t>
+  </si>
+  <si>
+    <t>136726576</t>
+  </si>
+  <si>
+    <t>136724366</t>
+  </si>
+  <si>
+    <t>136730089</t>
+  </si>
+  <si>
+    <t>136724217</t>
+  </si>
+  <si>
+    <t>136724245</t>
+  </si>
+  <si>
+    <t>136673325</t>
+  </si>
+  <si>
+    <t>136724805</t>
+  </si>
+  <si>
+    <t>136679933</t>
+  </si>
+  <si>
+    <t>136679581</t>
+  </si>
+  <si>
+    <t>136681490</t>
+  </si>
+  <si>
+    <t>136722921</t>
+  </si>
+  <si>
+    <t>136733403</t>
+  </si>
+  <si>
+    <t>136733601</t>
+  </si>
+  <si>
+    <t>136733681</t>
+  </si>
+  <si>
+    <t>136733785</t>
+  </si>
+  <si>
+    <t>136727335</t>
+  </si>
+  <si>
+    <t>136734786</t>
+  </si>
+  <si>
+    <t>136736493</t>
+  </si>
+  <si>
+    <t>136735931</t>
+  </si>
+  <si>
+    <t>136727233</t>
+  </si>
+  <si>
+    <t>136730654</t>
+  </si>
+  <si>
+    <t>136730967</t>
+  </si>
+  <si>
+    <t>136731705</t>
+  </si>
+  <si>
+    <t>136733115</t>
+  </si>
+  <si>
+    <t>136733202</t>
+  </si>
+  <si>
+    <t>136734975</t>
+  </si>
+  <si>
+    <t>136735098</t>
+  </si>
+  <si>
+    <t>136667128</t>
+  </si>
+  <si>
+    <t>136669978</t>
+  </si>
+  <si>
+    <t>136689136</t>
+  </si>
+  <si>
+    <t>136723546</t>
+  </si>
+  <si>
+    <t>136723669</t>
+  </si>
+  <si>
+    <t>136725436</t>
+  </si>
+  <si>
+    <t>136725702</t>
+  </si>
+  <si>
+    <t>136740470</t>
+  </si>
+  <si>
+    <t>136823048</t>
+  </si>
+  <si>
+    <t>136816299</t>
+  </si>
+  <si>
+    <t>136825656</t>
+  </si>
+  <si>
+    <t>136757414</t>
+  </si>
+  <si>
+    <t>136804031</t>
   </si>
   <si>
     <t>Relatório de Recusas 23.02.2026 a 01.03.2026</t>
@@ -654,7 +609,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -686,7 +641,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136644540</v>
+        <v>136838916</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -695,7 +650,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -713,7 +668,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -731,7 +686,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -749,7 +704,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -767,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -785,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -803,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -821,7 +776,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -839,7 +794,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -857,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -875,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -893,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -911,7 +866,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -929,7 +884,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -947,7 +902,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -965,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -983,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1001,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1019,7 +974,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1037,7 +992,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1055,7 +1010,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1073,7 +1028,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1091,7 +1046,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1109,7 +1064,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1127,7 +1082,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1145,7 +1100,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1163,7 +1118,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1181,7 +1136,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1198,7 +1153,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1215,7 +1170,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1232,7 +1187,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1249,7 +1204,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1266,7 +1221,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1283,7 +1238,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1300,7 +1255,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1317,7 +1272,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1334,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1351,7 +1306,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1368,7 +1323,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1385,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1402,7 +1357,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1419,7 +1374,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1436,7 +1391,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1453,7 +1408,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1470,7 +1425,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1487,7 +1442,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1504,7 +1459,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1521,7 +1476,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1538,7 +1493,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1555,264 +1510,9 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E66" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82BFEBE-AD9F-4879-8812-3E21CBEF77F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E917102D-786D-45C7-9035-203133097948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="43">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,157 +54,109 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 24.02.2026</t>
-  </si>
-  <si>
-    <t>136728307</t>
-  </si>
-  <si>
-    <t>136734997</t>
-  </si>
-  <si>
-    <t>136722223</t>
-  </si>
-  <si>
-    <t>136724519</t>
-  </si>
-  <si>
-    <t>136735180</t>
-  </si>
-  <si>
-    <t>136723934</t>
-  </si>
-  <si>
-    <t>136729172</t>
-  </si>
-  <si>
-    <t>136725270</t>
-  </si>
-  <si>
-    <t>136723951</t>
-  </si>
-  <si>
-    <t>136726576</t>
-  </si>
-  <si>
-    <t>136724366</t>
-  </si>
-  <si>
-    <t>136730089</t>
-  </si>
-  <si>
-    <t>136724217</t>
-  </si>
-  <si>
-    <t>136724245</t>
-  </si>
-  <si>
-    <t>136673325</t>
-  </si>
-  <si>
-    <t>136724805</t>
-  </si>
-  <si>
-    <t>136679933</t>
-  </si>
-  <si>
-    <t>136679581</t>
-  </si>
-  <si>
-    <t>136681490</t>
-  </si>
-  <si>
-    <t>136722921</t>
-  </si>
-  <si>
-    <t>136733403</t>
-  </si>
-  <si>
-    <t>136733601</t>
-  </si>
-  <si>
-    <t>136733681</t>
-  </si>
-  <si>
-    <t>136733785</t>
-  </si>
-  <si>
-    <t>136727335</t>
-  </si>
-  <si>
-    <t>136734786</t>
-  </si>
-  <si>
-    <t>136736493</t>
-  </si>
-  <si>
-    <t>136735931</t>
-  </si>
-  <si>
-    <t>136727233</t>
-  </si>
-  <si>
-    <t>136730654</t>
-  </si>
-  <si>
-    <t>136730967</t>
-  </si>
-  <si>
-    <t>136731705</t>
-  </si>
-  <si>
-    <t>136733115</t>
-  </si>
-  <si>
-    <t>136733202</t>
-  </si>
-  <si>
-    <t>136734975</t>
-  </si>
-  <si>
-    <t>136735098</t>
-  </si>
-  <si>
-    <t>136667128</t>
-  </si>
-  <si>
-    <t>136669978</t>
-  </si>
-  <si>
-    <t>136689136</t>
-  </si>
-  <si>
-    <t>136723546</t>
-  </si>
-  <si>
-    <t>136723669</t>
-  </si>
-  <si>
-    <t>136725436</t>
-  </si>
-  <si>
-    <t>136725702</t>
-  </si>
-  <si>
-    <t>136740470</t>
-  </si>
-  <si>
-    <t>136823048</t>
-  </si>
-  <si>
-    <t>136816299</t>
-  </si>
-  <si>
-    <t>136825656</t>
-  </si>
-  <si>
-    <t>136757414</t>
-  </si>
-  <si>
-    <t>136804031</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 23.02.2026 a 01.03.2026</t>
+    <t>Relatório de Recusas Santander - 25.02.2026</t>
+  </si>
+  <si>
+    <t>136694861</t>
+  </si>
+  <si>
+    <t>136754447</t>
+  </si>
+  <si>
+    <t>136708451</t>
+  </si>
+  <si>
+    <t>136698193</t>
+  </si>
+  <si>
+    <t>136751455</t>
+  </si>
+  <si>
+    <t>136742229</t>
+  </si>
+  <si>
+    <t>136740126</t>
+  </si>
+  <si>
+    <t>136740300</t>
+  </si>
+  <si>
+    <t>136751006</t>
+  </si>
+  <si>
+    <t>136755188</t>
+  </si>
+  <si>
+    <t>136757699</t>
+  </si>
+  <si>
+    <t>136762893</t>
+  </si>
+  <si>
+    <t>136705225</t>
+  </si>
+  <si>
+    <t>136739201</t>
+  </si>
+  <si>
+    <t>136739218</t>
+  </si>
+  <si>
+    <t>136723533</t>
+  </si>
+  <si>
+    <t>136806525</t>
+  </si>
+  <si>
+    <t>136808710</t>
+  </si>
+  <si>
+    <t>136730296</t>
+  </si>
+  <si>
+    <t>136841851</t>
+  </si>
+  <si>
+    <t>136832984</t>
+  </si>
+  <si>
+    <t>136809532</t>
+  </si>
+  <si>
+    <t>136798798</t>
+  </si>
+  <si>
+    <t>136821098</t>
+  </si>
+  <si>
+    <t>136786742</t>
+  </si>
+  <si>
+    <t>136784554</t>
+  </si>
+  <si>
+    <t>136799830</t>
+  </si>
+  <si>
+    <t>136803511</t>
+  </si>
+  <si>
+    <t>136784744</t>
+  </si>
+  <si>
+    <t>136798825</t>
+  </si>
+  <si>
+    <t>136791856</t>
+  </si>
+  <si>
+    <t>136795898</t>
+  </si>
+  <si>
+    <t>136801483</t>
+  </si>
+  <si>
+    <t>BLOQUEIOS HONDA 25.02.2026</t>
   </si>
 </sst>
 </file>
@@ -609,7 +561,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -641,7 +593,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136838916</v>
+        <v>136739463</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -650,7 +602,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -668,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -686,7 +638,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -704,7 +656,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -722,7 +674,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -740,7 +692,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -758,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -776,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -794,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -812,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -830,7 +782,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -848,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -866,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -884,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -902,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -920,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -938,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -956,7 +908,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -974,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -992,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1010,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1028,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1046,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1064,7 +1016,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1082,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1100,7 +1052,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1118,7 +1070,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1136,7 +1088,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1153,7 +1105,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1170,7 +1122,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1187,7 +1139,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1204,7 +1156,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1221,7 +1173,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1238,281 +1190,9 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E51" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E917102D-786D-45C7-9035-203133097948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C49F044-24CE-421C-9DBE-9735FDA168A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -156,7 +156,7 @@
     <t>136801483</t>
   </si>
   <si>
-    <t>BLOQUEIOS HONDA 25.02.2026</t>
+    <t>Relatório de Recusas 23.02.2026 a 01.03.2026</t>
   </si>
 </sst>
 </file>
@@ -1210,31 +1210,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C49F044-24CE-421C-9DBE-9735FDA168A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BD81A0-B131-4C3E-8462-71F1AC5F8329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,106 +54,88 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 25.02.2026</t>
-  </si>
-  <si>
-    <t>136694861</t>
-  </si>
-  <si>
-    <t>136754447</t>
-  </si>
-  <si>
-    <t>136708451</t>
-  </si>
-  <si>
-    <t>136698193</t>
-  </si>
-  <si>
-    <t>136751455</t>
-  </si>
-  <si>
-    <t>136742229</t>
-  </si>
-  <si>
-    <t>136740126</t>
-  </si>
-  <si>
-    <t>136740300</t>
-  </si>
-  <si>
-    <t>136751006</t>
-  </si>
-  <si>
-    <t>136755188</t>
-  </si>
-  <si>
-    <t>136757699</t>
-  </si>
-  <si>
-    <t>136762893</t>
-  </si>
-  <si>
-    <t>136705225</t>
-  </si>
-  <si>
-    <t>136739201</t>
-  </si>
-  <si>
-    <t>136739218</t>
-  </si>
-  <si>
-    <t>136723533</t>
-  </si>
-  <si>
-    <t>136806525</t>
-  </si>
-  <si>
-    <t>136808710</t>
-  </si>
-  <si>
-    <t>136730296</t>
-  </si>
-  <si>
-    <t>136841851</t>
-  </si>
-  <si>
-    <t>136832984</t>
-  </si>
-  <si>
-    <t>136809532</t>
-  </si>
-  <si>
-    <t>136798798</t>
-  </si>
-  <si>
-    <t>136821098</t>
-  </si>
-  <si>
-    <t>136786742</t>
-  </si>
-  <si>
-    <t>136784554</t>
-  </si>
-  <si>
-    <t>136799830</t>
-  </si>
-  <si>
-    <t>136803511</t>
-  </si>
-  <si>
-    <t>136784744</t>
-  </si>
-  <si>
-    <t>136798825</t>
-  </si>
-  <si>
-    <t>136791856</t>
-  </si>
-  <si>
-    <t>136795898</t>
-  </si>
-  <si>
-    <t>136801483</t>
+    <t>Relatório de Recusas Santander - 26.02.2026</t>
+  </si>
+  <si>
+    <t>136722239</t>
+  </si>
+  <si>
+    <t>136731087</t>
+  </si>
+  <si>
+    <t>136736113</t>
+  </si>
+  <si>
+    <t>136728596</t>
+  </si>
+  <si>
+    <t>136793825</t>
+  </si>
+  <si>
+    <t>136803786</t>
+  </si>
+  <si>
+    <t>136791849</t>
+  </si>
+  <si>
+    <t>136781844</t>
+  </si>
+  <si>
+    <t>136804304</t>
+  </si>
+  <si>
+    <t>136798866</t>
+  </si>
+  <si>
+    <t>136787620</t>
+  </si>
+  <si>
+    <t>136756475</t>
+  </si>
+  <si>
+    <t>136821256</t>
+  </si>
+  <si>
+    <t>136815577</t>
+  </si>
+  <si>
+    <t>136831227</t>
+  </si>
+  <si>
+    <t>136828937</t>
+  </si>
+  <si>
+    <t>136823111</t>
+  </si>
+  <si>
+    <t>136823219</t>
+  </si>
+  <si>
+    <t>136823783</t>
+  </si>
+  <si>
+    <t>136832828</t>
+  </si>
+  <si>
+    <t>136878558</t>
+  </si>
+  <si>
+    <t>136831744</t>
+  </si>
+  <si>
+    <t>136833555</t>
+  </si>
+  <si>
+    <t>136872045</t>
+  </si>
+  <si>
+    <t>136860566</t>
+  </si>
+  <si>
+    <t>136821297</t>
+  </si>
+  <si>
+    <t>136833725</t>
   </si>
   <si>
     <t>Relatório de Recusas 23.02.2026 a 01.03.2026</t>
@@ -561,7 +543,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -593,7 +575,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136739463</v>
+        <v>136798731</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -602,7 +584,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -620,7 +602,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -638,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -656,7 +638,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -674,7 +656,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -692,7 +674,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -710,7 +692,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -728,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -746,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -764,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -782,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -800,7 +782,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -818,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -836,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -854,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -872,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -890,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -908,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -926,7 +908,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -944,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -962,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -980,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -998,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1016,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1034,7 +1016,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1052,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1070,7 +1052,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1088,111 +1070,9 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1210,31 +1090,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BD81A0-B131-4C3E-8462-71F1AC5F8329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B4D931-E139-4364-9C14-08FFCE3FF60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,91 +54,82 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 26.02.2026</t>
-  </si>
-  <si>
-    <t>136722239</t>
-  </si>
-  <si>
-    <t>136731087</t>
-  </si>
-  <si>
-    <t>136736113</t>
-  </si>
-  <si>
-    <t>136728596</t>
-  </si>
-  <si>
-    <t>136793825</t>
-  </si>
-  <si>
-    <t>136803786</t>
-  </si>
-  <si>
-    <t>136791849</t>
-  </si>
-  <si>
-    <t>136781844</t>
-  </si>
-  <si>
-    <t>136804304</t>
-  </si>
-  <si>
-    <t>136798866</t>
-  </si>
-  <si>
-    <t>136787620</t>
-  </si>
-  <si>
-    <t>136756475</t>
-  </si>
-  <si>
-    <t>136821256</t>
-  </si>
-  <si>
-    <t>136815577</t>
-  </si>
-  <si>
-    <t>136831227</t>
-  </si>
-  <si>
-    <t>136828937</t>
-  </si>
-  <si>
-    <t>136823111</t>
-  </si>
-  <si>
-    <t>136823219</t>
-  </si>
-  <si>
-    <t>136823783</t>
-  </si>
-  <si>
-    <t>136832828</t>
-  </si>
-  <si>
-    <t>136878558</t>
-  </si>
-  <si>
-    <t>136831744</t>
-  </si>
-  <si>
-    <t>136833555</t>
-  </si>
-  <si>
-    <t>136872045</t>
-  </si>
-  <si>
-    <t>136860566</t>
-  </si>
-  <si>
-    <t>136821297</t>
-  </si>
-  <si>
-    <t>136833725</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 23.02.2026 a 01.03.2026</t>
+    <t>Relatório de Recusas Santander - 27 e 28.02.2026</t>
+  </si>
+  <si>
+    <t>136754063</t>
+  </si>
+  <si>
+    <t>136761293</t>
+  </si>
+  <si>
+    <t>136768342</t>
+  </si>
+  <si>
+    <t>136740031</t>
+  </si>
+  <si>
+    <t>136805982</t>
+  </si>
+  <si>
+    <t>136816181</t>
+  </si>
+  <si>
+    <t>136770962</t>
+  </si>
+  <si>
+    <t>136885073</t>
+  </si>
+  <si>
+    <t>136899823</t>
+  </si>
+  <si>
+    <t>136877510</t>
+  </si>
+  <si>
+    <t>136843279</t>
+  </si>
+  <si>
+    <t>136886579</t>
+  </si>
+  <si>
+    <t>136851850</t>
+  </si>
+  <si>
+    <t>136865550</t>
+  </si>
+  <si>
+    <t>136821706</t>
+  </si>
+  <si>
+    <t>136915804</t>
+  </si>
+  <si>
+    <t>136902169</t>
+  </si>
+  <si>
+    <t>136907420</t>
+  </si>
+  <si>
+    <t>136856830</t>
+  </si>
+  <si>
+    <t>136880290</t>
+  </si>
+  <si>
+    <t>136876846</t>
+  </si>
+  <si>
+    <t>136881108</t>
+  </si>
+  <si>
+    <t>136880952</t>
+  </si>
+  <si>
+    <t>136839230</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 23.02.2026 a 01.03.2026 (1)</t>
   </si>
 </sst>
 </file>
@@ -543,7 +534,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -575,7 +566,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136798731</v>
+        <v>136754543</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -584,7 +575,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -602,7 +593,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -620,7 +611,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -638,7 +629,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -656,7 +647,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -674,7 +665,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -692,7 +683,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -710,7 +701,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -728,7 +719,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -746,7 +737,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -764,7 +755,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -782,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -800,7 +791,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -818,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -836,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -854,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -872,7 +863,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -890,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -908,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -926,7 +917,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -944,7 +935,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -962,7 +953,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -980,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -998,7 +989,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1016,7 +1007,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1024,57 +1015,10 @@
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F28"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
